--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 00:54:12</t>
+          <t>2026-07-08 03:00:37</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 00:54:12</t>
+          <t>2026-07-08 03:00:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 03:00:37</t>
+          <t>2026-07-08 05:06:46</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 03:00:37</t>
+          <t>2026-07-08 05:06:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 05:06:46</t>
+          <t>2026-07-08 07:13:04</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 05:06:46</t>
+          <t>2026-07-08 07:13:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,498 +843,1260 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.05</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 07:13:04</t>
+          <t>2026-07-08 09:19:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>South Korean K2 League</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>07:30:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Suwon FC</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Jeonnam Dragons</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X3" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>22</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:19:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chinese Super League</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>08:35:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Shandong Taishan</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Yunnan Yukun</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X4" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:19:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:19:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.05</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-07-08 07:13:04</t>
+      <c r="Q6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:19:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -857,40 +857,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
         <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
         <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
@@ -905,31 +905,31 @@
         <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE2" t="n">
         <v>70</v>
@@ -938,13 +938,13 @@
         <v>14</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
         <v>25</v>
@@ -962,7 +962,7 @@
         <v>17.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP2" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
         <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
@@ -986,10 +986,10 @@
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY2" t="n">
         <v>7.8</v>
@@ -998,7 +998,7 @@
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB2" t="n">
         <v>16.5</v>
@@ -1007,80 +1007,80 @@
         <v>16</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF2" t="n">
         <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO2" t="n">
         <v>3.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 09:19:36</t>
+          <t>2026-07-08 11:26:12</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
         <v>5</v>
@@ -1306,7 +1306,7 @@
         <v>27</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT3" t="n">
         <v>7.8</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
         <v>22</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 09:19:36</t>
+          <t>2026-07-08 11:26:12</t>
         </is>
       </c>
     </row>
@@ -1377,13 +1377,13 @@
         <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
         <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
@@ -1431,7 +1431,7 @@
         <v>110</v>
       </c>
       <c r="AB4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC4" t="n">
         <v>14</v>
@@ -1473,19 +1473,19 @@
         <v>30</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR4" t="n">
         <v>5.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
@@ -1494,7 +1494,7 @@
         <v>4.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1503,19 +1503,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA4" t="n">
         <v>5.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC4" t="n">
         <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
         <v>5.3</v>
@@ -1527,68 +1527,68 @@
         <v>19</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BN4" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BR4" t="n">
         <v>24</v>
       </c>
       <c r="BS4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BV4" t="n">
         <v>40</v>
       </c>
       <c r="BW4" t="n">
-        <v>17.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4" t="n">
         <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>17.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 09:19:36</t>
+          <t>2026-07-08 11:26:12</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 09:19:36</t>
+          <t>2026-07-08 11:26:12</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 09:19:36</t>
+          <t>2026-07-08 11:26:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="G2" t="n">
         <v>2.12</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
         <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.44</v>
@@ -884,10 +884,10 @@
         <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
         <v>2.02</v>
@@ -896,7 +896,7 @@
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
         <v>1.84</v>
@@ -956,7 +956,7 @@
         <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
         <v>17.5</v>
@@ -1022,7 +1022,7 @@
         <v>3.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
@@ -1040,7 +1040,7 @@
         <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP2" t="n">
         <v>15.5</v>
@@ -1067,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
         <v>8.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 11:26:12</t>
+          <t>2026-07-08 13:33:28</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1165,7 +1165,7 @@
         <v>1.92</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
@@ -1177,10 +1177,10 @@
         <v>100</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
         <v>21</v>
@@ -1225,19 +1225,19 @@
         <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="AS3" t="n">
         <v>1.01</v>
       </c>
       <c r="AT3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU3" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AV3" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AW3" t="n">
         <v>1.01</v>
@@ -1276,13 +1276,13 @@
         <v>3.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1300,7 +1300,7 @@
         <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
         <v>27</v>
@@ -1312,7 +1312,7 @@
         <v>7.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 11:26:12</t>
+          <t>2026-07-08 13:33:28</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H4" t="n">
         <v>4.3</v>
@@ -1407,7 +1407,7 @@
         <v>1.94</v>
       </c>
       <c r="T4" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="U4" t="n">
         <v>2.88</v>
@@ -1416,7 +1416,7 @@
         <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X4" t="n">
         <v>44</v>
@@ -1446,7 +1446,7 @@
         <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
         <v>17</v>
@@ -1461,40 +1461,40 @@
         <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AM4" t="n">
         <v>55</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AO4" t="n">
         <v>30</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1503,22 +1503,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
         <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
         <v>4.5</v>
@@ -1530,13 +1530,13 @@
         <v>5.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1548,16 +1548,16 @@
         <v>5.3</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP4" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
         <v>8</v>
@@ -1566,16 +1566,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BX4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
         <v>9.800000000000001</v>
@@ -1584,18 +1584,18 @@
         <v>10.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 11:26:12</t>
+          <t>2026-07-08 13:33:28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,234 +1605,234 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>1.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X5" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
         <v>1.01</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,261 +1842,769 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 11:26:12</t>
+          <t>2026-07-08 13:33:28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X6" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:33:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:33:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.05</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q8" t="n">
         <v>1.01</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-07-08 11:26:12</t>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:33:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -875,7 +875,7 @@
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
@@ -884,7 +884,7 @@
         <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
         <v>1.84</v>
@@ -1022,7 +1022,7 @@
         <v>3.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
@@ -1040,7 +1040,7 @@
         <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP2" t="n">
         <v>15.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
         <v>1.92</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
@@ -1180,7 +1180,7 @@
         <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
         <v>21</v>
@@ -1225,7 +1225,7 @@
         <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
         <v>1.01</v>
@@ -1294,7 +1294,7 @@
         <v>5</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BP3" t="n">
         <v>14</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>
@@ -1407,10 +1407,10 @@
         <v>1.94</v>
       </c>
       <c r="T4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
         <v>1.25</v>
@@ -1425,7 +1425,7 @@
         <v>36</v>
       </c>
       <c r="Z4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA4" t="n">
         <v>110</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>
@@ -1619,28 +1619,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="H5" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
         <v>4.5</v>
@@ -1649,136 +1649,136 @@
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
         <v>1.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y5" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH5" t="n">
         <v>19.5</v>
       </c>
-      <c r="AG5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>19</v>
-      </c>
       <c r="AI5" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AM5" t="n">
         <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AP5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
         <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AW5" t="n">
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD5" t="n">
         <v>21</v>
       </c>
-      <c r="BC5" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
         <v>2.22</v>
@@ -1891,7 +1891,7 @@
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
@@ -1903,7 +1903,7 @@
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
         <v>1.69</v>
@@ -1918,7 +1918,7 @@
         <v>1.62</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V6" t="n">
         <v>1.37</v>
@@ -1996,7 +1996,7 @@
         <v>9.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
         <v>11.5</v>
@@ -2038,55 +2038,55 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P7" t="n">
-        <v>1.05</v>
+        <v>1.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-08 13:33:28</t>
+          <t>2026-07-08 15:40:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1022,7 +1022,7 @@
         <v>3.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R3" t="n">
         <v>1.41</v>
@@ -1153,7 +1153,7 @@
         <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U3" t="n">
         <v>2.16</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
         <v>1.91</v>
       </c>
       <c r="S4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T4" t="n">
         <v>1.4</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,175 +1610,175 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trans Narva</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.28</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>1.08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>1.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>2.78</v>
+        <v>1.56</v>
       </c>
       <c r="T5" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1835,21 +1835,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>San Martin de Burzaco</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>1.08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>1.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.72</v>
+        <v>1.56</v>
       </c>
       <c r="T6" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,189 +2113,189 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.68</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.56</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="X7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
         <v>9.4</v>
       </c>
-      <c r="Y7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>16</v>
-      </c>
       <c r="BG7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
         <v>1.01</v>
@@ -2307,13 +2307,13 @@
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
         <v>1.01</v>
@@ -2325,7 +2325,7 @@
         <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
         <v>1.01</v>
@@ -2343,268 +2343,5094 @@
         <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-08 15:40:20</t>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>46</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Arsenal de Sarandi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Defensores Unidos</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K9" t="n">
+        <v>950</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Deportivo Laferrere</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Deportivo Armenio</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K10" t="n">
+        <v>950</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Talleres (RE)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Flandria</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Uai Urquiza</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Deportivo Merlo</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K12" t="n">
+        <v>950</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Brown de Adrogue</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CA Ituzaingo</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K13" t="n">
+        <v>950</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Excursionistas</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Comunicaciones B Aires</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K14" t="n">
+        <v>950</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Longford</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>130</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>950</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Athlone Town</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Wexford F.C</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kerry FC</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Finn Harps</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Drogheda</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X20" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Waterford</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>St Patricks</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X21" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Aegir</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>HK Kopavogur</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>48</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Leiknir R</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Grotta</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X23" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Throttur</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X24" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Njardvik</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Grindavik</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="X25" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>17</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>12</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>1.05</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-07-08 15:40:20</t>
+      <c r="Q27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-07-08 17:49:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB27"/>
+  <dimension ref="A1:CB31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,22 +869,22 @@
         <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
         <v>1.84</v>
@@ -896,7 +896,7 @@
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
         <v>1.84</v>
@@ -962,7 +962,7 @@
         <v>17.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="n">
         <v>10</v>
@@ -1007,7 +1007,7 @@
         <v>16</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
         <v>6.4</v>
@@ -1022,40 +1022,40 @@
         <v>3.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP2" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
         <v>34</v>
       </c>
       <c r="BS2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT2" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>8</v>
       </c>
       <c r="BU2" t="n">
         <v>4.4</v>
@@ -1064,23 +1064,23 @@
         <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>32</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
         <v>2.08</v>
@@ -1120,7 +1120,7 @@
         <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
         <v>3.65</v>
@@ -1150,13 +1150,13 @@
         <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T3" t="n">
         <v>1.71</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
         <v>1.28</v>
@@ -1216,7 +1216,7 @@
         <v>15</v>
       </c>
       <c r="AO3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
         <v>12.5</v>
@@ -1282,31 +1282,31 @@
         <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP3" t="n">
         <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>7.8</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
         <v>22</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G4" t="n">
         <v>1.81</v>
@@ -1374,7 +1374,7 @@
         <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
         <v>4.4</v>
@@ -1413,7 +1413,7 @@
         <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W4" t="n">
         <v>2.24</v>
@@ -1428,7 +1428,7 @@
         <v>46</v>
       </c>
       <c r="AA4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB4" t="n">
         <v>20</v>
@@ -1437,7 +1437,7 @@
         <v>14</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
         <v>46</v>
@@ -1452,7 +1452,7 @@
         <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ4" t="n">
         <v>25</v>
@@ -1476,25 +1476,25 @@
         <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
         <v>6.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1503,7 +1503,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA4" t="n">
         <v>6.8</v>
@@ -1515,10 +1515,10 @@
         <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
         <v>4.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
         <v>1.04</v>
       </c>
-      <c r="G5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
         <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.04</v>
       </c>
-      <c r="G6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -1921,7 +1921,7 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -2136,13 +2136,13 @@
         <v>3.35</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.28</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
         <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R8" t="n">
         <v>1.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,13 +2659,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q9" t="n">
         <v>1.01</v>
@@ -2674,7 +2674,7 @@
         <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
         <v>1.04</v>
       </c>
-      <c r="G10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O10" t="n">
         <v>1.01</v>
@@ -2937,10 +2937,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -3134,22 +3134,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Talleres (RE)</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
@@ -3158,7 +3158,7 @@
         <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P11" t="n">
         <v>1.09</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Q11" t="n">
         <v>1.01</v>
       </c>
       <c r="R11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S11" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O12" t="n">
         <v>1.01</v>
@@ -3433,10 +3433,10 @@
         <v>1.01</v>
       </c>
       <c r="R12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3690,7 +3690,7 @@
         <v>1.08</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3699,7 +3699,7 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3932,19 +3932,19 @@
         <v>1.08</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q14" t="n">
         <v>1.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S14" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G15" t="n">
-        <v>1.41</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4183,22 +4183,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>1.09</v>
       </c>
       <c r="O15" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>1.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>1.51</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4207,10 +4207,10 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4225,7 +4225,7 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
         <v>1000</v>
@@ -4237,7 +4237,7 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
         <v>1000</v>
@@ -4279,7 +4279,7 @@
         <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
         <v>1.03</v>
@@ -4291,7 +4291,7 @@
         <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
         <v>1.03</v>
@@ -4321,75 +4321,75 @@
         <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,114 +4399,114 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Argentino de Merlo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>2.68</v>
+        <v>1.85</v>
       </c>
       <c r="I16" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>1.08</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9</v>
+        <v>1.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="S16" t="n">
-        <v>2.66</v>
+        <v>1.49</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
         <v>1000</v>
@@ -4524,34 +4524,34 @@
         <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
         <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
         <v>1.03</v>
@@ -4560,7 +4560,7 @@
         <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
         <v>1.03</v>
@@ -4575,68 +4575,68 @@
         <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -4658,55 +4658,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
         <v>3.65</v>
       </c>
-      <c r="I17" t="n">
-        <v>5.6</v>
-      </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.52</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>2.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.84</v>
+        <v>1.54</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>2.46</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -4715,52 +4715,52 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
         <v>1000</v>
@@ -4778,43 +4778,43 @@
         <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
         <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
         <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
         <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
         <v>1.03</v>
@@ -4829,58 +4829,58 @@
         <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
         <v>1.79</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
         <v>2.96</v>
@@ -5092,49 +5092,49 @@
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN18" t="n">
         <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,31 +5166,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="I19" t="n">
-        <v>3.65</v>
+        <v>5.9</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,196 +5199,196 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P19" t="n">
         <v>2.34</v>
       </c>
-      <c r="O19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.26</v>
-      </c>
       <c r="Q19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T19" t="n">
         <v>1.54</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V19" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7</v>
+        <v>2.32</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>2.9</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,229 +5420,229 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1.66</v>
       </c>
-      <c r="G20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.53</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="T20" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="U20" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="X20" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK20" t="n">
         <v>34</v>
       </c>
-      <c r="Z20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>22</v>
-      </c>
       <c r="AL20" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.66</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.68</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.78</v>
+        <v>14</v>
       </c>
       <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK20" t="n">
         <v>2.9</v>
       </c>
-      <c r="AT20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BO20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ20" t="n">
         <v>3.3</v>
       </c>
-      <c r="BP20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BR20" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV20" t="n">
         <v>29</v>
       </c>
-      <c r="BS20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>50</v>
-      </c>
       <c r="BW20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,251 +5669,251 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5.5</v>
+        <v>1.31</v>
       </c>
       <c r="G21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
         <v>6.2</v>
       </c>
-      <c r="H21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V21" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X21" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>970</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>210</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>140</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AU21" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BN21" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI21" t="n">
+      <c r="BO21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS21" t="n">
         <v>3.2</v>
       </c>
-      <c r="BJ21" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BT21" t="n">
-        <v>4.3</v>
+        <v>19</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="BV21" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA21" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.75</v>
+        <v>1.79</v>
       </c>
       <c r="G22" t="n">
-        <v>6.2</v>
+        <v>2.28</v>
       </c>
       <c r="H22" t="n">
-        <v>1.59</v>
+        <v>3.65</v>
       </c>
       <c r="I22" t="n">
-        <v>1.72</v>
+        <v>5.6</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>6.4</v>
+        <v>2.52</v>
       </c>
       <c r="O22" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="P22" t="n">
-        <v>2.76</v>
+        <v>1.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.37</v>
+        <v>1.84</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.82</v>
+        <v>3.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="W22" t="n">
-        <v>1.19</v>
+        <v>1.78</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH22" t="n">
         <v>28</v>
       </c>
-      <c r="AB22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AC22" t="n">
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR22" t="n">
         <v>20</v>
       </c>
-      <c r="AD22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AS22" t="n">
-        <v>2</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.06</v>
+        <v>5.7</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.95</v>
+        <v>5.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.92</v>
+        <v>11.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.97</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>2.16</v>
+        <v>7.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>2.02</v>
+        <v>6.8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.99</v>
+        <v>12.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.02</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>2.16</v>
+        <v>15</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.16</v>
+        <v>14</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.16</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.16</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.14</v>
+        <v>2.64</v>
       </c>
       <c r="BJ22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>2.08</v>
+        <v>1.34</v>
       </c>
       <c r="BN22" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="BP22" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="BR22" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="BT22" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.64</v>
+        <v>1.34</v>
       </c>
       <c r="BV22" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.87</v>
+        <v>1.34</v>
       </c>
       <c r="BX22" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.97</v>
+        <v>1.34</v>
       </c>
       <c r="BZ22" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,189 +6177,189 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.38</v>
+        <v>5.5</v>
       </c>
       <c r="G23" t="n">
-        <v>2.64</v>
+        <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>2.68</v>
+        <v>1.67</v>
       </c>
       <c r="I23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X23" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU23" t="n">
         <v>3.25</v>
       </c>
-      <c r="J23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="AV23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA23" t="n">
         <v>4.5</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X23" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="BJ23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK23" t="n">
         <v>5.3</v>
@@ -6368,53 +6368,53 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>2.02</v>
+        <v>9.6</v>
       </c>
       <c r="BN23" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.88</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.93</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT23" t="n">
-        <v>9.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="BU23" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.93</v>
+        <v>5.3</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.95</v>
+        <v>7.4</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.86</v>
+        <v>6.8</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -6436,239 +6436,239 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="G24" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="H24" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="J24" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="K24" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="P24" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="R24" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="S24" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="T24" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="U24" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="V24" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="W24" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="X24" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Z24" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AA24" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AB24" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AC24" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AD24" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AH24" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AJ24" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BG24" t="n">
         <v>3.5</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BH24" t="n">
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
@@ -6690,73 +6690,73 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="G25" t="n">
-        <v>1.63</v>
+        <v>2.62</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>2.68</v>
       </c>
       <c r="I25" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="J25" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K25" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="O25" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="P25" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R25" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="S25" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="T25" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="W25" t="n">
-        <v>2.58</v>
+        <v>1.62</v>
       </c>
       <c r="X25" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
         <v>1000</v>
@@ -6771,10 +6771,10 @@
         <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF25" t="n">
         <v>1000</v>
@@ -6783,16 +6783,16 @@
         <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ25" t="n">
-        <v>17.5</v>
+        <v>40</v>
       </c>
       <c r="AK25" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
         <v>34</v>
@@ -6801,135 +6801,135 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.49</v>
+        <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.56</v>
+        <v>10</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="BJ25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BK25" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="BN25" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="BP25" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BR25" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="BT25" t="n">
-        <v>14.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.92</v>
+        <v>4.4</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="BZ25" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,498 +6939,1514 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.86</v>
+        <v>3.85</v>
       </c>
       <c r="G26" t="n">
-        <v>1.98</v>
+        <v>4.7</v>
       </c>
       <c r="H26" t="n">
-        <v>5.1</v>
+        <v>1.77</v>
       </c>
       <c r="I26" t="n">
-        <v>5.6</v>
+        <v>1.93</v>
       </c>
       <c r="J26" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>1.21</v>
       </c>
       <c r="M26" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>2.72</v>
+        <v>6.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="P26" t="n">
-        <v>1.58</v>
+        <v>2.82</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.52</v>
+        <v>1.44</v>
       </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>1.74</v>
       </c>
       <c r="S26" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2</v>
+        <v>1.49</v>
       </c>
       <c r="U26" t="n">
-        <v>1.72</v>
+        <v>2.64</v>
       </c>
       <c r="V26" t="n">
-        <v>1.21</v>
+        <v>2.06</v>
       </c>
       <c r="W26" t="n">
-        <v>2.02</v>
+        <v>1.27</v>
       </c>
       <c r="X26" t="n">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="Y26" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z26" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AA26" t="n">
-        <v>200</v>
+        <v>24</v>
       </c>
       <c r="AB26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX26" t="n">
         <v>6.4</v>
       </c>
-      <c r="AC26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>9</v>
-      </c>
       <c r="AY26" t="n">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>9.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="BA26" t="n">
-        <v>12.5</v>
+        <v>2.38</v>
       </c>
       <c r="BB26" t="n">
-        <v>8.6</v>
+        <v>2.94</v>
       </c>
       <c r="BC26" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="BD26" t="n">
-        <v>38</v>
+        <v>6.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>13</v>
+        <v>2.9</v>
       </c>
       <c r="BF26" t="n">
-        <v>16</v>
+        <v>2.38</v>
       </c>
       <c r="BG26" t="n">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="BH26" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BN26" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP26" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BT26" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-08 17:49:14</t>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Njardvik</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Grindavik</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>17</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-07-08 19:58:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Albion FC</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-07-08 19:58:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>12</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-07-08 19:58:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CD Leones del Norte</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Ecu)</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>44</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>40</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-07-08 19:58:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>1.05</v>
       </c>
-      <c r="Q27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB27" t="inlineStr">
-        <is>
-          <t>2026-07-08 17:49:14</t>
+      <c r="Q31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>2026-07-08 19:58:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G2" t="n">
         <v>2.12</v>
@@ -872,7 +872,7 @@
         <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.44</v>
@@ -899,10 +899,10 @@
         <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>1.28</v>
@@ -920,7 +920,7 @@
         <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB2" t="n">
         <v>8.800000000000001</v>
@@ -932,7 +932,7 @@
         <v>19.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
         <v>14</v>
@@ -971,7 +971,7 @@
         <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS2" t="n">
         <v>6.4</v>
@@ -1010,13 +1010,13 @@
         <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
         <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.3</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
         <v>3.9</v>
@@ -1162,7 +1162,7 @@
         <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>1.19</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="R4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S4" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="X4" t="n">
         <v>44</v>
@@ -1425,13 +1425,13 @@
         <v>36</v>
       </c>
       <c r="Z4" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA4" t="n">
         <v>100</v>
       </c>
       <c r="AB4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AC4" t="n">
         <v>14</v>
@@ -1440,22 +1440,22 @@
         <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
         <v>44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1473,55 +1473,55 @@
         <v>30</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX4" t="n">
         <v>6</v>
       </c>
-      <c r="AW4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>13</v>
-      </c>
       <c r="AY4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BG4" t="n">
         <v>19</v>
@@ -1536,13 +1536,13 @@
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="BN4" t="n">
         <v>5.3</v>
@@ -1554,41 +1554,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="G8" t="n">
         <v>2.22</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2674,7 +2674,7 @@
         <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2683,10 +2683,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3167,7 +3167,7 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="O11" t="n">
         <v>1.01</v>
@@ -3179,7 +3179,7 @@
         <v>1.01</v>
       </c>
       <c r="R11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S11" t="n">
         <v>1.01</v>
@@ -3191,10 +3191,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3445,10 +3445,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3702,7 +3702,7 @@
         <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3929,7 +3929,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O14" t="n">
         <v>1.02</v>
@@ -3938,7 +3938,7 @@
         <v>1.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R14" t="n">
         <v>1.08</v>
@@ -3953,10 +3953,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O15" t="n">
         <v>1.01</v>
@@ -4198,7 +4198,7 @@
         <v>1.08</v>
       </c>
       <c r="S15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4207,10 +4207,10 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4437,7 +4437,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O16" t="n">
         <v>1.01</v>
@@ -4452,7 +4452,7 @@
         <v>1.08</v>
       </c>
       <c r="S16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -4461,10 +4461,10 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>2.34</v>
       </c>
       <c r="O17" t="n">
         <v>1.19</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
         <v>1.79</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
         <v>2.96</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
         <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,16 +5199,16 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>1.18</v>
       </c>
       <c r="P19" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="R19" t="n">
         <v>1.49</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>1.31</v>
       </c>
       <c r="G21" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="H21" t="n">
         <v>4.1</v>
@@ -5707,7 +5707,7 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O21" t="n">
         <v>1.23</v>
@@ -5716,13 +5716,13 @@
         <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R21" t="n">
         <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -5734,7 +5734,7 @@
         <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -6200,10 +6200,10 @@
         <v>1.67</v>
       </c>
       <c r="I23" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="J23" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K23" t="n">
         <v>4.4</v>
@@ -6239,7 +6239,7 @@
         <v>1.94</v>
       </c>
       <c r="V23" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="W23" t="n">
         <v>1.19</v>
@@ -6260,7 +6260,7 @@
         <v>25</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD23" t="n">
         <v>12.5</v>
@@ -6272,10 +6272,10 @@
         <v>65</v>
       </c>
       <c r="AG23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>44</v>
@@ -6293,40 +6293,40 @@
         <v>140</v>
       </c>
       <c r="AN23" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AO23" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ23" t="n">
         <v>7.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW23" t="n">
         <v>4.1</v>
       </c>
-      <c r="AU23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4</v>
-      </c>
       <c r="AX23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ23" t="n">
         <v>4.2</v>
@@ -6341,13 +6341,13 @@
         <v>4.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG23" t="n">
         <v>6.8</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
         <v>1.58</v>
       </c>
       <c r="I24" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="J24" t="n">
         <v>4.8</v>
@@ -6478,13 +6478,13 @@
         <v>3.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="R24" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="S24" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="T24" t="n">
         <v>1.33</v>
@@ -6493,7 +6493,7 @@
         <v>2.2</v>
       </c>
       <c r="V24" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="W24" t="n">
         <v>1.21</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
         <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M25" t="n">
         <v>1.02</v>
@@ -6729,16 +6729,16 @@
         <v>1.14</v>
       </c>
       <c r="P25" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q25" t="n">
         <v>1.48</v>
       </c>
       <c r="R25" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="S25" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T25" t="n">
         <v>1.38</v>
@@ -6765,7 +6765,7 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC25" t="n">
         <v>1000</v>
@@ -6894,10 +6894,10 @@
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BT25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU25" t="n">
         <v>4.4</v>
@@ -6909,20 +6909,20 @@
         <v>1.93</v>
       </c>
       <c r="BX25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY25" t="n">
         <v>1.95</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -6953,19 +6953,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G26" t="n">
         <v>4.7</v>
       </c>
       <c r="H26" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="I26" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K26" t="n">
         <v>5</v>
@@ -6977,19 +6977,19 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.15</v>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q26" t="n">
         <v>1.44</v>
       </c>
       <c r="R26" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S26" t="n">
         <v>2.1</v>
@@ -7001,7 +7001,7 @@
         <v>2.64</v>
       </c>
       <c r="V26" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="W26" t="n">
         <v>1.27</v>
@@ -7031,7 +7031,7 @@
         <v>970</v>
       </c>
       <c r="AF26" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AG26" t="n">
         <v>20</v>
@@ -7061,19 +7061,19 @@
         <v>970</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="AQ26" t="n">
         <v>5.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS26" t="n">
         <v>2.7</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.36</v>
+        <v>4.4</v>
       </c>
       <c r="AU26" t="n">
         <v>4.7</v>
@@ -7088,13 +7088,13 @@
         <v>6.4</v>
       </c>
       <c r="AY26" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AZ26" t="n">
         <v>5.2</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.38</v>
+        <v>4.4</v>
       </c>
       <c r="BB26" t="n">
         <v>2.94</v>
@@ -7109,7 +7109,7 @@
         <v>2.9</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="BG26" t="n">
         <v>3.7</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="G27" t="n">
         <v>1.65</v>
       </c>
       <c r="H27" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J27" t="n">
         <v>4.3</v>
       </c>
       <c r="K27" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7231,22 +7231,22 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
         <v>1.18</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="T27" t="n">
         <v>1.64</v>
@@ -7255,7 +7255,7 @@
         <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W27" t="n">
         <v>2.56</v>
@@ -7309,85 +7309,85 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BD27" t="n">
         <v>20</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="BF27" t="n">
         <v>1.16</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="BJ27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK27" t="n">
-        <v>7</v>
+        <v>1.94</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="BN27" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO27" t="n">
         <v>3.1</v>
@@ -7396,41 +7396,41 @@
         <v>12</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="BR27" t="n">
         <v>26</v>
       </c>
       <c r="BS27" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="BT27" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BU27" t="n">
-        <v>7</v>
+        <v>1.98</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="BZ27" t="n">
         <v>17</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -7715,40 +7715,40 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="G29" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="H29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I29" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K29" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L29" t="n">
         <v>1.45</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O29" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P29" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R29" t="n">
         <v>1.21</v>
@@ -7757,7 +7757,7 @@
         <v>5.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U29" t="n">
         <v>1.72</v>
@@ -7766,10 +7766,10 @@
         <v>1.21</v>
       </c>
       <c r="W29" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X29" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y29" t="n">
         <v>13.5</v>
@@ -7793,7 +7793,7 @@
         <v>120</v>
       </c>
       <c r="AF29" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG29" t="n">
         <v>11</v>
@@ -7832,7 +7832,7 @@
         <v>27</v>
       </c>
       <c r="AS29" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT29" t="n">
         <v>5.7</v>
@@ -7841,40 +7841,40 @@
         <v>7</v>
       </c>
       <c r="AV29" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AY29" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA29" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BD29" t="n">
         <v>38</v>
       </c>
       <c r="BE29" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF29" t="n">
         <v>16</v>
       </c>
       <c r="BG29" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BH29" t="n">
         <v>2.8</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -8005,7 +8005,7 @@
         <v>2.02</v>
       </c>
       <c r="R30" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S30" t="n">
         <v>3.5</v>
@@ -8014,7 +8014,7 @@
         <v>1.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="V30" t="n">
         <v>1.72</v>
@@ -8050,7 +8050,7 @@
         <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>
@@ -8223,230 +8223,230 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P31" t="n">
-        <v>1.05</v>
+        <v>1.54</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-08 19:58:26</t>
+          <t>2026-07-08 22:07:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB31"/>
+  <dimension ref="A1:CB32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H2" t="n">
         <v>4.1</v>
@@ -875,7 +875,7 @@
         <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
@@ -884,7 +884,7 @@
         <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
         <v>1.84</v>
@@ -899,16 +899,16 @@
         <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U2" t="n">
         <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X2" t="n">
         <v>15</v>
@@ -1022,7 +1022,7 @@
         <v>3.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN2" t="n">
         <v>4.8</v>
@@ -1046,16 +1046,16 @@
         <v>15.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
         <v>34</v>
       </c>
       <c r="BS2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT2" t="n">
         <v>8</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>7.8</v>
       </c>
       <c r="BU2" t="n">
         <v>4.4</v>
@@ -1064,23 +1064,23 @@
         <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
         <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>32</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
         <v>3.9</v>
@@ -1162,7 +1162,7 @@
         <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H4" t="n">
         <v>4.5</v>
@@ -1389,142 +1389,142 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
         <v>1.12</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q4" t="n">
         <v>1.39</v>
       </c>
       <c r="R4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S4" t="n">
         <v>1.98</v>
       </c>
       <c r="T4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W4" t="n">
         <v>2.32</v>
       </c>
       <c r="X4" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="Z4" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AA4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
         <v>18.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL4" t="n">
         <v>22</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>23</v>
       </c>
       <c r="AM4" t="n">
         <v>55</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="AU4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="BB4" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BC4" t="n">
         <v>13.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BE4" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BF4" t="n">
         <v>4.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH4" t="n">
         <v>5.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
         <v>16.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AA7" t="n">
         <v>65</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -2626,22 +2626,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandi</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
@@ -2662,10 +2662,10 @@
         <v>1.09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q9" t="n">
         <v>1.01</v>
@@ -2674,7 +2674,7 @@
         <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -2880,22 +2880,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Arsenal de Sarandi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2916,10 +2916,10 @@
         <v>1.09</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q10" t="n">
         <v>1.01</v>
@@ -2928,7 +2928,7 @@
         <v>1.08</v>
       </c>
       <c r="S10" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -3134,28 +3134,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CSD Liniers de Ciudad Evita</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sportivo Italiano</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3173,7 +3173,7 @@
         <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Q11" t="n">
         <v>1.01</v>
@@ -3182,7 +3182,7 @@
         <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3194,7 +3194,7 @@
         <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -3388,28 +3388,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Talleres (RE)</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Comunicaciones B Aires</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3424,19 +3424,19 @@
         <v>1.09</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R12" t="n">
         <v>1.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3448,7 +3448,7 @@
         <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -3642,28 +3642,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>Argentino de Merlo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3675,7 +3675,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O13" t="n">
         <v>1.01</v>
@@ -3690,7 +3690,7 @@
         <v>1.08</v>
       </c>
       <c r="S13" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3702,7 +3702,7 @@
         <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -3896,28 +3896,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Comunicaciones B Aires</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3932,19 +3932,19 @@
         <v>1.09</v>
       </c>
       <c r="O14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>1.08</v>
       </c>
       <c r="S14" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3953,7 +3953,7 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -4150,28 +4150,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4183,13 +4183,13 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O15" t="n">
         <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q15" t="n">
         <v>1.01</v>
@@ -4198,7 +4198,7 @@
         <v>1.08</v>
       </c>
       <c r="S15" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -4404,28 +4404,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Argentino de Merlo</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4437,7 +4437,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="O16" t="n">
         <v>1.01</v>
@@ -4452,7 +4452,7 @@
         <v>1.08</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -4464,7 +4464,7 @@
         <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -4691,10 +4691,10 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P17" t="n">
         <v>2.36</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,229 +4912,229 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.66</v>
+        <v>1.66</v>
       </c>
       <c r="G18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X18" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI18" t="n">
         <v>3.05</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="BJ18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
         <v>3.55</v>
       </c>
-      <c r="K18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.29</v>
+        <v>3.55</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.29</v>
+        <v>2.82</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.29</v>
+        <v>3.15</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.29</v>
+        <v>2.74</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.29</v>
+        <v>3.3</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.29</v>
+        <v>3.35</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,31 +5166,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.66</v>
+        <v>2.62</v>
       </c>
       <c r="G19" t="n">
-        <v>1.75</v>
+        <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>4.9</v>
+        <v>2.48</v>
       </c>
       <c r="I19" t="n">
-        <v>5.9</v>
+        <v>2.88</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,196 +5199,196 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="R19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.49</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.32</v>
-      </c>
       <c r="X19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.78</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.82</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.82</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.82</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="BJ19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.4</v>
+        <v>1.29</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>3.55</v>
+        <v>1.29</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP19" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>7.2</v>
+        <v>1.29</v>
       </c>
       <c r="BR19" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>3.15</v>
+        <v>1.29</v>
       </c>
       <c r="BT19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>6.2</v>
+        <v>1.29</v>
       </c>
       <c r="BV19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>3.3</v>
+        <v>1.29</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.35</v>
+        <v>1.29</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -5420,109 +5420,109 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.24</v>
+        <v>1.31</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>1.43</v>
       </c>
       <c r="H20" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="I20" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -5540,34 +5540,34 @@
         <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
         <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
         <v>1.03</v>
@@ -5576,7 +5576,7 @@
         <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
         <v>1.03</v>
@@ -5591,58 +5591,58 @@
         <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>2.9</v>
+        <v>1.26</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>3.8</v>
+        <v>1.26</v>
       </c>
       <c r="BN20" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>4</v>
+        <v>1.26</v>
       </c>
       <c r="BP20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.3</v>
+        <v>1.26</v>
       </c>
       <c r="BR20" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>3.45</v>
+        <v>1.26</v>
       </c>
       <c r="BT20" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.4</v>
+        <v>1.26</v>
       </c>
       <c r="BV20" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>3.4</v>
+        <v>1.26</v>
       </c>
       <c r="BX20" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.5</v>
+        <v>1.26</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -5674,55 +5674,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.31</v>
+        <v>2.24</v>
       </c>
       <c r="G21" t="n">
-        <v>1.43</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J21" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -5731,52 +5731,52 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>3.35</v>
+        <v>1.5</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF21" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL21" t="n">
         <v>1000</v>
@@ -5794,34 +5794,34 @@
         <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
         <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BA21" t="n">
         <v>1.03</v>
@@ -5830,7 +5830,7 @@
         <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BD21" t="n">
         <v>1.03</v>
@@ -5845,55 +5845,55 @@
         <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BJ21" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="BK21" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BN21" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="BP21" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="BR21" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BS21" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BT21" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="BU21" t="n">
-        <v>2.98</v>
+        <v>4.4</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY21" t="n">
         <v>3.5</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -6203,13 +6203,13 @@
         <v>1.72</v>
       </c>
       <c r="J23" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K23" t="n">
         <v>4.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
@@ -6236,7 +6236,7 @@
         <v>1.84</v>
       </c>
       <c r="U23" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V23" t="n">
         <v>2.38</v>
@@ -6251,13 +6251,13 @@
         <v>10.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA23" t="n">
         <v>970</v>
       </c>
       <c r="AB23" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AC23" t="n">
         <v>970</v>
@@ -6269,7 +6269,7 @@
         <v>22</v>
       </c>
       <c r="AF23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG23" t="n">
         <v>28</v>
@@ -6281,13 +6281,13 @@
         <v>44</v>
       </c>
       <c r="AJ23" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AK23" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL23" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM23" t="n">
         <v>140</v>
@@ -6296,61 +6296,61 @@
         <v>130</v>
       </c>
       <c r="AO23" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AP23" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ23" t="n">
         <v>7.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AS23" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="BH23" t="n">
         <v>3.75</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
         <v>1.58</v>
       </c>
       <c r="I24" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="J24" t="n">
         <v>4.8</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
         <v>970</v>
       </c>
       <c r="AA26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AB26" t="n">
         <v>30</v>
@@ -7034,7 +7034,7 @@
         <v>42</v>
       </c>
       <c r="AG26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH26" t="n">
         <v>970</v>
@@ -7061,58 +7061,58 @@
         <v>970</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AQ26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX26" t="n">
         <v>5.2</v>
       </c>
-      <c r="AR26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AY26" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.4</v>
+        <v>2.84</v>
       </c>
       <c r="BB26" t="n">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BF26" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BG26" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
@@ -7372,22 +7372,22 @@
         <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="BJ27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="BN27" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BO27" t="n">
         <v>3.1</v>
@@ -7396,48 +7396,48 @@
         <v>12</v>
       </c>
       <c r="BQ27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS27" t="n">
         <v>1.96</v>
-      </c>
-      <c r="BR27" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS27" t="n">
-        <v>2.16</v>
       </c>
       <c r="BT27" t="n">
         <v>12.5</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="BZ27" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CA27" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7447,251 +7447,251 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>KA Asvellir</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="G28" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="K28" t="n">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7706,246 +7706,246 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="G29" t="n">
-        <v>1.93</v>
+        <v>2.36</v>
       </c>
       <c r="H29" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="I29" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K29" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BH29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BJ29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BL29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM29" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BN29" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BP29" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BQ29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BR29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BT29" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BU29" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BV29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW29" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BX29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY29" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BZ29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7960,493 +7960,747 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="G30" t="n">
-        <v>3.8</v>
+        <v>1.93</v>
       </c>
       <c r="H30" t="n">
-        <v>2.16</v>
+        <v>5.2</v>
       </c>
       <c r="I30" t="n">
-        <v>2.38</v>
+        <v>5.8</v>
       </c>
       <c r="J30" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K30" t="n">
         <v>3.7</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="O30" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="P30" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="T30" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>1.06</v>
+        <v>1.72</v>
       </c>
       <c r="V30" t="n">
-        <v>1.72</v>
+        <v>1.21</v>
       </c>
       <c r="W30" t="n">
-        <v>1.36</v>
+        <v>2.06</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG30" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK30" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AL30" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.09</v>
+        <v>8.4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.09</v>
+        <v>11.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.09</v>
+        <v>27</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.09</v>
+        <v>14.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.09</v>
+        <v>5.7</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.09</v>
+        <v>7.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.09</v>
+        <v>19.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.09</v>
+        <v>13.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.09</v>
+        <v>8.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.09</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.09</v>
+        <v>14</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.09</v>
+        <v>16.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.07</v>
+        <v>16</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.07</v>
+        <v>38</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.09</v>
+        <v>14.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.09</v>
+        <v>16</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.09</v>
+        <v>14.5</v>
       </c>
       <c r="BH30" t="n">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="BJ30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BK30" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>3.75</v>
+        <v>16</v>
       </c>
       <c r="BN30" t="n">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="BO30" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="BP30" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="BQ30" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>3.55</v>
+        <v>12</v>
       </c>
       <c r="BT30" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV30" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>3.2</v>
+        <v>13.5</v>
       </c>
       <c r="BX30" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>3.45</v>
+        <v>14</v>
       </c>
       <c r="BZ30" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>3.45</v>
+        <v>12</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-08 22:07:18</t>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CD Leones del Norte</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Ecu)</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>2026-07-09 00:16:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="F32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G32" t="n">
         <v>2.04</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H32" t="n">
         <v>4.3</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I32" t="n">
         <v>6.6</v>
       </c>
-      <c r="J31" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="J32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L32" t="n">
         <v>1.46</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M32" t="n">
         <v>1.09</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N32" t="n">
         <v>2.46</v>
       </c>
-      <c r="O31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="O32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P32" t="n">
         <v>1.54</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q32" t="n">
         <v>2.06</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="R32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S32" t="n">
         <v>3.9</v>
       </c>
-      <c r="T31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="T32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.68</v>
       </c>
-      <c r="V31" t="n">
+      <c r="V32" t="n">
         <v>1.19</v>
       </c>
-      <c r="W31" t="n">
+      <c r="W32" t="n">
         <v>1.97</v>
       </c>
-      <c r="X31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y31" t="n">
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
         <v>20</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="Z32" t="n">
         <v>50</v>
       </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
         <v>10</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AC32" t="n">
         <v>11</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AD32" t="n">
         <v>28</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AE32" t="n">
         <v>100</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AF32" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AG32" t="n">
         <v>15.5</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AH32" t="n">
         <v>32</v>
       </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>32</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AK32" t="n">
         <v>34</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AL32" t="n">
         <v>70</v>
       </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
         <v>2.18</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AQ32" t="n">
         <v>1.97</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AR32" t="n">
         <v>25</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AS32" t="n">
         <v>2.18</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AT32" t="n">
         <v>1.79</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AU32" t="n">
         <v>1.82</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AV32" t="n">
         <v>2.02</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AW32" t="n">
         <v>2.14</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="AX32" t="n">
         <v>1.91</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="AY32" t="n">
         <v>1.91</v>
       </c>
-      <c r="AZ31" t="n">
+      <c r="AZ32" t="n">
         <v>2.04</v>
       </c>
-      <c r="BA31" t="n">
+      <c r="BA32" t="n">
         <v>2.18</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BB32" t="n">
         <v>2.04</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BC32" t="n">
         <v>2.04</v>
       </c>
-      <c r="BD31" t="n">
+      <c r="BD32" t="n">
         <v>2.12</v>
       </c>
-      <c r="BE31" t="n">
+      <c r="BE32" t="n">
         <v>2.18</v>
       </c>
-      <c r="BF31" t="n">
+      <c r="BF32" t="n">
         <v>2.18</v>
       </c>
-      <c r="BG31" t="n">
+      <c r="BG32" t="n">
         <v>2.18</v>
       </c>
-      <c r="BH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB31" t="inlineStr">
-        <is>
-          <t>2026-07-08 22:07:18</t>
+      <c r="BH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>2026-07-09 00:16:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -872,7 +872,7 @@
         <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.43</v>
@@ -881,10 +881,10 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
         <v>1.84</v>
@@ -896,10 +896,10 @@
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
         <v>2</v>
@@ -1025,19 +1025,19 @@
         <v>2.66</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO2" t="n">
         <v>3.75</v>
@@ -1046,16 +1046,16 @@
         <v>15.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
         <v>34</v>
       </c>
       <c r="BS2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT2" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>8</v>
       </c>
       <c r="BU2" t="n">
         <v>4.4</v>
@@ -1064,23 +1064,23 @@
         <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>32</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -1111,46 +1111,46 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
         <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
         <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
         <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
         <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
         <v>1.71</v>
@@ -1159,19 +1159,19 @@
         <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA3" t="n">
         <v>100</v>
@@ -1180,25 +1180,25 @@
         <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>60</v>
       </c>
       <c r="AF3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -1207,7 +1207,7 @@
         <v>25</v>
       </c>
       <c r="AL3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -1216,7 +1216,7 @@
         <v>15</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
         <v>12.5</v>
@@ -1228,7 +1228,7 @@
         <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
         <v>8.800000000000001</v>
@@ -1252,7 +1252,7 @@
         <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB3" t="n">
         <v>16.5</v>
@@ -1273,16 +1273,16 @@
         <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,7 +1291,7 @@
         <v>11</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO3" t="n">
         <v>3.75</v>
@@ -1300,16 +1300,16 @@
         <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU3" t="n">
         <v>5.7</v>
@@ -1324,17 +1324,17 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>22</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -1365,127 +1365,127 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="H4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I4" t="n">
         <v>4.5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K4" t="n">
         <v>4.9</v>
       </c>
-      <c r="J4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R4" t="n">
         <v>1.96</v>
       </c>
       <c r="S4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="T4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="U4" t="n">
         <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W4" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="X4" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="Y4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Z4" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE4" t="n">
         <v>50</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
         <v>16</v>
       </c>
       <c r="AI4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM4" t="n">
         <v>42</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>55</v>
-      </c>
       <c r="AN4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AP4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU4" t="n">
         <v>11</v>
@@ -1494,7 +1494,7 @@
         <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX4" t="n">
         <v>12.5</v>
@@ -1509,28 +1509,28 @@
         <v>22</v>
       </c>
       <c r="BB4" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH4" t="n">
         <v>5.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.6</v>
@@ -1542,19 +1542,19 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>3.5</v>
+        <v>13</v>
       </c>
       <c r="BN4" t="n">
         <v>5.3</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1563,10 +1563,10 @@
         <v>8.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
         <v>2.28</v>
@@ -2139,7 +2139,7 @@
         <v>3.75</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
@@ -2151,28 +2151,28 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q7" t="n">
         <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T7" t="n">
         <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V7" t="n">
         <v>1.36</v>
@@ -2184,10 +2184,10 @@
         <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="n">
         <v>65</v>
@@ -2196,7 +2196,7 @@
         <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
         <v>15.5</v>
@@ -2226,7 +2226,7 @@
         <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN7" t="n">
         <v>15.5</v>
@@ -2235,10 +2235,10 @@
         <v>38</v>
       </c>
       <c r="AP7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
         <v>19</v>
@@ -2250,16 +2250,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY7" t="n">
         <v>8.199999999999999</v>
@@ -2271,22 +2271,22 @@
         <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
         <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I8" t="n">
         <v>3.7</v>
@@ -2396,46 +2396,46 @@
         <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
         <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
         <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
         <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
         <v>19.5</v>
@@ -2456,7 +2456,7 @@
         <v>17.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF8" t="n">
         <v>18</v>
@@ -2492,28 +2492,28 @@
         <v>17.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR8" t="n">
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY8" t="n">
         <v>9.800000000000001</v>
@@ -2522,22 +2522,22 @@
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
         <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG8" t="n">
         <v>21</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I17" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J17" t="n">
         <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4691,88 +4691,88 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.54</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.51</v>
       </c>
       <c r="S17" t="n">
         <v>2.46</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP17" t="n">
         <v>1.03</v>
@@ -4802,7 +4802,7 @@
         <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
         <v>1.03</v>
@@ -4823,10 +4823,10 @@
         <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -4924,10 +4924,10 @@
         <v>1.66</v>
       </c>
       <c r="G18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I18" t="n">
         <v>5.9</v>
@@ -4942,13 +4942,13 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P18" t="n">
         <v>2.38</v>
@@ -4957,64 +4957,64 @@
         <v>1.59</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
         <v>1.2</v>
       </c>
       <c r="W18" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X18" t="n">
         <v>32</v>
       </c>
       <c r="Y18" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Z18" t="n">
         <v>65</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB18" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF18" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
         <v>85</v>
       </c>
       <c r="AJ18" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AL18" t="n">
         <v>40</v>
@@ -5023,64 +5023,64 @@
         <v>100</v>
       </c>
       <c r="AN18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX18" t="n">
         <v>10</v>
       </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9</v>
-      </c>
       <c r="AY18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.82</v>
+        <v>7.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC18" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD18" t="n">
         <v>19</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.82</v>
+        <v>8</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.9</v>
+        <v>42</v>
       </c>
       <c r="BH18" t="n">
         <v>5.4</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I19" t="n">
         <v>2.88</v>
@@ -5190,7 +5190,7 @@
         <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,7 +5199,7 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
         <v>1.27</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -5429,115 +5429,115 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G20" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="J20" t="n">
         <v>5.1</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="R20" t="n">
         <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>610</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.03</v>
@@ -5549,10 +5549,10 @@
         <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV20" t="n">
         <v>1.03</v>
@@ -5561,10 +5561,10 @@
         <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
         <v>1.03</v>
@@ -5573,10 +5573,10 @@
         <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD20" t="n">
         <v>1.03</v>
@@ -5585,64 +5585,64 @@
         <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>95</v>
       </c>
       <c r="BH20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.26</v>
+        <v>6.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.26</v>
+        <v>12.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.26</v>
+        <v>6</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.26</v>
+        <v>9</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.26</v>
+        <v>7</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.26</v>
+        <v>12</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.26</v>
+        <v>12</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -5683,28 +5683,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="H21" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="I21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>5.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
         <v>3.5</v>
@@ -5719,10 +5719,10 @@
         <v>1.66</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -5731,52 +5731,52 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
         <v>1000</v>
@@ -5794,43 +5794,43 @@
         <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
         <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
         <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
         <v>1.03</v>
@@ -5848,7 +5848,7 @@
         <v>4.3</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="BJ21" t="n">
         <v>12</v>
@@ -5866,7 +5866,7 @@
         <v>7.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BP21" t="n">
         <v>24</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -5937,166 +5937,166 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="G22" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="H22" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>2.52</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
         <v>1.33</v>
       </c>
       <c r="P22" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V22" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W22" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB22" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG22" t="n">
         <v>11</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AH22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>25</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG22" t="n">
+      <c r="AK22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV22" t="n">
         <v>15</v>
       </c>
-      <c r="AH22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="AW22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD22" t="n">
         <v>32</v>
       </c>
-      <c r="AK22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV22" t="n">
+      <c r="BE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF22" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH22" t="n">
         <v>4</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G23" t="n">
         <v>6.2</v>
@@ -6200,10 +6200,10 @@
         <v>1.67</v>
       </c>
       <c r="I23" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="J23" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
         <v>4.4</v>
@@ -6233,13 +6233,13 @@
         <v>3.15</v>
       </c>
       <c r="T23" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U23" t="n">
         <v>1.96</v>
       </c>
       <c r="V23" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="W23" t="n">
         <v>1.19</v>
@@ -6272,7 +6272,7 @@
         <v>60</v>
       </c>
       <c r="AG23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH23" t="n">
         <v>25</v>
@@ -6305,7 +6305,7 @@
         <v>7.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS23" t="n">
         <v>4.6</v>
@@ -6314,13 +6314,13 @@
         <v>4.7</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AV23" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX23" t="n">
         <v>5.5</v>
@@ -6332,28 +6332,28 @@
         <v>4.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB23" t="n">
         <v>5.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD23" t="n">
         <v>5.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF23" t="n">
         <v>5.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI23" t="n">
         <v>3.2</v>
@@ -6362,31 +6362,31 @@
         <v>11</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN23" t="n">
         <v>10.5</v>
       </c>
       <c r="BO23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT23" t="n">
         <v>4.3</v>
@@ -6398,23 +6398,23 @@
         <v>11</v>
       </c>
       <c r="BW23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G24" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="I24" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="J24" t="n">
         <v>4.8</v>
@@ -6463,212 +6463,212 @@
         <v>5.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M24" t="n">
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="P24" t="n">
         <v>3.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="R24" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="S24" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="T24" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="U24" t="n">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="V24" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="W24" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y24" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Z24" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AA24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
         <v>28</v>
       </c>
-      <c r="AB24" t="n">
-        <v>50</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AJ24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR24" t="n">
         <v>32</v>
       </c>
-      <c r="AH24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ24" t="n">
+      <c r="BS24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ24" t="n">
         <v>10</v>
       </c>
-      <c r="BA24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>48</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>46</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>13.5</v>
-      </c>
       <c r="CA24" t="n">
-        <v>1.85</v>
+        <v>7.2</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
         <v>2.68</v>
       </c>
       <c r="I25" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
         <v>3.85</v>
@@ -6717,127 +6717,127 @@
         <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>2.68</v>
+        <v>5.7</v>
       </c>
       <c r="O25" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="Q25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T25" t="n">
         <v>1.48</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.38</v>
-      </c>
       <c r="U25" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="V25" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W25" t="n">
         <v>1.62</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>36</v>
       </c>
-      <c r="AF25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>40</v>
-      </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL25" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
         <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BA25" t="n">
         <v>1.01</v>
@@ -6846,25 +6846,25 @@
         <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE25" t="n">
         <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="BJ25" t="n">
         <v>12</v>
@@ -6876,53 +6876,53 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="BN25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BO25" t="n">
         <v>3.85</v>
       </c>
       <c r="BP25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="BT25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="BX25" t="n">
         <v>36</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="BZ25" t="n">
         <v>20</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="L26" t="n">
         <v>1.21</v>
@@ -6980,7 +6980,7 @@
         <v>6.4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P26" t="n">
         <v>2.84</v>
@@ -6992,10 +6992,10 @@
         <v>1.75</v>
       </c>
       <c r="S26" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T26" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U26" t="n">
         <v>2.64</v>
@@ -7040,7 +7040,7 @@
         <v>970</v>
       </c>
       <c r="AI26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ26" t="n">
         <v>85</v>
@@ -7061,59 +7061,59 @@
         <v>970</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.46</v>
+        <v>1.93</v>
       </c>
       <c r="AQ26" t="n">
         <v>11.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="AU26" t="n">
         <v>5.1</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY26" t="n">
         <v>5.9</v>
       </c>
-      <c r="AX26" t="n">
+      <c r="AZ26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG26" t="n">
         <v>5.2</v>
       </c>
-      <c r="AY26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BH26" t="n">
         <v>1000</v>
       </c>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G27" t="n">
         <v>1.65</v>
       </c>
       <c r="H27" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I27" t="n">
         <v>6.4</v>
@@ -7231,28 +7231,28 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
         <v>1.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S27" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V27" t="n">
         <v>1.18</v>
@@ -7261,112 +7261,112 @@
         <v>2.56</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ27" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK27" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN27" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.34</v>
+        <v>17</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.34</v>
+        <v>18.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.34</v>
+        <v>5.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.34</v>
+        <v>5.9</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.34</v>
+        <v>9.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.34</v>
+        <v>9</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.34</v>
+        <v>17</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.34</v>
+        <v>5.7</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.34</v>
+        <v>8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.34</v>
+        <v>14.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.34</v>
+        <v>5.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.25</v>
+        <v>12.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.25</v>
+        <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>20</v>
+        <v>5.1</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.34</v>
+        <v>5.7</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.16</v>
+        <v>6.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.34</v>
+        <v>5.7</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K28" t="n">
         <v>950</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G30" t="n">
         <v>1.93</v>
@@ -7978,13 +7978,13 @@
         <v>5.2</v>
       </c>
       <c r="I30" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J30" t="n">
         <v>3.35</v>
       </c>
       <c r="K30" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L30" t="n">
         <v>1.45</v>
@@ -8014,7 +8014,7 @@
         <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V30" t="n">
         <v>1.21</v>
@@ -8035,7 +8035,7 @@
         <v>200</v>
       </c>
       <c r="AB30" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC30" t="n">
         <v>8</v>
@@ -8074,7 +8074,7 @@
         <v>30</v>
       </c>
       <c r="AO30" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP30" t="n">
         <v>8.4</v>
@@ -8086,7 +8086,7 @@
         <v>27</v>
       </c>
       <c r="AS30" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT30" t="n">
         <v>5.7</v>
@@ -8098,7 +8098,7 @@
         <v>19.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX30" t="n">
         <v>8.6</v>
@@ -8107,10 +8107,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BA30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB30" t="n">
         <v>16.5</v>
@@ -8122,13 +8122,13 @@
         <v>38</v>
       </c>
       <c r="BE30" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF30" t="n">
         <v>16</v>
       </c>
       <c r="BG30" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH30" t="n">
         <v>2.8</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -8223,28 +8223,28 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G31" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H31" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I31" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
         <v>3.25</v>
@@ -8259,61 +8259,61 @@
         <v>2.02</v>
       </c>
       <c r="R31" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T31" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U31" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V31" t="n">
         <v>1.72</v>
       </c>
       <c r="W31" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG31" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK31" t="n">
         <v>55</v>
@@ -8322,88 +8322,88 @@
         <v>65</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.09</v>
+        <v>3.7</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.09</v>
+        <v>4.3</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.09</v>
+        <v>5.1</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.09</v>
+        <v>4.9</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.09</v>
+        <v>4.9</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.09</v>
+        <v>4.6</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.09</v>
+        <v>5.3</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.09</v>
+        <v>5.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.07</v>
+        <v>5.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.07</v>
+        <v>5.3</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.09</v>
+        <v>5.7</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.09</v>
+        <v>5.3</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.09</v>
+        <v>15.5</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="BJ31" t="n">
         <v>13.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>2.74</v>
+        <v>1.64</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>3.45</v>
+        <v>1.86</v>
       </c>
       <c r="BN31" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO31" t="n">
         <v>5</v>
@@ -8412,41 +8412,41 @@
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>3.2</v>
+        <v>1.79</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>3.25</v>
+        <v>1.81</v>
       </c>
       <c r="BT31" t="n">
         <v>6.6</v>
       </c>
       <c r="BU31" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BV31" t="n">
         <v>23</v>
       </c>
       <c r="BW31" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>3.2</v>
+        <v>1.79</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>3.15</v>
+        <v>1.78</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -8477,166 +8477,166 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="G32" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="H32" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="J32" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="K32" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L32" t="n">
         <v>1.46</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P32" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="Q32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.06</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.9</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="V32" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W32" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y32" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB32" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AC32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF32" t="n">
         <v>11</v>
       </c>
-      <c r="AD32" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AG32" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AH32" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ32" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AK32" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AL32" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.18</v>
+        <v>9.4</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.97</v>
+        <v>6.6</v>
       </c>
       <c r="AR32" t="n">
-        <v>25</v>
+        <v>9.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.18</v>
+        <v>5.1</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.79</v>
+        <v>6.4</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.82</v>
+        <v>7</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.02</v>
+        <v>7.8</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.14</v>
+        <v>10.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.91</v>
+        <v>5.8</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.91</v>
+        <v>5.8</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.04</v>
+        <v>8</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.18</v>
+        <v>6.4</v>
       </c>
       <c r="BB32" t="n">
-        <v>2.04</v>
+        <v>8</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.18</v>
+        <v>11.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>2.18</v>
+        <v>7.4</v>
       </c>
       <c r="BG32" t="n">
-        <v>2.18</v>
+        <v>11.5</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -872,7 +872,7 @@
         <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.43</v>
@@ -884,7 +884,7 @@
         <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
         <v>1.84</v>
@@ -902,7 +902,7 @@
         <v>1.83</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
         <v>1.27</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G3" t="n">
         <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
         <v>4.4</v>
@@ -1126,40 +1126,40 @@
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
         <v>1.9</v>
@@ -1168,7 +1168,7 @@
         <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z3" t="n">
         <v>38</v>
@@ -1210,13 +1210,13 @@
         <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN3" t="n">
         <v>15</v>
       </c>
       <c r="AO3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
         <v>12.5</v>
@@ -1237,7 +1237,7 @@
         <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
         <v>1.01</v>
@@ -1282,7 +1282,7 @@
         <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,7 +1294,7 @@
         <v>5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BP3" t="n">
         <v>14</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H4" t="n">
         <v>4.2</v>
@@ -1377,10 +1377,10 @@
         <v>4.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.22</v>
@@ -1401,16 +1401,16 @@
         <v>1.41</v>
       </c>
       <c r="R4" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="S4" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
         <v>1.46</v>
       </c>
       <c r="U4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
         <v>1.28</v>
@@ -1419,7 +1419,7 @@
         <v>2.2</v>
       </c>
       <c r="X4" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="Y4" t="n">
         <v>50</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AC4" t="n">
         <v>12</v>
@@ -1440,16 +1440,16 @@
         <v>19.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI4" t="n">
         <v>44</v>
@@ -1458,22 +1458,22 @@
         <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>30</v>
       </c>
       <c r="AM4" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AO4" t="n">
         <v>36</v>
       </c>
       <c r="AP4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AQ4" t="n">
         <v>19.5</v>
@@ -1485,37 +1485,37 @@
         <v>36</v>
       </c>
       <c r="AT4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC4" t="n">
         <v>13.5</v>
       </c>
-      <c r="BA4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>15</v>
-      </c>
       <c r="BD4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BE4" t="n">
         <v>25</v>
@@ -1524,7 +1524,7 @@
         <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BH4" t="n">
         <v>5.5</v>
@@ -1536,13 +1536,13 @@
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN4" t="n">
         <v>5.3</v>
@@ -1554,41 +1554,41 @@
         <v>11</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>8.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>10</v>
       </c>
       <c r="CA4" t="n">
         <v>6.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -1652,13 +1652,13 @@
         <v>1.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
         <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>2.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R7" t="n">
         <v>1.46</v>
@@ -2187,7 +2187,7 @@
         <v>19.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AA7" t="n">
         <v>65</v>
@@ -2223,7 +2223,7 @@
         <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM7" t="n">
         <v>75</v>
@@ -2235,16 +2235,16 @@
         <v>38</v>
       </c>
       <c r="AP7" t="n">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>19</v>
+        <v>4.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT7" t="n">
         <v>8.800000000000001</v>
@@ -2256,7 +2256,7 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX7" t="n">
         <v>11</v>
@@ -2268,25 +2268,25 @@
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>19.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>15.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -2387,10 +2387,10 @@
         <v>2.18</v>
       </c>
       <c r="H8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J8" t="n">
         <v>3.8</v>
@@ -2399,13 +2399,13 @@
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.24</v>
@@ -2414,7 +2414,7 @@
         <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R8" t="n">
         <v>1.51</v>
@@ -2426,7 +2426,7 @@
         <v>1.63</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
         <v>1.37</v>
@@ -2471,7 +2471,7 @@
         <v>48</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK8" t="n">
         <v>24</v>
@@ -2498,7 +2498,7 @@
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>10.5</v>
@@ -2510,7 +2510,7 @@
         <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
         <v>13.5</v>
@@ -2531,7 +2531,7 @@
         <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE8" t="n">
         <v>4.9</v>
@@ -2543,58 +2543,58 @@
         <v>21</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.98</v>
+        <v>3.6</v>
       </c>
       <c r="BJ8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
         <v>12.5</v>
       </c>
-      <c r="BK8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.98</v>
-      </c>
       <c r="BN8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT8" t="n">
         <v>7</v>
       </c>
-      <c r="BO8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BR8" t="n">
+      <c r="BU8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX8" t="n">
         <v>34</v>
       </c>
-      <c r="BS8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>46</v>
-      </c>
       <c r="BY8" t="n">
-        <v>1.9</v>
+        <v>10</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -3427,16 +3427,16 @@
         <v>1.02</v>
       </c>
       <c r="P12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q12" t="n">
         <v>1.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -4437,16 +4437,16 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.08</v>
+        <v>1.93</v>
       </c>
       <c r="O16" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P16" t="n">
         <v>1.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="R16" t="n">
         <v>1.08</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
         <v>5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
         <v>1.01</v>
@@ -4697,13 +4697,13 @@
         <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
         <v>2.46</v>
@@ -4712,7 +4712,7 @@
         <v>1.54</v>
       </c>
       <c r="U17" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V17" t="n">
         <v>1.4</v>
@@ -4772,7 +4772,7 @@
         <v>13.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP17" t="n">
         <v>1.03</v>
@@ -4829,58 +4829,58 @@
         <v>16.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -4924,22 +4924,22 @@
         <v>1.66</v>
       </c>
       <c r="G18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H18" t="n">
         <v>5.1</v>
       </c>
       <c r="I18" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J18" t="n">
         <v>4.2</v>
       </c>
       <c r="K18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
         <v>1.03</v>
@@ -4957,34 +4957,34 @@
         <v>1.59</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T18" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W18" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X18" t="n">
         <v>32</v>
       </c>
       <c r="Y18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z18" t="n">
         <v>65</v>
       </c>
       <c r="AA18" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB18" t="n">
         <v>12</v>
@@ -5038,7 +5038,7 @@
         <v>32</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT18" t="n">
         <v>9.6</v>
@@ -5050,7 +5050,7 @@
         <v>18</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -5062,7 +5062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB18" t="n">
         <v>14</v>
@@ -5074,67 +5074,67 @@
         <v>19</v>
       </c>
       <c r="BE18" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF18" t="n">
         <v>6.2</v>
       </c>
       <c r="BG18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BV18" t="n">
         <v>42</v>
       </c>
-      <c r="BH18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>50</v>
-      </c>
       <c r="BW18" t="n">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.35</v>
+        <v>8.4</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -5175,220 +5175,220 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H19" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="I19" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
         <v>3.55</v>
       </c>
       <c r="K19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X19" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO19" t="n">
         <v>4.7</v>
       </c>
-      <c r="L19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.29</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.29</v>
+        <v>10</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.29</v>
+        <v>4.6</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.29</v>
+        <v>8.4</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.29</v>
+        <v>10</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I20" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="J20" t="n">
         <v>5.1</v>
       </c>
       <c r="K20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
         <v>1.33</v>
@@ -5453,16 +5453,16 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
         <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R20" t="n">
         <v>1.45</v>
@@ -5477,10 +5477,10 @@
         <v>1.73</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X20" t="n">
         <v>23</v>
@@ -5489,22 +5489,22 @@
         <v>36</v>
       </c>
       <c r="Z20" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA20" t="n">
-        <v>610</v>
+        <v>560</v>
       </c>
       <c r="AB20" t="n">
         <v>8.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE20" t="n">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AF20" t="n">
         <v>8</v>
@@ -5513,10 +5513,10 @@
         <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AI20" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AJ20" t="n">
         <v>12</v>
@@ -5525,91 +5525,91 @@
         <v>15.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM20" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AO20" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="AP20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BB20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC20" t="n">
         <v>11.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF20" t="n">
         <v>4.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="BJ20" t="n">
         <v>13</v>
       </c>
       <c r="BK20" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN20" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BO20" t="n">
         <v>3</v>
@@ -5624,25 +5624,25 @@
         <v>26</v>
       </c>
       <c r="BS20" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT20" t="n">
         <v>14.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -5683,154 +5683,154 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U21" t="n">
         <v>2.28</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
         <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
         <v>1.03</v>
@@ -5839,64 +5839,64 @@
         <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.02</v>
+        <v>3.25</v>
       </c>
       <c r="BJ21" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="BK21" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN21" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP21" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BQ21" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="BR21" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>3.45</v>
+        <v>8</v>
       </c>
       <c r="BT21" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV21" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BW21" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="BX21" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G22" t="n">
         <v>2.12</v>
@@ -5955,7 +5955,7 @@
         <v>3.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
@@ -5964,13 +5964,13 @@
         <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R22" t="n">
         <v>1.31</v>
@@ -5979,10 +5979,10 @@
         <v>3.55</v>
       </c>
       <c r="T22" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V22" t="n">
         <v>1.26</v>
@@ -6012,7 +6012,7 @@
         <v>18.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF22" t="n">
         <v>13</v>
@@ -6042,7 +6042,7 @@
         <v>16.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP22" t="n">
         <v>9.800000000000001</v>
@@ -6066,7 +6066,7 @@
         <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
         <v>10</v>
@@ -6099,58 +6099,58 @@
         <v>55</v>
       </c>
       <c r="BH22" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BI22" t="n">
         <v>2.64</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.34</v>
+        <v>5.4</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.34</v>
+        <v>10.5</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.34</v>
+        <v>4</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.34</v>
+        <v>6.4</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.34</v>
+        <v>8.4</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.34</v>
+        <v>4.6</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.34</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -6191,58 +6191,58 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="G23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I23" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K23" t="n">
         <v>4.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O23" t="n">
         <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
         <v>3.15</v>
       </c>
       <c r="T23" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
         <v>970</v>
@@ -6269,109 +6269,109 @@
         <v>22</v>
       </c>
       <c r="AF23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
         <v>44</v>
       </c>
       <c r="AJ23" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AK23" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL23" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM23" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN23" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AO23" t="n">
         <v>970</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY23" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BH23" t="n">
         <v>3.8</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ23" t="n">
         <v>11</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BO23" t="n">
         <v>5.1</v>
@@ -6386,25 +6386,25 @@
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BV23" t="n">
         <v>11</v>
       </c>
       <c r="BW23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
         <v>40</v>
       </c>
       <c r="AC24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD24" t="n">
         <v>14</v>
@@ -6550,73 +6550,73 @@
         <v>38</v>
       </c>
       <c r="AO24" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AP24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX24" t="n">
         <v>4</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS24" t="n">
+      <c r="AY24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA24" t="n">
         <v>16</v>
       </c>
-      <c r="AT24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX24" t="n">
+      <c r="BB24" t="n">
         <v>4.1</v>
       </c>
-      <c r="AY24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BC24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BD24" t="n">
         <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG24" t="n">
         <v>3.9</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>4.5</v>
       </c>
       <c r="BH24" t="n">
         <v>5.5</v>
       </c>
       <c r="BI24" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BJ24" t="n">
         <v>9</v>
       </c>
       <c r="BK24" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
@@ -6628,7 +6628,7 @@
         <v>9.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="BP24" t="n">
         <v>34</v>
@@ -6646,13 +6646,13 @@
         <v>5.1</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BV24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BW24" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BX24" t="n">
         <v>17.5</v>
@@ -6664,11 +6664,11 @@
         <v>10</v>
       </c>
       <c r="CA24" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -6717,10 +6717,10 @@
         <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
         <v>5.7</v>
@@ -6738,13 +6738,13 @@
         <v>1.65</v>
       </c>
       <c r="S25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T25" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U25" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V25" t="n">
         <v>1.48</v>
@@ -6822,7 +6822,7 @@
         <v>12.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV25" t="n">
         <v>11.5</v>
@@ -6834,7 +6834,7 @@
         <v>15</v>
       </c>
       <c r="AY25" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
         <v>10.5</v>
@@ -6843,7 +6843,7 @@
         <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
         <v>16</v>
@@ -6858,71 +6858,71 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG25" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BH25" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.02</v>
+        <v>3.6</v>
       </c>
       <c r="BJ25" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.99</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN25" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BP25" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.86</v>
+        <v>6.2</v>
       </c>
       <c r="BR25" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.91</v>
+        <v>7</v>
       </c>
       <c r="BT25" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV25" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="BX25" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.92</v>
+        <v>7.2</v>
       </c>
       <c r="BZ25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.84</v>
+        <v>10.5</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G26" t="n">
         <v>4.7</v>
@@ -6962,13 +6962,13 @@
         <v>1.73</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="J26" t="n">
         <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L26" t="n">
         <v>1.21</v>
@@ -6977,37 +6977,37 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="O26" t="n">
         <v>1.14</v>
       </c>
       <c r="P26" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R26" t="n">
         <v>1.75</v>
       </c>
       <c r="S26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V26" t="n">
         <v>2.08</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="V26" t="n">
-        <v>2.1</v>
       </c>
       <c r="W26" t="n">
         <v>1.27</v>
       </c>
       <c r="X26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y26" t="n">
         <v>970</v>
@@ -7019,7 +7019,7 @@
         <v>22</v>
       </c>
       <c r="AB26" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AC26" t="n">
         <v>970</v>
@@ -7031,7 +7031,7 @@
         <v>970</v>
       </c>
       <c r="AF26" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AG26" t="n">
         <v>19.5</v>
@@ -7040,16 +7040,16 @@
         <v>970</v>
       </c>
       <c r="AI26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AK26" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AL26" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM26" t="n">
         <v>60</v>
@@ -7058,58 +7058,58 @@
         <v>28</v>
       </c>
       <c r="AO26" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.93</v>
+        <v>6.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.74</v>
+        <v>5.9</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.82</v>
+        <v>6.2</v>
       </c>
       <c r="AU26" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AV26" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="AW26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY26" t="n">
         <v>5.7</v>
       </c>
-      <c r="AX26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AZ26" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB26" t="n">
-        <v>3</v>
+        <v>7.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.92</v>
+        <v>27</v>
       </c>
       <c r="BD26" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.96</v>
+        <v>7.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG26" t="n">
         <v>5.2</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G27" t="n">
         <v>1.65</v>
@@ -7219,13 +7219,13 @@
         <v>6.4</v>
       </c>
       <c r="J27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
         <v>5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
@@ -7294,22 +7294,22 @@
         <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK27" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AM27" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AN27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO27" t="n">
         <v>75</v>
@@ -7321,22 +7321,22 @@
         <v>18.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.4</v>
+        <v>3.8</v>
       </c>
       <c r="AU27" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV27" t="n">
         <v>17</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX27" t="n">
         <v>8.800000000000001</v>
@@ -7348,7 +7348,7 @@
         <v>14.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BB27" t="n">
         <v>12.5</v>
@@ -7357,80 +7357,80 @@
         <v>12</v>
       </c>
       <c r="BD27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE27" t="n">
         <v>5.1</v>
       </c>
-      <c r="BE27" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>15</v>
+      </c>
+      <c r="CA27" t="n">
         <v>6.2</v>
       </c>
-      <c r="BG27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ27" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BR27" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS27" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BT27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BU27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BV27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BX27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BZ27" t="n">
-        <v>20</v>
-      </c>
-      <c r="CA27" t="n">
-        <v>1.9</v>
-      </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -7461,112 +7461,112 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="H28" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="J28" t="n">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="K28" t="n">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M28" t="n">
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="O28" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="P28" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="R28" t="n">
-        <v>1.08</v>
+        <v>2.48</v>
       </c>
       <c r="S28" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="AP28" t="n">
         <v>1.03</v>
@@ -7617,10 +7617,10 @@
         <v>1.03</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>1.84</v>
       </c>
       <c r="G30" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H30" t="n">
         <v>5.2</v>
@@ -7996,7 +7996,7 @@
         <v>2.76</v>
       </c>
       <c r="O30" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P30" t="n">
         <v>1.59</v>
@@ -8020,13 +8020,13 @@
         <v>1.21</v>
       </c>
       <c r="W30" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X30" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z30" t="n">
         <v>55</v>
@@ -8038,7 +8038,7 @@
         <v>6.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
         <v>30</v>
@@ -8071,7 +8071,7 @@
         <v>260</v>
       </c>
       <c r="AN30" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="n">
         <v>200</v>
@@ -8086,7 +8086,7 @@
         <v>27</v>
       </c>
       <c r="AS30" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT30" t="n">
         <v>5.7</v>
@@ -8098,7 +8098,7 @@
         <v>19.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX30" t="n">
         <v>8.6</v>
@@ -8107,10 +8107,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BA30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB30" t="n">
         <v>16.5</v>
@@ -8122,31 +8122,31 @@
         <v>38</v>
       </c>
       <c r="BE30" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF30" t="n">
         <v>16</v>
       </c>
       <c r="BG30" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH30" t="n">
         <v>2.8</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ30" t="n">
         <v>12</v>
       </c>
       <c r="BK30" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BN30" t="n">
         <v>4.3</v>
@@ -8155,7 +8155,7 @@
         <v>3.45</v>
       </c>
       <c r="BP30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ30" t="n">
         <v>8</v>
@@ -8170,19 +8170,19 @@
         <v>8.6</v>
       </c>
       <c r="BU30" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -8226,10 +8226,10 @@
         <v>3.25</v>
       </c>
       <c r="G31" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H31" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I31" t="n">
         <v>2.4</v>
@@ -8238,13 +8238,13 @@
         <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M31" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
         <v>3.25</v>
@@ -8259,7 +8259,7 @@
         <v>2.02</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
         <v>3.65</v>
@@ -8271,10 +8271,10 @@
         <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W31" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X31" t="n">
         <v>15</v>
@@ -8286,22 +8286,22 @@
         <v>16.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB31" t="n">
         <v>14</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG31" t="n">
         <v>19.5</v>
@@ -8310,16 +8310,16 @@
         <v>22</v>
       </c>
       <c r="AI31" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ31" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK31" t="n">
         <v>55</v>
       </c>
       <c r="AL31" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM31" t="n">
         <v>130</v>
@@ -8331,122 +8331,122 @@
         <v>24</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AU31" t="n">
         <v>6.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AY31" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AZ31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO31" t="n">
         <v>4.6</v>
       </c>
-      <c r="BA31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC31" t="n">
+      <c r="BP31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT31" t="n">
         <v>5.2</v>
       </c>
-      <c r="BD31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BJ31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BN31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BO31" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ31" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BR31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS31" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BT31" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BU31" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BV31" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.73</v>
+        <v>6.4</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.79</v>
+        <v>7.8</v>
       </c>
       <c r="BZ31" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.78</v>
+        <v>7.6</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -8477,37 +8477,37 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="G32" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I32" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J32" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K32" t="n">
         <v>3.7</v>
       </c>
       <c r="L32" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M32" t="n">
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O32" t="n">
         <v>1.44</v>
       </c>
       <c r="P32" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q32" t="n">
         <v>2.3</v>
@@ -8525,22 +8525,22 @@
         <v>1.83</v>
       </c>
       <c r="V32" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W32" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X32" t="n">
         <v>11</v>
       </c>
       <c r="Y32" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z32" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AA32" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB32" t="n">
         <v>7.2</v>
@@ -8552,7 +8552,7 @@
         <v>21</v>
       </c>
       <c r="AE32" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF32" t="n">
         <v>11</v>
@@ -8582,7 +8582,7 @@
         <v>18.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP32" t="n">
         <v>9.4</v>
@@ -8591,10 +8591,10 @@
         <v>6.6</v>
       </c>
       <c r="AR32" t="n">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT32" t="n">
         <v>6.4</v>
@@ -8603,104 +8603,104 @@
         <v>7</v>
       </c>
       <c r="AV32" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="AW32" t="n">
         <v>10.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AY32" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AZ32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC32" t="n">
         <v>8</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BD32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>22</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>24</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU32" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB32" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU32" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BZ32" t="n">
         <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB32"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>1.98</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
         <v>4.1</v>
@@ -872,7 +872,7 @@
         <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.43</v>
@@ -884,13 +884,13 @@
         <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
         <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
@@ -902,13 +902,13 @@
         <v>1.83</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
         <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X2" t="n">
         <v>15</v>
@@ -938,7 +938,7 @@
         <v>14</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>22</v>
@@ -971,10 +971,10 @@
         <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
@@ -986,7 +986,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX2" t="n">
         <v>9.6</v>
@@ -998,7 +998,7 @@
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
         <v>16.5</v>
@@ -1007,19 +1007,19 @@
         <v>16</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF2" t="n">
         <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI2" t="n">
         <v>2.66</v>
@@ -1028,16 +1028,16 @@
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO2" t="n">
         <v>3.75</v>
@@ -1046,10 +1046,10 @@
         <v>15.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS2" t="n">
         <v>8</v>
@@ -1058,29 +1058,29 @@
         <v>7.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV2" t="n">
         <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
         <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -1123,37 +1123,37 @@
         <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
         <v>2.4</v>
@@ -1171,22 +1171,22 @@
         <v>20</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="n">
         <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
         <v>15.5</v>
@@ -1198,28 +1198,28 @@
         <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP3" t="n">
         <v>15</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>12</v>
@@ -1231,19 +1231,19 @@
         <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU3" t="n">
         <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
         <v>7.8</v>
@@ -1267,22 +1267,22 @@
         <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,7 +1294,7 @@
         <v>5</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BP3" t="n">
         <v>14</v>
@@ -1306,13 +1306,13 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
         <v>7.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1327,14 +1327,14 @@
         <v>9.6</v>
       </c>
       <c r="BZ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H4" t="n">
         <v>4.2</v>
@@ -1377,10 +1377,10 @@
         <v>4.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>1.22</v>
@@ -1395,31 +1395,31 @@
         <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
         <v>1.41</v>
       </c>
       <c r="R4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V4" t="n">
         <v>1.28</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X4" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="Y4" t="n">
         <v>50</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AC4" t="n">
         <v>12</v>
@@ -1446,25 +1446,25 @@
         <v>17.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="n">
         <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL4" t="n">
         <v>30</v>
       </c>
       <c r="AM4" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
         <v>5.9</v>
@@ -1473,7 +1473,7 @@
         <v>36</v>
       </c>
       <c r="AP4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AQ4" t="n">
         <v>19.5</v>
@@ -1485,16 +1485,16 @@
         <v>36</v>
       </c>
       <c r="AT4" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
         <v>14.5</v>
@@ -1503,7 +1503,7 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
         <v>25</v>
@@ -1518,19 +1518,19 @@
         <v>16.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BF4" t="n">
         <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BH4" t="n">
         <v>5.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.6</v>
@@ -1548,7 +1548,7 @@
         <v>5.3</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP4" t="n">
         <v>11</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -1652,13 +1652,13 @@
         <v>1.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
         <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1903,16 +1903,16 @@
         <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="R6" t="n">
         <v>1.08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.56</v>
+        <v>2.46</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1924,7 +1924,7 @@
         <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
         <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AK7" t="n">
         <v>26</v>
@@ -2289,58 +2289,58 @@
         <v>5.1</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
         <v>3.8</v>
@@ -2399,7 +2399,7 @@
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -2426,7 +2426,7 @@
         <v>1.63</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
         <v>1.37</v>
@@ -2435,7 +2435,7 @@
         <v>1.84</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
         <v>19.5</v>
@@ -2450,13 +2450,13 @@
         <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>17.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF8" t="n">
         <v>18</v>
@@ -2471,7 +2471,7 @@
         <v>48</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
         <v>24</v>
@@ -2495,10 +2495,10 @@
         <v>14.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT8" t="n">
         <v>10.5</v>
@@ -2510,7 +2510,7 @@
         <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX8" t="n">
         <v>13.5</v>
@@ -2522,25 +2522,25 @@
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="BC8" t="n">
         <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF8" t="n">
         <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BH8" t="n">
         <v>4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2937,7 +2937,7 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
         <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q11" t="n">
         <v>1.01</v>
@@ -3182,7 +3182,7 @@
         <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3191,11 +3191,11 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.02</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
       <c r="X11" t="n">
         <v>1000</v>
       </c>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3932,19 +3932,19 @@
         <v>1.09</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P14" t="n">
         <v>1.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R14" t="n">
         <v>1.08</v>
       </c>
       <c r="S14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3953,7 +3953,7 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G17" t="n">
         <v>2.38</v>
@@ -4682,7 +4682,7 @@
         <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L17" t="n">
         <v>1.26</v>
@@ -4697,10 +4697,10 @@
         <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R17" t="n">
         <v>1.55</v>
@@ -4802,7 +4802,7 @@
         <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
         <v>1.03</v>
@@ -4838,7 +4838,7 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4850,25 +4850,25 @@
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>1.66</v>
       </c>
       <c r="G18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H18" t="n">
         <v>5.1</v>
@@ -4954,7 +4954,7 @@
         <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R18" t="n">
         <v>1.54</v>
@@ -4972,16 +4972,16 @@
         <v>1.21</v>
       </c>
       <c r="W18" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X18" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y18" t="n">
         <v>24</v>
       </c>
       <c r="Z18" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AA18" t="n">
         <v>130</v>
@@ -4996,7 +4996,7 @@
         <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AF18" t="n">
         <v>12.5</v>
@@ -5008,7 +5008,7 @@
         <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AJ18" t="n">
         <v>18</v>
@@ -5017,16 +5017,16 @@
         <v>17</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AM18" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="n">
         <v>7.8</v>
       </c>
       <c r="AO18" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AP18" t="n">
         <v>19.5</v>
@@ -5035,7 +5035,7 @@
         <v>20</v>
       </c>
       <c r="AR18" t="n">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="AS18" t="n">
         <v>8.800000000000001</v>
@@ -5071,7 +5071,7 @@
         <v>13.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
         <v>8.4</v>
@@ -5080,19 +5080,19 @@
         <v>6.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="BH18" t="n">
         <v>4.4</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BJ18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK18" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5104,13 +5104,13 @@
         <v>4.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="BP18" t="n">
         <v>11</v>
       </c>
       <c r="BQ18" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="BR18" t="n">
         <v>23</v>
@@ -5122,10 +5122,10 @@
         <v>9.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV18" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
         <v>8.199999999999999</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -5184,10 +5184,10 @@
         <v>2.56</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
         <v>3.9</v>
@@ -5205,7 +5205,7 @@
         <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
         <v>1.82</v>
@@ -5244,7 +5244,7 @@
         <v>15</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>14.5</v>
@@ -5259,7 +5259,7 @@
         <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
         <v>44</v>
@@ -5268,13 +5268,13 @@
         <v>50</v>
       </c>
       <c r="AK19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL19" t="n">
         <v>46</v>
       </c>
       <c r="AM19" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN19" t="n">
         <v>27</v>
@@ -5286,7 +5286,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR19" t="n">
         <v>14</v>
@@ -5295,10 +5295,10 @@
         <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV19" t="n">
         <v>9.4</v>
@@ -5313,7 +5313,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA19" t="n">
         <v>1.03</v>
@@ -5331,7 +5331,7 @@
         <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG19" t="n">
         <v>16</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -5441,13 +5441,13 @@
         <v>13.5</v>
       </c>
       <c r="J20" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K20" t="n">
         <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5465,7 +5465,7 @@
         <v>1.72</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
         <v>2.86</v>
@@ -5513,13 +5513,13 @@
         <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AI20" t="n">
         <v>180</v>
       </c>
       <c r="AJ20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK20" t="n">
         <v>15.5</v>
@@ -5540,13 +5540,13 @@
         <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT20" t="n">
         <v>6.8</v>
@@ -5555,10 +5555,10 @@
         <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX20" t="n">
         <v>7</v>
@@ -5567,10 +5567,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA20" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB20" t="n">
         <v>9</v>
@@ -5579,16 +5579,16 @@
         <v>11.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH20" t="n">
         <v>3.95</v>
@@ -5600,7 +5600,7 @@
         <v>13</v>
       </c>
       <c r="BK20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -5686,22 +5686,22 @@
         <v>2.38</v>
       </c>
       <c r="G21" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H21" t="n">
         <v>2.84</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J21" t="n">
         <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
@@ -5716,7 +5716,7 @@
         <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R21" t="n">
         <v>1.4</v>
@@ -5731,7 +5731,7 @@
         <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W21" t="n">
         <v>1.6</v>
@@ -5758,7 +5758,7 @@
         <v>14</v>
       </c>
       <c r="AE21" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="n">
         <v>18.5</v>
@@ -5770,19 +5770,19 @@
         <v>17</v>
       </c>
       <c r="AI21" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ21" t="n">
         <v>38</v>
       </c>
       <c r="AK21" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AL21" t="n">
         <v>38</v>
       </c>
       <c r="AM21" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN21" t="n">
         <v>19.5</v>
@@ -5827,7 +5827,7 @@
         <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
         <v>19</v>
@@ -5848,13 +5848,13 @@
         <v>3.8</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.4</v>
       </c>
       <c r="BK21" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
@@ -5866,7 +5866,7 @@
         <v>5.8</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP21" t="n">
         <v>19</v>
@@ -5884,7 +5884,7 @@
         <v>6.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV21" t="n">
         <v>23</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
         <v>4.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
         <v>3.9</v>
@@ -6120,7 +6120,7 @@
         <v>4.8</v>
       </c>
       <c r="BO22" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BP22" t="n">
         <v>15</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>6</v>
       </c>
       <c r="H23" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I23" t="n">
         <v>1.76</v>
@@ -6206,10 +6206,10 @@
         <v>3.95</v>
       </c>
       <c r="K23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
@@ -6221,25 +6221,25 @@
         <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R23" t="n">
         <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
         <v>1.8</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V23" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="W23" t="n">
         <v>1.2</v>
@@ -6251,13 +6251,13 @@
         <v>10.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AA23" t="n">
         <v>970</v>
       </c>
       <c r="AB23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC23" t="n">
         <v>970</v>
@@ -6299,79 +6299,79 @@
         <v>970</v>
       </c>
       <c r="AP23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY23" t="n">
         <v>4.9</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX23" t="n">
+      <c r="AZ23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE23" t="n">
         <v>5.8</v>
       </c>
-      <c r="AY23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BF23" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BH23" t="n">
         <v>3.8</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="BJ23" t="n">
         <v>11</v>
       </c>
       <c r="BK23" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO23" t="n">
         <v>5.1</v>
@@ -6380,13 +6380,13 @@
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT23" t="n">
         <v>4.4</v>
@@ -6398,7 +6398,7 @@
         <v>11</v>
       </c>
       <c r="BW23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
@@ -6410,11 +6410,11 @@
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
         <v>1.91</v>
       </c>
       <c r="S24" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="T24" t="n">
         <v>1.5</v>
@@ -6571,7 +6571,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AW24" t="n">
         <v>11</v>
@@ -6598,7 +6598,7 @@
         <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="BF24" t="n">
         <v>3.85</v>
@@ -6610,7 +6610,7 @@
         <v>5.5</v>
       </c>
       <c r="BI24" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BJ24" t="n">
         <v>9</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
         <v>2.68</v>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J25" t="n">
         <v>3.85</v>
@@ -6720,7 +6720,7 @@
         <v>1.22</v>
       </c>
       <c r="M25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N25" t="n">
         <v>5.7</v>
@@ -6750,7 +6750,7 @@
         <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X25" t="n">
         <v>34</v>
@@ -6918,11 +6918,11 @@
         <v>15</v>
       </c>
       <c r="CA25" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -6956,10 +6956,10 @@
         <v>3.9</v>
       </c>
       <c r="G26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H26" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I26" t="n">
         <v>1.91</v>
@@ -6983,7 +6983,7 @@
         <v>1.14</v>
       </c>
       <c r="P26" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="Q26" t="n">
         <v>1.43</v>
@@ -7004,7 +7004,7 @@
         <v>2.08</v>
       </c>
       <c r="W26" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X26" t="n">
         <v>34</v>
@@ -7031,7 +7031,7 @@
         <v>970</v>
       </c>
       <c r="AF26" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG26" t="n">
         <v>19.5</v>
@@ -7043,13 +7043,13 @@
         <v>25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK26" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AL26" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM26" t="n">
         <v>60</v>
@@ -7058,22 +7058,22 @@
         <v>28</v>
       </c>
       <c r="AO26" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AP26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT26" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>6.2</v>
       </c>
       <c r="AU26" t="n">
         <v>9</v>
@@ -7082,101 +7082,101 @@
         <v>8.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX26" t="n">
-        <v>25</v>
+        <v>4.2</v>
       </c>
       <c r="AY26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>5.7</v>
       </c>
-      <c r="AZ26" t="n">
+      <c r="BA26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>48</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>22</v>
+      </c>
+      <c r="BT26" t="n">
         <v>5.4</v>
       </c>
-      <c r="BA26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G27" t="n">
         <v>1.65</v>
@@ -7234,22 +7234,22 @@
         <v>4.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R27" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T27" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U27" t="n">
         <v>2.16</v>
@@ -7261,10 +7261,10 @@
         <v>2.56</v>
       </c>
       <c r="X27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z27" t="n">
         <v>60</v>
@@ -7273,16 +7273,16 @@
         <v>160</v>
       </c>
       <c r="AB27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD27" t="n">
         <v>26</v>
       </c>
       <c r="AE27" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF27" t="n">
         <v>13</v>
@@ -7294,7 +7294,7 @@
         <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ27" t="n">
         <v>19</v>
@@ -7321,13 +7321,13 @@
         <v>18.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU27" t="n">
         <v>8.199999999999999</v>
@@ -7336,7 +7336,7 @@
         <v>17</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX27" t="n">
         <v>8.800000000000001</v>
@@ -7348,7 +7348,7 @@
         <v>14.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BB27" t="n">
         <v>12.5</v>
@@ -7357,22 +7357,22 @@
         <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="BG27" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BH27" t="n">
         <v>4.4</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BJ27" t="n">
         <v>10</v>
@@ -7396,7 +7396,7 @@
         <v>10.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="BR27" t="n">
         <v>23</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -7464,22 +7464,22 @@
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="H28" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="I28" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J28" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
         <v>5.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="M28" t="n">
         <v>1.01</v>
@@ -7488,52 +7488,52 @@
         <v>1.01</v>
       </c>
       <c r="O28" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P28" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="R28" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="S28" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="T28" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="U28" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="V28" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W28" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X28" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Y28" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Z28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AC28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD28" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE28" t="n">
         <v>22</v>
@@ -7542,10 +7542,10 @@
         <v>60</v>
       </c>
       <c r="AG28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH28" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI28" t="n">
         <v>22</v>
@@ -7560,13 +7560,13 @@
         <v>28</v>
       </c>
       <c r="AM28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AN28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AP28" t="n">
         <v>1.03</v>
@@ -7617,81 +7617,81 @@
         <v>1.03</v>
       </c>
       <c r="BF28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>25</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>15</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BT28" t="n">
         <v>7.4</v>
       </c>
-      <c r="BG28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU28" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV28" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BX28" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ28" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7706,246 +7706,246 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="G29" t="n">
-        <v>2.36</v>
+        <v>1.92</v>
       </c>
       <c r="H29" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K29" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BI29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK29" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BN29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BR29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BT29" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU29" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BV29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BX29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BZ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7960,202 +7960,202 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.84</v>
+        <v>3.3</v>
       </c>
       <c r="G30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.92</v>
       </c>
-      <c r="H30" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I30" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.73</v>
-      </c>
       <c r="V30" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="W30" t="n">
-        <v>2.08</v>
+        <v>1.35</v>
       </c>
       <c r="X30" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK30" t="n">
         <v>55</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>38</v>
       </c>
       <c r="AL30" t="n">
         <v>70</v>
       </c>
       <c r="AM30" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AO30" t="n">
-        <v>200</v>
+        <v>24</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="AR30" t="n">
-        <v>27</v>
+        <v>4.8</v>
       </c>
       <c r="AS30" t="n">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW30" t="n">
         <v>5.7</v>
       </c>
-      <c r="AU30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>12</v>
-      </c>
       <c r="AX30" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.6</v>
+        <v>4.9</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="BA30" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>16.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="BD30" t="n">
-        <v>38</v>
+        <v>6.4</v>
       </c>
       <c r="BE30" t="n">
-        <v>12.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>16</v>
+        <v>6.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>12.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH30" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="BJ30" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN30" t="n">
         <v>7.2</v>
       </c>
-      <c r="BL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BO30" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="BP30" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ30" t="n">
         <v>8</v>
@@ -8164,42 +8164,42 @@
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BT30" t="n">
-        <v>8.6</v>
+        <v>5.2</v>
       </c>
       <c r="BU30" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8214,239 +8214,239 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="G31" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K31" t="n">
         <v>3.8</v>
       </c>
-      <c r="H31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="BJ31" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK31" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BL31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM31" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BN31" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BP31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ31" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BR31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS31" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BT31" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BV31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW31" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BX31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY31" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BZ31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CA31" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -8477,10 +8477,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G32" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="H32" t="n">
         <v>5.2</v>
@@ -8492,7 +8492,7 @@
         <v>3.45</v>
       </c>
       <c r="K32" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
         <v>1.5</v>
@@ -8501,148 +8501,148 @@
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="O32" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P32" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S32" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T32" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V32" t="n">
         <v>1.21</v>
       </c>
       <c r="W32" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y32" t="n">
         <v>15</v>
       </c>
       <c r="Z32" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA32" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AB32" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC32" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD32" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE32" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AF32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG32" t="n">
         <v>11</v>
       </c>
       <c r="AH32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI32" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL32" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AM32" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AN32" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AP32" t="n">
-        <v>9.4</v>
+        <v>5.2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR32" t="n">
         <v>32</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU32" t="n">
         <v>7</v>
       </c>
       <c r="AV32" t="n">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="AW32" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AX32" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="AY32" t="n">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC32" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BD32" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC32" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BE32" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF32" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG32" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH32" t="n">
         <v>2.98</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ32" t="n">
         <v>11</v>
@@ -8660,13 +8660,13 @@
         <v>4.3</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BP32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ32" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,261 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>21:15:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Macara</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H2" t="n">
         <v>4.1</v>
@@ -881,16 +881,16 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
@@ -899,19 +899,19 @@
         <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
         <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
         <v>17</v>
@@ -923,10 +923,10 @@
         <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
         <v>19.5</v>
@@ -935,31 +935,31 @@
         <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
         <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO2" t="n">
         <v>80</v>
@@ -968,55 +968,55 @@
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH2" t="n">
         <v>3.35</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G3" t="n">
         <v>2.1</v>
@@ -1123,10 +1123,10 @@
         <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.29</v>
@@ -1138,22 +1138,22 @@
         <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
         <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U3" t="n">
         <v>2.4</v>
@@ -1162,22 +1162,22 @@
         <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="n">
         <v>20</v>
       </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AA3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
         <v>11</v>
@@ -1189,16 +1189,16 @@
         <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG3" t="n">
         <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -1207,10 +1207,10 @@
         <v>24</v>
       </c>
       <c r="AL3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN3" t="n">
         <v>14.5</v>
@@ -1219,49 +1219,49 @@
         <v>50</v>
       </c>
       <c r="AP3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>15</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>12</v>
-      </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
         <v>9.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
         <v>36</v>
       </c>
       <c r="BB3" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BC3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BE3" t="n">
         <v>1.01</v>
@@ -1306,7 +1306,7 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT3" t="n">
         <v>7.6</v>
@@ -1318,7 +1318,7 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1330,11 +1330,11 @@
         <v>21</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
         <v>4.2</v>
@@ -1377,10 +1377,10 @@
         <v>4.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.22</v>
@@ -1395,22 +1395,22 @@
         <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q4" t="n">
         <v>1.41</v>
       </c>
       <c r="R4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
         <v>1.28</v>
@@ -1419,7 +1419,7 @@
         <v>2.24</v>
       </c>
       <c r="X4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Y4" t="n">
         <v>50</v>
@@ -1431,10 +1431,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AD4" t="n">
         <v>19.5</v>
@@ -1464,19 +1464,19 @@
         <v>30</v>
       </c>
       <c r="AM4" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP4" t="n">
         <v>28</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
         <v>24</v>
@@ -1488,7 +1488,7 @@
         <v>15.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV4" t="n">
         <v>16</v>
@@ -1503,7 +1503,7 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
         <v>25</v>
@@ -1521,7 +1521,7 @@
         <v>29</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG4" t="n">
         <v>21</v>
@@ -1536,13 +1536,13 @@
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN4" t="n">
         <v>5.3</v>
@@ -1557,7 +1557,7 @@
         <v>6.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS4" t="n">
         <v>8.199999999999999</v>
@@ -1572,7 +1572,7 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -1619,112 +1619,112 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9</v>
+        <v>3.75</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>1.09</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="P5" t="n">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.57</v>
+        <v>2.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.7</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP5" t="n">
         <v>1.03</v>
@@ -1781,16 +1781,16 @@
         <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,16 +1799,16 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1817,10 +1817,10 @@
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -1873,112 +1873,112 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>2.96</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5</v>
+        <v>2.68</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>2.6</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09</v>
+        <v>2.18</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="P6" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="R6" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="S6" t="n">
-        <v>2.46</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP6" t="n">
         <v>1.03</v>
@@ -2035,68 +2035,68 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -2187,25 +2187,25 @@
         <v>19.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB7" t="n">
         <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AE7" t="n">
         <v>46</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AG7" t="n">
         <v>13.5</v>
@@ -2217,76 +2217,76 @@
         <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AK7" t="n">
         <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AM7" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
         <v>38</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.6</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AT7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="AX7" t="n">
         <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.4</v>
+        <v>34</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="BH7" t="n">
         <v>3.9</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
         <v>1.28</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
         <v>4.7</v>
@@ -2411,10 +2411,10 @@
         <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
         <v>1.51</v>
@@ -2450,7 +2450,7 @@
         <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD8" t="n">
         <v>17.5</v>
@@ -2495,7 +2495,7 @@
         <v>14.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.9</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
         <v>5.3</v>
@@ -2519,13 +2519,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA8" t="n">
         <v>5.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.9</v>
+        <v>20</v>
       </c>
       <c r="BC8" t="n">
         <v>18</v>
@@ -2540,7 +2540,7 @@
         <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BH8" t="n">
         <v>4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -2635,112 +2635,112 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>2.34</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>1.09</v>
+        <v>2.22</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="P9" t="n">
-        <v>1.08</v>
+        <v>1.43</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="R9" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP9" t="n">
         <v>1.03</v>
@@ -2791,74 +2791,74 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -2889,64 +2889,64 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.55</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85</v>
+        <v>6.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M10" t="n">
         <v>1.09</v>
       </c>
-      <c r="K10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.09</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.11</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>2.78</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z10" t="n">
         <v>1000</v>
@@ -2955,43 +2955,43 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
@@ -3009,7 +3009,7 @@
         <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AU10" t="n">
         <v>1.03</v>
@@ -3045,7 +3045,7 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
@@ -3054,65 +3054,65 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
         <v>1.01</v>
       </c>
       <c r="R11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -3433,10 +3433,10 @@
         <v>1.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3445,7 +3445,7 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
         <v>1.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="R14" t="n">
         <v>1.08</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
         <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4452,7 +4452,7 @@
         <v>1.08</v>
       </c>
       <c r="S16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -4670,19 +4670,19 @@
         <v>2.14</v>
       </c>
       <c r="G17" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H17" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="I17" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="J17" t="n">
         <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.26</v>
@@ -4691,13 +4691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
         <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q17" t="n">
         <v>1.58</v>
@@ -4715,16 +4715,16 @@
         <v>2.46</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X17" t="n">
         <v>27</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="n">
         <v>30</v>
@@ -4733,43 +4733,43 @@
         <v>60</v>
       </c>
       <c r="AB17" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AE17" t="n">
         <v>38</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
         <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AI17" t="n">
         <v>42</v>
       </c>
       <c r="AJ17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK17" t="n">
         <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AM17" t="n">
         <v>70</v>
       </c>
       <c r="AN17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO17" t="n">
         <v>25</v>
@@ -4787,10 +4787,10 @@
         <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
         <v>1.03</v>
@@ -4814,7 +4814,7 @@
         <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BD17" t="n">
         <v>1.03</v>
@@ -4856,7 +4856,7 @@
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
@@ -4874,7 +4874,7 @@
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
         <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
         <v>5</v>
@@ -4960,7 +4960,7 @@
         <v>1.54</v>
       </c>
       <c r="S18" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="T18" t="n">
         <v>1.66</v>
@@ -4975,16 +4975,16 @@
         <v>2.36</v>
       </c>
       <c r="X18" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z18" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA18" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB18" t="n">
         <v>12</v>
@@ -4993,7 +4993,7 @@
         <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
         <v>65</v>
@@ -5002,13 +5002,13 @@
         <v>12.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH18" t="n">
         <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ18" t="n">
         <v>18</v>
@@ -5017,28 +5017,28 @@
         <v>17</v>
       </c>
       <c r="AL18" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AM18" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN18" t="n">
         <v>7.8</v>
       </c>
       <c r="AO18" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>19.5</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>20</v>
-      </c>
       <c r="AR18" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT18" t="n">
         <v>9.6</v>
@@ -5047,10 +5047,10 @@
         <v>9</v>
       </c>
       <c r="AV18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -5062,25 +5062,25 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC18" t="n">
         <v>13.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>42</v>
+        <v>7.6</v>
       </c>
       <c r="BH18" t="n">
         <v>4.4</v>
@@ -5092,7 +5092,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK18" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5104,13 +5104,13 @@
         <v>4.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BP18" t="n">
         <v>11</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR18" t="n">
         <v>23</v>
@@ -5122,7 +5122,7 @@
         <v>9.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -5184,10 +5184,10 @@
         <v>2.56</v>
       </c>
       <c r="I19" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
         <v>3.9</v>
@@ -5277,7 +5277,7 @@
         <v>90</v>
       </c>
       <c r="AN19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO19" t="n">
         <v>25</v>
@@ -5286,7 +5286,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR19" t="n">
         <v>14</v>
@@ -5295,22 +5295,22 @@
         <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AU19" t="n">
         <v>7.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW19" t="n">
         <v>21</v>
       </c>
       <c r="AX19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ19" t="n">
         <v>12.5</v>
@@ -5319,7 +5319,7 @@
         <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BC19" t="n">
         <v>1.03</v>
@@ -5331,10 +5331,10 @@
         <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BG19" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BH19" t="n">
         <v>3.65</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.31</v>
       </c>
       <c r="G20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H20" t="n">
         <v>11</v>
@@ -5441,10 +5441,10 @@
         <v>13.5</v>
       </c>
       <c r="J20" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L20" t="n">
         <v>1.29</v>
@@ -5468,7 +5468,7 @@
         <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T20" t="n">
         <v>2.18</v>
@@ -5480,97 +5480,97 @@
         <v>1.08</v>
       </c>
       <c r="W20" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y20" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z20" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AA20" t="n">
-        <v>560</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
         <v>8.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL20" t="n">
         <v>50</v>
       </c>
-      <c r="AE20" t="n">
-        <v>230</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK20" t="n">
+      <c r="AM20" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP20" t="n">
         <v>15.5</v>
       </c>
-      <c r="AL20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>360</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>16</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB20" t="n">
         <v>9</v>
@@ -5579,16 +5579,16 @@
         <v>11.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BH20" t="n">
         <v>3.95</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
         <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
         <v>1.32</v>
@@ -5716,7 +5716,7 @@
         <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R21" t="n">
         <v>1.4</v>
@@ -5737,58 +5737,58 @@
         <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA21" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD21" t="n">
         <v>14</v>
       </c>
       <c r="AE21" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF21" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH21" t="n">
         <v>17</v>
       </c>
       <c r="AI21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL21" t="n">
         <v>42</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>38</v>
-      </c>
       <c r="AM21" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN21" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AO21" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AP21" t="n">
         <v>13</v>
@@ -5797,13 +5797,13 @@
         <v>10.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT21" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU21" t="n">
         <v>6.6</v>
@@ -5815,10 +5815,10 @@
         <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
         <v>12</v>
@@ -5827,22 +5827,22 @@
         <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG21" t="n">
         <v>19</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>19.5</v>
       </c>
       <c r="BH21" t="n">
         <v>3.8</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
         <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="n">
         <v>3.4</v>
@@ -5967,7 +5967,7 @@
         <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
         <v>1.99</v>
@@ -5991,58 +5991,58 @@
         <v>1.89</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Z22" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA22" t="n">
         <v>120</v>
       </c>
       <c r="AB22" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AE22" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG22" t="n">
         <v>13</v>
       </c>
-      <c r="AG22" t="n">
-        <v>11</v>
-      </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI22" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL22" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
         <v>140</v>
       </c>
       <c r="AN22" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP22" t="n">
         <v>9.800000000000001</v>
@@ -6072,10 +6072,10 @@
         <v>10</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA22" t="n">
         <v>1.03</v>
@@ -6084,19 +6084,19 @@
         <v>20</v>
       </c>
       <c r="BC22" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD22" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
         <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG22" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BH22" t="n">
         <v>3.4</v>
@@ -6120,7 +6120,7 @@
         <v>4.8</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BP22" t="n">
         <v>15</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -6215,28 +6215,28 @@
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P23" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U23" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>2.3</v>
@@ -6266,7 +6266,7 @@
         <v>12.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="n">
         <v>55</v>
@@ -6299,16 +6299,16 @@
         <v>970</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ23" t="n">
         <v>8</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT23" t="n">
         <v>4.7</v>
@@ -6323,34 +6323,34 @@
         <v>4.8</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>4.9</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BA23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE23" t="n">
         <v>5.9</v>
       </c>
-      <c r="BC23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BF23" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.75</v>
+        <v>7.8</v>
       </c>
       <c r="BH23" t="n">
         <v>3.8</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -6454,10 +6454,10 @@
         <v>1.59</v>
       </c>
       <c r="I24" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="J24" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="K24" t="n">
         <v>5.5</v>
@@ -6478,7 +6478,7 @@
         <v>3.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="R24" t="n">
         <v>1.91</v>
@@ -6493,7 +6493,7 @@
         <v>2.68</v>
       </c>
       <c r="V24" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="W24" t="n">
         <v>1.19</v>
@@ -6514,7 +6514,7 @@
         <v>40</v>
       </c>
       <c r="AC24" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD24" t="n">
         <v>14</v>
@@ -6553,7 +6553,7 @@
         <v>6</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AQ24" t="n">
         <v>12.5</v>
@@ -6565,7 +6565,7 @@
         <v>13</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AU24" t="n">
         <v>9.800000000000001</v>
@@ -6595,10 +6595,10 @@
         <v>4</v>
       </c>
       <c r="BD24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE24" t="n">
         <v>4</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>36</v>
       </c>
       <c r="BF24" t="n">
         <v>3.85</v>
@@ -6616,31 +6616,31 @@
         <v>9</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN24" t="n">
         <v>9.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP24" t="n">
         <v>34</v>
       </c>
       <c r="BQ24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR24" t="n">
         <v>32</v>
       </c>
       <c r="BS24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT24" t="n">
         <v>5.1</v>
@@ -6652,23 +6652,23 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BW24" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX24" t="n">
         <v>17.5</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA24" t="n">
         <v>5.8</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -6699,133 +6699,133 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H25" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="I25" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M25" t="n">
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
         <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
         <v>1.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S25" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T25" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U25" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V25" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE25" t="n">
         <v>29</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>28</v>
       </c>
       <c r="AF25" t="n">
         <v>25</v>
       </c>
       <c r="AG25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ25" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AK25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL25" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AM25" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN25" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AO25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AS25" t="n">
         <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW25" t="n">
         <v>19</v>
@@ -6834,28 +6834,28 @@
         <v>15</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
         <v>10.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
         <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
         <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG25" t="n">
         <v>11</v>
@@ -6864,65 +6864,65 @@
         <v>4.8</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ25" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU25" t="n">
         <v>4.7</v>
       </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BV25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BW25" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX25" t="n">
         <v>26</v>
       </c>
       <c r="BY25" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BZ25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CA25" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G26" t="n">
         <v>4.6</v>
@@ -6962,13 +6962,13 @@
         <v>1.74</v>
       </c>
       <c r="I26" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="K26" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="L26" t="n">
         <v>1.21</v>
@@ -6977,7 +6977,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.14</v>
@@ -6989,7 +6989,7 @@
         <v>1.43</v>
       </c>
       <c r="R26" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S26" t="n">
         <v>2.06</v>
@@ -6998,16 +6998,16 @@
         <v>1.49</v>
       </c>
       <c r="U26" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X26" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="Y26" t="n">
         <v>970</v>
@@ -7016,103 +7016,103 @@
         <v>970</v>
       </c>
       <c r="AA26" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AB26" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AC26" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD26" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>970</v>
       </c>
       <c r="AF26" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG26" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AH26" t="n">
         <v>970</v>
       </c>
       <c r="AI26" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AJ26" t="n">
         <v>90</v>
       </c>
       <c r="AK26" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AL26" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM26" t="n">
         <v>60</v>
       </c>
       <c r="AN26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO26" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AP26" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ26" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU26" t="n">
-        <v>9</v>
+        <v>3.95</v>
       </c>
       <c r="AV26" t="n">
         <v>8.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AX26" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AY26" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BA26" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>2.08</v>
+        <v>5.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH26" t="n">
         <v>5.2</v>
@@ -7136,7 +7136,7 @@
         <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
@@ -7172,11 +7172,11 @@
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
         <v>1.63</v>
       </c>
       <c r="R27" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S27" t="n">
         <v>2.54</v>
@@ -7252,7 +7252,7 @@
         <v>1.71</v>
       </c>
       <c r="U27" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V27" t="n">
         <v>1.18</v>
@@ -7264,7 +7264,7 @@
         <v>25</v>
       </c>
       <c r="Y27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z27" t="n">
         <v>60</v>
@@ -7279,10 +7279,10 @@
         <v>12</v>
       </c>
       <c r="AD27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE27" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="n">
         <v>13</v>
@@ -7291,7 +7291,7 @@
         <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
         <v>70</v>
@@ -7312,43 +7312,43 @@
         <v>7.6</v>
       </c>
       <c r="AO27" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ27" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV27" t="n">
         <v>17</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AX27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY27" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>8</v>
       </c>
       <c r="AZ27" t="n">
         <v>14.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BB27" t="n">
         <v>12.5</v>
@@ -7357,16 +7357,16 @@
         <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF27" t="n">
         <v>5.7</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH27" t="n">
         <v>4.4</v>
@@ -7414,10 +7414,10 @@
         <v>46</v>
       </c>
       <c r="BW27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX27" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY27" t="n">
         <v>8.6</v>
@@ -7426,11 +7426,11 @@
         <v>15</v>
       </c>
       <c r="CA27" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G28" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="H28" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="I28" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="K28" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="L28" t="n">
         <v>1.12</v>
@@ -7491,16 +7491,16 @@
         <v>1.05</v>
       </c>
       <c r="P28" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="Q28" t="n">
         <v>1.17</v>
       </c>
       <c r="R28" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="S28" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T28" t="n">
         <v>1.24</v>
@@ -7509,64 +7509,64 @@
         <v>4.1</v>
       </c>
       <c r="V28" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="X28" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="Y28" t="n">
         <v>46</v>
       </c>
       <c r="Z28" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA28" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB28" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AC28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD28" t="n">
         <v>18.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF28" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AG28" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AH28" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ28" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AL28" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AM28" t="n">
         <v>32</v>
       </c>
       <c r="AN28" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AP28" t="n">
         <v>1.03</v>
@@ -7617,19 +7617,19 @@
         <v>1.03</v>
       </c>
       <c r="BF28" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG28" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="BH28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI28" t="n">
         <v>6.4</v>
       </c>
       <c r="BJ28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK28" t="n">
         <v>6.2</v>
@@ -7641,50 +7641,50 @@
         <v>25</v>
       </c>
       <c r="BN28" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BO28" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BP28" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BQ28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BR28" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BS28" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU28" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV28" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BW28" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BX28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BY28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ28" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="CA28" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7721,7 @@
         <v>1.92</v>
       </c>
       <c r="H29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I29" t="n">
         <v>5.7</v>
@@ -7877,68 +7877,68 @@
         <v>13</v>
       </c>
       <c r="BH29" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ29" t="n">
         <v>12</v>
       </c>
       <c r="BK29" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN29" t="n">
         <v>4.3</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP29" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ29" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT29" t="n">
         <v>8.6</v>
       </c>
       <c r="BU29" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ29" t="n">
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -7972,28 +7972,28 @@
         <v>3.3</v>
       </c>
       <c r="G30" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H30" t="n">
         <v>2.18</v>
       </c>
       <c r="I30" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>3.45</v>
       </c>
       <c r="K30" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L30" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M30" t="n">
         <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O30" t="n">
         <v>1.38</v>
@@ -8017,10 +8017,10 @@
         <v>1.92</v>
       </c>
       <c r="V30" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W30" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X30" t="n">
         <v>14</v>
@@ -8029,10 +8029,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z30" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA30" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB30" t="n">
         <v>13.5</v>
@@ -8044,10 +8044,10 @@
         <v>13</v>
       </c>
       <c r="AE30" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG30" t="n">
         <v>970</v>
@@ -8056,79 +8056,79 @@
         <v>22</v>
       </c>
       <c r="AI30" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ30" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL30" t="n">
         <v>75</v>
       </c>
-      <c r="AK30" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>70</v>
-      </c>
       <c r="AM30" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN30" t="n">
         <v>65</v>
       </c>
       <c r="AO30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT30" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="AU30" t="n">
         <v>6.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB30" t="n">
         <v>5.6</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="BC30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG30" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>5.4</v>
       </c>
       <c r="BH30" t="n">
         <v>3.3</v>
@@ -8146,7 +8146,7 @@
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN30" t="n">
         <v>7.2</v>
@@ -8158,7 +8158,7 @@
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
@@ -8170,7 +8170,7 @@
         <v>5.2</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
@@ -8182,7 +8182,7 @@
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
         <v>2.1</v>
       </c>
       <c r="G31" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H31" t="n">
         <v>3.5</v>
@@ -8238,7 +8238,7 @@
         <v>3.3</v>
       </c>
       <c r="K31" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -8480,73 +8480,73 @@
         <v>1.82</v>
       </c>
       <c r="G32" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H32" t="n">
         <v>5.2</v>
       </c>
       <c r="I32" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J32" t="n">
         <v>3.45</v>
       </c>
       <c r="K32" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L32" t="n">
         <v>1.5</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="P32" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
         <v>4.6</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U32" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="V32" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W32" t="n">
         <v>2.12</v>
       </c>
       <c r="X32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y32" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AA32" t="n">
         <v>200</v>
       </c>
       <c r="AB32" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD32" t="n">
         <v>25</v>
@@ -8555,97 +8555,97 @@
         <v>120</v>
       </c>
       <c r="AF32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG32" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AI32" t="n">
         <v>130</v>
       </c>
       <c r="AJ32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN32" t="n">
         <v>21</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>17.5</v>
       </c>
       <c r="AO32" t="n">
         <v>180</v>
       </c>
       <c r="AP32" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="AQ32" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AR32" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="AS32" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU32" t="n">
         <v>7</v>
       </c>
       <c r="AV32" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX32" t="n">
         <v>8.6</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="BA32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BB32" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD32" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BF32" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BG32" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK32" t="n">
         <v>8.199999999999999</v>
@@ -8675,7 +8675,7 @@
         <v>24</v>
       </c>
       <c r="BT32" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU32" t="n">
         <v>6.4</v>
@@ -8684,23 +8684,23 @@
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BZ32" t="n">
         <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
@@ -8740,10 +8740,10 @@
         <v>2.92</v>
       </c>
       <c r="I33" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J33" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K33" t="n">
         <v>3.35</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -887,10 +887,10 @@
         <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
@@ -899,7 +899,7 @@
         <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U2" t="n">
         <v>2.04</v>
@@ -926,7 +926,7 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
         <v>19.5</v>
@@ -971,13 +971,13 @@
         <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU2" t="n">
         <v>6.4</v>
@@ -986,7 +986,7 @@
         <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
         <v>9.800000000000001</v>
@@ -998,7 +998,7 @@
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB2" t="n">
         <v>18.5</v>
@@ -1007,16 +1007,16 @@
         <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
         <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH2" t="n">
         <v>3.35</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="G3" t="n">
         <v>2.1</v>
@@ -1129,7 +1129,7 @@
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1168,10 +1168,10 @@
         <v>23</v>
       </c>
       <c r="Y3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
         <v>100</v>
@@ -1180,43 +1180,43 @@
         <v>11.5</v>
       </c>
       <c r="AC3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG3" t="n">
         <v>11</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AH3" t="n">
         <v>19.5</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AI3" t="n">
         <v>55</v>
       </c>
-      <c r="AF3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG3" t="n">
+      <c r="AJ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AO3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP3" t="n">
         <v>13.5</v>
@@ -1240,13 +1240,13 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX3" t="n">
         <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
@@ -1270,7 +1270,7 @@
         <v>10</v>
       </c>
       <c r="BG3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH3" t="n">
         <v>3.85</v>
@@ -1282,7 +1282,7 @@
         <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,13 +1294,13 @@
         <v>5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP3" t="n">
         <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H4" t="n">
         <v>4.2</v>
@@ -1380,139 +1380,139 @@
         <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="T4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X4" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="Y4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Z4" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD4" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF4" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
         <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL4" t="n">
         <v>23</v>
       </c>
-      <c r="AK4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP4" t="n">
         <v>30</v>
       </c>
-      <c r="AM4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>28</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS4" t="n">
         <v>36</v>
       </c>
       <c r="AT4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BB4" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BC4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD4" t="n">
         <v>16.5</v>
@@ -1521,31 +1521,31 @@
         <v>29</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO4" t="n">
         <v>4.8</v>
@@ -1554,41 +1554,41 @@
         <v>11</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
         <v>8.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>10.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -1619,37 +1619,37 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M5" t="n">
         <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="O5" t="n">
         <v>1.63</v>
       </c>
       <c r="P5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" t="n">
         <v>2.92</v>
@@ -1661,43 +1661,43 @@
         <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="X5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA5" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE5" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
         <v>14.5</v>
@@ -1706,13 +1706,13 @@
         <v>34</v>
       </c>
       <c r="AI5" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
         <v>90</v>
@@ -1721,10 +1721,10 @@
         <v>320</v>
       </c>
       <c r="AN5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AO5" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AP5" t="n">
         <v>1.03</v>
@@ -1775,7 +1775,7 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BG5" t="n">
         <v>1.01</v>
@@ -1784,10 +1784,10 @@
         <v>2.58</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="BJ5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK5" t="n">
         <v>9.6</v>
@@ -1799,16 +1799,16 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BP5" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1817,10 +1817,10 @@
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>2.68</v>
       </c>
       <c r="I6" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J6" t="n">
         <v>2.6</v>
@@ -1897,31 +1897,31 @@
         <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
         <v>1.65</v>
       </c>
       <c r="P6" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
         <v>1.61</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
         <v>1.38</v>
@@ -1939,7 +1939,7 @@
         <v>70</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>8.199999999999999</v>
@@ -2038,7 +2038,7 @@
         <v>2.54</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
@@ -2080,13 +2080,13 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H7" t="n">
         <v>3.35</v>
       </c>
       <c r="I7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
         <v>3.65</v>
@@ -2157,7 +2157,7 @@
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
         <v>1.72</v>
@@ -2172,13 +2172,13 @@
         <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V7" t="n">
         <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -2235,16 +2235,16 @@
         <v>38</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.6</v>
+        <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.8</v>
+        <v>19.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
         <v>8.800000000000001</v>
@@ -2256,7 +2256,7 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AX7" t="n">
         <v>11</v>
@@ -2268,19 +2268,19 @@
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>34</v>
+        <v>3.95</v>
       </c>
       <c r="BB7" t="n">
-        <v>5</v>
+        <v>19.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF7" t="n">
         <v>9.800000000000001</v>
@@ -2292,7 +2292,7 @@
         <v>3.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
         <v>9</v>
@@ -2316,13 +2316,13 @@
         <v>15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BT7" t="n">
         <v>7</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
         <v>4.1</v>
@@ -2402,19 +2402,19 @@
         <v>1.28</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
         <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R8" t="n">
         <v>1.51</v>
@@ -2426,91 +2426,91 @@
         <v>1.63</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V8" t="n">
         <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL8" t="n">
         <v>32</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>36</v>
       </c>
       <c r="AM8" t="n">
         <v>80</v>
       </c>
       <c r="AN8" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="AT8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
         <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.1</v>
+        <v>22</v>
       </c>
       <c r="AX8" t="n">
         <v>13.5</v>
@@ -2519,28 +2519,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.1</v>
+        <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC8" t="n">
         <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>5</v>
+        <v>19.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.4</v>
+        <v>32</v>
       </c>
       <c r="BF8" t="n">
         <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH8" t="n">
         <v>4</v>
@@ -2570,7 +2570,7 @@
         <v>14.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BR8" t="n">
         <v>25</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -2638,16 +2638,16 @@
         <v>2.34</v>
       </c>
       <c r="G9" t="n">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="H9" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="I9" t="n">
         <v>4.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="K9" t="n">
         <v>3.2</v>
@@ -2656,61 +2656,61 @@
         <v>1.52</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="O9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P9" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="R9" t="n">
         <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
         <v>16</v>
@@ -2719,16 +2719,16 @@
         <v>13.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
         <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AL9" t="n">
         <v>85</v>
@@ -2740,7 +2740,7 @@
         <v>60</v>
       </c>
       <c r="AO9" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
         <v>1.03</v>
@@ -2794,7 +2794,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
         <v>2.68</v>
@@ -2830,7 +2830,7 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>1.43</v>
       </c>
       <c r="G10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H10" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="J10" t="n">
         <v>3.85</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.47</v>
@@ -2913,7 +2913,7 @@
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O10" t="n">
         <v>1.44</v>
@@ -2922,16 +2922,16 @@
         <v>1.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
         <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U10" t="n">
         <v>1.51</v>
@@ -2940,13 +2940,13 @@
         <v>1.09</v>
       </c>
       <c r="W10" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X10" t="n">
         <v>12</v>
       </c>
       <c r="Y10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Z10" t="n">
         <v>1000</v>
@@ -2955,10 +2955,10 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD10" t="n">
         <v>50</v>
@@ -2967,10 +2967,10 @@
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
         <v>46</v>
@@ -2979,13 +2979,13 @@
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -3009,7 +3009,7 @@
         <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AU10" t="n">
         <v>1.03</v>
@@ -3021,10 +3021,10 @@
         <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AZ10" t="n">
         <v>1.03</v>
@@ -3045,40 +3045,40 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BG10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
@@ -3090,13 +3090,13 @@
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
         <v>1.01</v>
       </c>
       <c r="R11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
         <v>1.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S12" t="n">
         <v>1.46</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
         <v>1.09</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P13" t="n">
         <v>1.08</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
         <v>1.08</v>
       </c>
       <c r="S16" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -4673,16 +4673,16 @@
         <v>2.42</v>
       </c>
       <c r="H17" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J17" t="n">
         <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.26</v>
@@ -4694,13 +4694,13 @@
         <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="R17" t="n">
         <v>1.55</v>
@@ -4712,10 +4712,10 @@
         <v>1.54</v>
       </c>
       <c r="U17" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
         <v>1.7</v>
@@ -4736,7 +4736,7 @@
         <v>16.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD17" t="n">
         <v>16.5</v>
@@ -4745,7 +4745,7 @@
         <v>38</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG17" t="n">
         <v>13.5</v>
@@ -4787,7 +4787,7 @@
         <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
         <v>7.4</v>
@@ -4802,7 +4802,7 @@
         <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
         <v>1.03</v>
@@ -4814,7 +4814,7 @@
         <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
         <v>1.03</v>
@@ -4847,16 +4847,16 @@
         <v>21</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
@@ -4868,13 +4868,13 @@
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -4924,13 +4924,13 @@
         <v>1.66</v>
       </c>
       <c r="G18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H18" t="n">
         <v>5.1</v>
       </c>
       <c r="I18" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J18" t="n">
         <v>4.2</v>
@@ -4942,7 +4942,7 @@
         <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
         <v>5</v>
@@ -4954,7 +4954,7 @@
         <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R18" t="n">
         <v>1.54</v>
@@ -4966,16 +4966,16 @@
         <v>1.66</v>
       </c>
       <c r="U18" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W18" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y18" t="n">
         <v>25</v>
@@ -4990,16 +4990,16 @@
         <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD18" t="n">
         <v>25</v>
       </c>
       <c r="AE18" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AF18" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AG18" t="n">
         <v>10</v>
@@ -5008,7 +5008,7 @@
         <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AJ18" t="n">
         <v>18</v>
@@ -5017,10 +5017,10 @@
         <v>17</v>
       </c>
       <c r="AL18" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN18" t="n">
         <v>7.8</v>
@@ -5029,7 +5029,7 @@
         <v>65</v>
       </c>
       <c r="AP18" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>19.5</v>
@@ -5038,7 +5038,7 @@
         <v>36</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
         <v>9.6</v>
@@ -5050,7 +5050,7 @@
         <v>17.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -5062,7 +5062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB18" t="n">
         <v>14.5</v>
@@ -5071,16 +5071,16 @@
         <v>13.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH18" t="n">
         <v>4.4</v>
@@ -5122,7 +5122,7 @@
         <v>9.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="H19" t="n">
         <v>2.56</v>
@@ -5193,7 +5193,7 @@
         <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -5226,7 +5226,7 @@
         <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X19" t="n">
         <v>19</v>
@@ -5244,7 +5244,7 @@
         <v>15</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
         <v>14.5</v>
@@ -5331,7 +5331,7 @@
         <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BG19" t="n">
         <v>17.5</v>
@@ -5340,7 +5340,7 @@
         <v>3.65</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.199999999999999</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -5429,16 +5429,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G20" t="n">
         <v>1.36</v>
       </c>
       <c r="H20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I20" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
         <v>5.5</v>
@@ -5447,7 +5447,7 @@
         <v>6.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5456,13 +5456,13 @@
         <v>4.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
         <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R20" t="n">
         <v>1.46</v>
@@ -5471,13 +5471,13 @@
         <v>2.84</v>
       </c>
       <c r="T20" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U20" t="n">
         <v>1.73</v>
       </c>
       <c r="V20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W20" t="n">
         <v>3.75</v>
@@ -5486,7 +5486,7 @@
         <v>24</v>
       </c>
       <c r="Y20" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Z20" t="n">
         <v>140</v>
@@ -5495,7 +5495,7 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC20" t="n">
         <v>15.5</v>
@@ -5507,13 +5507,13 @@
         <v>270</v>
       </c>
       <c r="AF20" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI20" t="n">
         <v>210</v>
@@ -5540,13 +5540,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT20" t="n">
         <v>6.4</v>
@@ -5555,40 +5555,40 @@
         <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX20" t="n">
         <v>6.8</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC20" t="n">
         <v>11.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>34</v>
+        <v>5.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH20" t="n">
         <v>3.95</v>
@@ -5600,7 +5600,7 @@
         <v>13</v>
       </c>
       <c r="BK20" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5612,13 +5612,13 @@
         <v>3.7</v>
       </c>
       <c r="BO20" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BP20" t="n">
         <v>7.8</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BR20" t="n">
         <v>26</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G21" t="n">
         <v>2.64</v>
       </c>
       <c r="H21" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="I21" t="n">
         <v>3.15</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
         <v>1.32</v>
@@ -5713,10 +5713,10 @@
         <v>1.26</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="R21" t="n">
         <v>1.4</v>
@@ -5728,7 +5728,7 @@
         <v>1.64</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="V21" t="n">
         <v>1.46</v>
@@ -5737,70 +5737,70 @@
         <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y21" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
         <v>14</v>
       </c>
       <c r="AE21" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG21" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
         <v>17</v>
       </c>
       <c r="AI21" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AJ21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL21" t="n">
         <v>42</v>
       </c>
       <c r="AM21" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN21" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO21" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AP21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -5812,7 +5812,7 @@
         <v>10</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX21" t="n">
         <v>14.5</v>
@@ -5833,7 +5833,7 @@
         <v>21</v>
       </c>
       <c r="BD21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BE21" t="n">
         <v>1.03</v>
@@ -5866,7 +5866,7 @@
         <v>5.8</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP21" t="n">
         <v>19</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G22" t="n">
         <v>2.12</v>
@@ -5946,10 +5946,10 @@
         <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
         <v>3.9</v>
@@ -6012,7 +6012,7 @@
         <v>22</v>
       </c>
       <c r="AE22" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF22" t="n">
         <v>15</v>
@@ -6030,7 +6030,7 @@
         <v>29</v>
       </c>
       <c r="AK22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
         <v>48</v>
@@ -6048,43 +6048,43 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
         <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW22" t="n">
         <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY22" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
         <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BC22" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BD22" t="n">
         <v>1.03</v>
@@ -6093,7 +6093,7 @@
         <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG22" t="n">
         <v>48</v>
@@ -6120,7 +6120,7 @@
         <v>4.8</v>
       </c>
       <c r="BO22" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BP22" t="n">
         <v>15</v>
@@ -6138,7 +6138,7 @@
         <v>7.8</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="G23" t="n">
         <v>6</v>
@@ -6200,7 +6200,7 @@
         <v>1.69</v>
       </c>
       <c r="I23" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="J23" t="n">
         <v>3.95</v>
@@ -6215,7 +6215,7 @@
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
         <v>1.26</v>
@@ -6233,31 +6233,31 @@
         <v>3.05</v>
       </c>
       <c r="T23" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="U23" t="n">
         <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="W23" t="n">
         <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AA23" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AB23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AC23" t="n">
         <v>970</v>
@@ -6269,7 +6269,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG23" t="n">
         <v>26</v>
@@ -6281,7 +6281,7 @@
         <v>44</v>
       </c>
       <c r="AJ23" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AK23" t="n">
         <v>95</v>
@@ -6296,61 +6296,61 @@
         <v>110</v>
       </c>
       <c r="AO23" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.75</v>
+        <v>7.8</v>
       </c>
       <c r="AV23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="BA23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC23" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BD23" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH23" t="n">
         <v>3.8</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>4.8</v>
       </c>
       <c r="G24" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="H24" t="n">
         <v>1.59</v>
@@ -6457,7 +6457,7 @@
         <v>1.68</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K24" t="n">
         <v>5.5</v>
@@ -6478,13 +6478,13 @@
         <v>3.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="R24" t="n">
         <v>1.91</v>
       </c>
       <c r="S24" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="T24" t="n">
         <v>1.5</v>
@@ -6493,124 +6493,124 @@
         <v>2.68</v>
       </c>
       <c r="V24" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="W24" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="Y24" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Z24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA24" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG24" t="n">
         <v>22</v>
       </c>
-      <c r="AB24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>27</v>
-      </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AI24" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AJ24" t="n">
         <v>130</v>
       </c>
       <c r="AK24" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM24" t="n">
         <v>55</v>
       </c>
-      <c r="AM24" t="n">
-        <v>65</v>
-      </c>
       <c r="AN24" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AO24" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB24" t="n">
         <v>11</v>
       </c>
-      <c r="AS24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.95</v>
+        <v>9.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BH24" t="n">
         <v>5.5</v>
       </c>
       <c r="BI24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ24" t="n">
         <v>9</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -6699,100 +6699,100 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="H25" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="J25" t="n">
         <v>3.75</v>
       </c>
       <c r="K25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
         <v>1.23</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O25" t="n">
         <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R25" t="n">
         <v>1.62</v>
       </c>
       <c r="S25" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T25" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U25" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W25" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="X25" t="n">
         <v>32</v>
       </c>
       <c r="Y25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA25" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AB25" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
         <v>17.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ25" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL25" t="n">
         <v>34</v>
@@ -6801,25 +6801,25 @@
         <v>65</v>
       </c>
       <c r="AN25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AQ25" t="n">
         <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU25" t="n">
         <v>7.4</v>
@@ -6828,43 +6828,43 @@
         <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
         <v>10.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC25" t="n">
         <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BF25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH25" t="n">
         <v>4.8</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ25" t="n">
         <v>9</v>
@@ -6882,7 +6882,7 @@
         <v>6.6</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP25" t="n">
         <v>18.5</v>
@@ -6894,7 +6894,7 @@
         <v>26</v>
       </c>
       <c r="BS25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT25" t="n">
         <v>6.6</v>
@@ -6903,7 +6903,7 @@
         <v>4.7</v>
       </c>
       <c r="BV25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW25" t="n">
         <v>5.8</v>
@@ -6912,7 +6912,7 @@
         <v>26</v>
       </c>
       <c r="BY25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ25" t="n">
         <v>16</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -6962,22 +6962,22 @@
         <v>1.74</v>
       </c>
       <c r="I26" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="J26" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="O26" t="n">
         <v>1.14</v>
@@ -6989,7 +6989,7 @@
         <v>1.43</v>
       </c>
       <c r="R26" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="S26" t="n">
         <v>2.06</v>
@@ -7004,7 +7004,7 @@
         <v>2.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X26" t="n">
         <v>40</v>
@@ -7019,37 +7019,37 @@
         <v>25</v>
       </c>
       <c r="AB26" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AC26" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE26" t="n">
         <v>970</v>
       </c>
       <c r="AF26" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AG26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="n">
         <v>970</v>
       </c>
       <c r="AI26" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AJ26" t="n">
         <v>90</v>
       </c>
       <c r="AK26" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL26" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM26" t="n">
         <v>60</v>
@@ -7058,61 +7058,61 @@
         <v>30</v>
       </c>
       <c r="AO26" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AT26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV26" t="n">
         <v>4.7</v>
       </c>
-      <c r="AU26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AW26" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AY26" t="n">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BD26" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="BH26" t="n">
         <v>5.2</v>
@@ -7124,7 +7124,7 @@
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
@@ -7136,25 +7136,25 @@
         <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BT26" t="n">
         <v>5.4</v>
       </c>
       <c r="BU26" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O27" t="n">
         <v>1.21</v>
@@ -7240,7 +7240,7 @@
         <v>2.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R27" t="n">
         <v>1.51</v>
@@ -7294,7 +7294,7 @@
         <v>23</v>
       </c>
       <c r="AI27" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ27" t="n">
         <v>19</v>
@@ -7309,7 +7309,7 @@
         <v>100</v>
       </c>
       <c r="AN27" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO27" t="n">
         <v>80</v>
@@ -7321,10 +7321,10 @@
         <v>18</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT27" t="n">
         <v>9</v>
@@ -7336,10 +7336,10 @@
         <v>17</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AX27" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AY27" t="n">
         <v>8.800000000000001</v>
@@ -7348,7 +7348,7 @@
         <v>14.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BB27" t="n">
         <v>12.5</v>
@@ -7357,16 +7357,16 @@
         <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF27" t="n">
         <v>5.7</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BH27" t="n">
         <v>4.4</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G28" t="n">
         <v>4.2</v>
       </c>
       <c r="H28" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="I28" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J28" t="n">
         <v>4.8</v>
       </c>
       <c r="K28" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L28" t="n">
         <v>1.12</v>
@@ -7491,13 +7491,13 @@
         <v>1.05</v>
       </c>
       <c r="P28" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="Q28" t="n">
         <v>1.17</v>
       </c>
       <c r="R28" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="S28" t="n">
         <v>1.41</v>
@@ -7512,7 +7512,7 @@
         <v>2.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X28" t="n">
         <v>120</v>
@@ -7626,7 +7626,7 @@
         <v>9</v>
       </c>
       <c r="BI28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BJ28" t="n">
         <v>8.6</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -7727,16 +7727,16 @@
         <v>5.7</v>
       </c>
       <c r="J29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K29" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L29" t="n">
         <v>1.45</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N29" t="n">
         <v>2.66</v>
@@ -7748,19 +7748,19 @@
         <v>1.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U29" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V29" t="n">
         <v>1.21</v>
@@ -7769,70 +7769,70 @@
         <v>2.08</v>
       </c>
       <c r="X29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y29" t="n">
         <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AA29" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB29" t="n">
         <v>6.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE29" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF29" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI29" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AL29" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM29" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AO29" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="AQ29" t="n">
         <v>11.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT29" t="n">
         <v>5.7</v>
@@ -7841,40 +7841,40 @@
         <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY29" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB29" t="n">
         <v>18.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD29" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BE29" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BF29" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="BG29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BH29" t="n">
         <v>2.82</v>
@@ -7898,7 +7898,7 @@
         <v>4.3</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BP29" t="n">
         <v>15</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>3.3</v>
       </c>
       <c r="G30" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H30" t="n">
         <v>2.18</v>
@@ -7984,7 +7984,7 @@
         <v>3.45</v>
       </c>
       <c r="K30" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L30" t="n">
         <v>1.44</v>
@@ -7993,7 +7993,7 @@
         <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
         <v>1.38</v>
@@ -8011,22 +8011,22 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U30" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V30" t="n">
         <v>1.71</v>
       </c>
       <c r="W30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X30" t="n">
         <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Z30" t="n">
         <v>16</v>
@@ -8038,7 +8038,7 @@
         <v>13.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD30" t="n">
         <v>13</v>
@@ -8053,7 +8053,7 @@
         <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI30" t="n">
         <v>55</v>
@@ -8077,58 +8077,58 @@
         <v>27</v>
       </c>
       <c r="AP30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX30" t="n">
+      <c r="BA30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB30" t="n">
         <v>4.9</v>
       </c>
-      <c r="AY30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BC30" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BH30" t="n">
         <v>3.3</v>
@@ -8152,7 +8152,7 @@
         <v>7.2</v>
       </c>
       <c r="BO30" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -8477,13 +8477,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="G32" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I32" t="n">
         <v>5.8</v>
@@ -8492,10 +8492,10 @@
         <v>3.45</v>
       </c>
       <c r="K32" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
@@ -8507,19 +8507,19 @@
         <v>1.42</v>
       </c>
       <c r="P32" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R32" t="n">
         <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U32" t="n">
         <v>1.82</v>
@@ -8528,49 +8528,49 @@
         <v>1.2</v>
       </c>
       <c r="W32" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X32" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y32" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AA32" t="n">
         <v>200</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE32" t="n">
         <v>120</v>
       </c>
       <c r="AF32" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG32" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI32" t="n">
         <v>130</v>
       </c>
       <c r="AJ32" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AL32" t="n">
         <v>60</v>
@@ -8579,22 +8579,22 @@
         <v>210</v>
       </c>
       <c r="AN32" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AO32" t="n">
         <v>180</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="AQ32" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="AT32" t="n">
         <v>6.4</v>
@@ -8603,40 +8603,40 @@
         <v>7</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="AW32" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AX32" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="AY32" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="BA32" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="BB32" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH32" t="n">
         <v>3.05</v>
@@ -8693,14 +8693,14 @@
         <v>46</v>
       </c>
       <c r="BZ32" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA32" t="n">
         <v>22</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
         <v>2.58</v>
       </c>
       <c r="G33" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H33" t="n">
         <v>2.92</v>
@@ -8746,7 +8746,7 @@
         <v>3.05</v>
       </c>
       <c r="K33" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-09 08:56:31</t>
+          <t>2026-07-09 11:27:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G2" t="n">
         <v>2.1</v>
@@ -869,10 +869,10 @@
         <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.43</v>
@@ -881,52 +881,52 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
         <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T2" t="n">
         <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
         <v>1.9</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
         <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
         <v>19.5</v>
@@ -935,7 +935,7 @@
         <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -962,7 +962,7 @@
         <v>19.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP2" t="n">
         <v>10</v>
@@ -971,34 +971,34 @@
         <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
         <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AX2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB2" t="n">
         <v>18.5</v>
@@ -1007,16 +1007,16 @@
         <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BF2" t="n">
         <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BH2" t="n">
         <v>3.35</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
         <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
         <v>1.73</v>
@@ -1153,7 +1153,7 @@
         <v>2.86</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U3" t="n">
         <v>2.4</v>
@@ -1225,10 +1225,10 @@
         <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AT3" t="n">
         <v>9.6</v>
@@ -1240,7 +1240,7 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX3" t="n">
         <v>12</v>
@@ -1258,13 +1258,13 @@
         <v>20</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
         <v>10</v>
@@ -1282,7 +1282,7 @@
         <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1312,7 +1312,7 @@
         <v>7.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -1374,46 +1374,46 @@
         <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
         <v>7.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q4" t="n">
         <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="T4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
         <v>2.16</v>
@@ -1422,10 +1422,10 @@
         <v>36</v>
       </c>
       <c r="Y4" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="Z4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
@@ -1434,13 +1434,13 @@
         <v>22</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
@@ -1449,10 +1449,10 @@
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="n">
         <v>32</v>
@@ -1464,19 +1464,19 @@
         <v>30</v>
       </c>
       <c r="AM4" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR4" t="n">
         <v>24</v>
@@ -1491,22 +1491,22 @@
         <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW4" t="n">
         <v>23</v>
       </c>
       <c r="AX4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BB4" t="n">
         <v>16.5</v>
@@ -1518,13 +1518,13 @@
         <v>16.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BF4" t="n">
         <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BH4" t="n">
         <v>5.3</v>
@@ -1539,7 +1539,7 @@
         <v>5.7</v>
       </c>
       <c r="BL4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
         <v>13</v>
@@ -1554,7 +1554,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BR4" t="n">
         <v>18</v>
@@ -1584,11 +1584,11 @@
         <v>10.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
         <v>7.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
         <v>40</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>1.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R6" t="n">
         <v>1.13</v>
@@ -2038,7 +2038,7 @@
         <v>2.54</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q7" t="n">
         <v>1.72</v>
@@ -2256,7 +2256,7 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX7" t="n">
         <v>11</v>
@@ -2277,7 +2277,7 @@
         <v>17.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE7" t="n">
         <v>4.8</v>
@@ -2286,7 +2286,7 @@
         <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH7" t="n">
         <v>3.9</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I8" t="n">
         <v>3.65</v>
@@ -2399,7 +2399,7 @@
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -2411,16 +2411,16 @@
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
         <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
         <v>1.62</v>
@@ -2462,10 +2462,10 @@
         <v>15.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>46</v>
@@ -2477,10 +2477,10 @@
         <v>23</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN8" t="n">
         <v>12</v>
@@ -2525,7 +2525,7 @@
         <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC8" t="n">
         <v>18</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -2644,31 +2644,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P9" t="n">
         <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R9" t="n">
         <v>1.2</v>
@@ -2677,7 +2677,7 @@
         <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
         <v>1.48</v>
@@ -2689,7 +2689,7 @@
         <v>2.8</v>
       </c>
       <c r="X9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="n">
         <v>25</v>
@@ -2701,13 +2701,13 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2728,7 +2728,7 @@
         <v>14</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2755,7 +2755,7 @@
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AU9" t="n">
         <v>1.03</v>
@@ -2782,7 +2782,7 @@
         <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BD9" t="n">
         <v>1.03</v>
@@ -2797,10 +2797,10 @@
         <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
         <v>3.5</v>
@@ -2901,13 +2901,13 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="K10" t="n">
         <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="M10" t="n">
         <v>1.14</v>
@@ -2931,7 +2931,7 @@
         <v>5.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
         <v>1.7</v>
@@ -2940,7 +2940,7 @@
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
         <v>8.199999999999999</v>
@@ -2949,7 +2949,7 @@
         <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
         <v>100</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="G11" t="n">
-        <v>110</v>
+        <v>2.78</v>
       </c>
       <c r="H11" t="n">
         <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>110</v>
+        <v>8.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>2.4</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="O11" t="n">
         <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="R11" t="n">
         <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>1.54</v>
+        <v>2.46</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3191,10 +3191,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="G12" t="n">
         <v>3.45</v>
@@ -3406,46 +3406,46 @@
         <v>2.96</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J12" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="K12" t="n">
         <v>3.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="M12" t="n">
         <v>1.16</v>
       </c>
       <c r="N12" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="O12" t="n">
         <v>1.68</v>
       </c>
       <c r="P12" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Q12" t="n">
         <v>3.05</v>
       </c>
       <c r="R12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>5.9</v>
       </c>
       <c r="T12" t="n">
         <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
         <v>1.4</v>
@@ -3454,25 +3454,25 @@
         <v>7.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB12" t="n">
         <v>8</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
         <v>21</v>
@@ -3481,10 +3481,10 @@
         <v>16</v>
       </c>
       <c r="AH12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI12" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ12" t="n">
         <v>70</v>
@@ -3493,19 +3493,19 @@
         <v>65</v>
       </c>
       <c r="AL12" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM12" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AN12" t="n">
         <v>90</v>
       </c>
       <c r="AO12" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.03</v>
@@ -3517,10 +3517,10 @@
         <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV12" t="n">
         <v>1.03</v>
@@ -3532,7 +3532,7 @@
         <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.03</v>
@@ -3553,22 +3553,22 @@
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,13 +3580,13 @@
         <v>6</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP12" t="n">
         <v>32</v>
       </c>
       <c r="BQ12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
@@ -3595,22 +3595,22 @@
         <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -3654,73 +3654,73 @@
         <v>3.1</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="H13" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="I13" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="K13" t="n">
         <v>3.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="M13" t="n">
         <v>1.16</v>
       </c>
       <c r="N13" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="O13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="P13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.37</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.32</v>
       </c>
       <c r="X13" t="n">
         <v>7.6</v>
       </c>
       <c r="Y13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC13" t="n">
         <v>7.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.4</v>
       </c>
       <c r="AD13" t="n">
         <v>15</v>
@@ -3729,43 +3729,43 @@
         <v>50</v>
       </c>
       <c r="AF13" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI13" t="n">
         <v>110</v>
       </c>
       <c r="AJ13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN13" t="n">
         <v>110</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>340</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>140</v>
       </c>
       <c r="AO13" t="n">
         <v>65</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS13" t="n">
         <v>1.03</v>
@@ -3783,10 +3783,10 @@
         <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>1.03</v>
@@ -3807,22 +3807,22 @@
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.199999999999999</v>
+        <v>75</v>
       </c>
       <c r="BG13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="BJ13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3831,37 +3831,37 @@
         <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BP13" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BT13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BW13" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BX13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -3905,155 +3905,155 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="U14" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="X14" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="Y14" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>230</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC14" t="n">
         <v>15</v>
       </c>
-      <c r="Z14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BD14" t="n">
         <v>1.03</v>
       </c>
@@ -4061,10 +4061,10 @@
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>140</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -4159,61 +4159,61 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G15" t="n">
         <v>2.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
         <v>2.9</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="R15" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
         <v>1.71</v>
       </c>
       <c r="X15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y15" t="n">
         <v>12</v>
@@ -4222,19 +4222,19 @@
         <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="n">
         <v>7.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD15" t="n">
         <v>20</v>
       </c>
       <c r="AE15" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="n">
         <v>13</v>
@@ -4255,25 +4255,25 @@
         <v>34</v>
       </c>
       <c r="AL15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM15" t="n">
         <v>250</v>
       </c>
       <c r="AN15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO15" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AQ15" t="n">
         <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AS15" t="n">
         <v>1.03</v>
@@ -4321,13 +4321,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI15" t="n">
         <v>2.2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK15" t="n">
         <v>8.4</v>
@@ -4342,13 +4342,13 @@
         <v>5</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP15" t="n">
         <v>20</v>
       </c>
       <c r="BQ15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
@@ -4357,10 +4357,10 @@
         <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="G16" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="H16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.47</v>
@@ -4437,106 +4437,106 @@
         <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P16" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W16" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X16" t="n">
         <v>11</v>
       </c>
       <c r="Y16" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="n">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="AB16" t="n">
         <v>6.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AF16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI16" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AJ16" t="n">
         <v>21</v>
       </c>
       <c r="AK16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AS16" t="n">
         <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV16" t="n">
         <v>1.03</v>
@@ -4551,7 +4551,7 @@
         <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BA16" t="n">
         <v>1.03</v>
@@ -4560,7 +4560,7 @@
         <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BD16" t="n">
         <v>1.03</v>
@@ -4572,16 +4572,16 @@
         <v>13.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI16" t="n">
         <v>2.38</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK16" t="n">
         <v>8</v>
@@ -4596,28 +4596,28 @@
         <v>4.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="BP16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BU16" t="n">
         <v>6.2</v>
       </c>
       <c r="BV16" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BW16" t="n">
         <v>8.800000000000001</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -4667,118 +4667,118 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="G17" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="H17" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P17" t="n">
         <v>1.47</v>
       </c>
-      <c r="P17" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>2.74</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="S17" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="T17" t="n">
         <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="W17" t="n">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="Z17" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>560</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AE17" t="n">
-        <v>410</v>
+        <v>310</v>
       </c>
       <c r="AF17" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AI17" t="n">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="AJ17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AK17" t="n">
         <v>27</v>
       </c>
       <c r="AL17" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM17" t="n">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="AN17" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
         <v>1.03</v>
@@ -4787,10 +4787,10 @@
         <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
         <v>1.03</v>
@@ -4799,10 +4799,10 @@
         <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
         <v>1.03</v>
@@ -4811,10 +4811,10 @@
         <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
         <v>1.03</v>
@@ -4823,22 +4823,22 @@
         <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BG17" t="n">
         <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BK17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4847,28 +4847,28 @@
         <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BO17" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="BP17" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR17" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BT17" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
@@ -4883,14 +4883,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="CA17" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -4924,10 +4924,10 @@
         <v>2.14</v>
       </c>
       <c r="G18" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H18" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
         <v>3.45</v>
@@ -4954,13 +4954,13 @@
         <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="R18" t="n">
         <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T18" t="n">
         <v>1.54</v>
@@ -4972,7 +4972,7 @@
         <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X18" t="n">
         <v>27</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
         <v>1.29</v>
       </c>
       <c r="M19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
         <v>5</v>
@@ -5205,7 +5205,7 @@
         <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
         <v>1.6</v>
@@ -5226,7 +5226,7 @@
         <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X19" t="n">
         <v>24</v>
@@ -5244,16 +5244,16 @@
         <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
         <v>65</v>
       </c>
       <c r="AF19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
         <v>10</v>
@@ -5292,7 +5292,7 @@
         <v>36</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -5304,7 +5304,7 @@
         <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX19" t="n">
         <v>10</v>
@@ -5316,7 +5316,7 @@
         <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB19" t="n">
         <v>14.5</v>
@@ -5325,34 +5325,34 @@
         <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>40</v>
+        <v>7.8</v>
       </c>
       <c r="BH19" t="n">
         <v>4.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN19" t="n">
         <v>4.7</v>
@@ -5364,31 +5364,31 @@
         <v>11</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT19" t="n">
         <v>9.4</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV19" t="n">
         <v>42</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -5438,13 +5438,13 @@
         <v>2.56</v>
       </c>
       <c r="I20" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L20" t="n">
         <v>1.32</v>
@@ -5453,31 +5453,31 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>1.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
         <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U20" t="n">
         <v>2.26</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
         <v>1.51</v>
@@ -5552,7 +5552,7 @@
         <v>11</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV20" t="n">
         <v>10.5</v>
@@ -5561,7 +5561,7 @@
         <v>21</v>
       </c>
       <c r="AX20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY20" t="n">
         <v>11</v>
@@ -5573,7 +5573,7 @@
         <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BC20" t="n">
         <v>1.03</v>
@@ -5600,7 +5600,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5612,7 +5612,7 @@
         <v>6</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
@@ -5630,7 +5630,7 @@
         <v>5.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -5683,25 +5683,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="J21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K21" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -5710,157 +5710,157 @@
         <v>4.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P21" t="n">
         <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R21" t="n">
         <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U21" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="X21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Z21" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AB21" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AD21" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AE21" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AF21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI21" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM21" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN21" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AO21" t="n">
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="AP21" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.7</v>
+        <v>30</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT21" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5.5</v>
+        <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC21" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.8</v>
+        <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH21" t="n">
         <v>3.95</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BJ21" t="n">
         <v>13</v>
       </c>
       <c r="BK21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN21" t="n">
         <v>3.7</v>
@@ -5872,31 +5872,31 @@
         <v>7.8</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BR21" t="n">
         <v>26</v>
       </c>
       <c r="BS21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT21" t="n">
         <v>14.5</v>
       </c>
       <c r="BU21" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -5940,19 +5940,19 @@
         <v>2.4</v>
       </c>
       <c r="G22" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H22" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="I22" t="n">
         <v>3.15</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L22" t="n">
         <v>1.35</v>
@@ -5970,13 +5970,13 @@
         <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T22" t="n">
         <v>1.64</v>
@@ -5988,7 +5988,7 @@
         <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X22" t="n">
         <v>18</v>
@@ -6033,7 +6033,7 @@
         <v>27</v>
       </c>
       <c r="AL22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM22" t="n">
         <v>80</v>
@@ -6045,46 +6045,46 @@
         <v>27</v>
       </c>
       <c r="AP22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ22" t="n">
         <v>11.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA22" t="n">
         <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="BC22" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD22" t="n">
         <v>1.03</v>
@@ -6093,7 +6093,7 @@
         <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BG22" t="n">
         <v>19</v>
@@ -6102,19 +6102,19 @@
         <v>3.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ22" t="n">
         <v>9.4</v>
       </c>
       <c r="BK22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN22" t="n">
         <v>5.8</v>
@@ -6123,16 +6123,16 @@
         <v>4.8</v>
       </c>
       <c r="BP22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT22" t="n">
         <v>6.4</v>
@@ -6144,13 +6144,13 @@
         <v>23</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX22" t="n">
         <v>34</v>
       </c>
       <c r="BY22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G23" t="n">
         <v>2.12</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
         <v>3.9</v>
@@ -6215,34 +6215,34 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
         <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U23" t="n">
         <v>1.99</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W23" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X23" t="n">
         <v>16</v>
@@ -6260,7 +6260,7 @@
         <v>10.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23" t="n">
         <v>22</v>
@@ -6278,7 +6278,7 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ23" t="n">
         <v>29</v>
@@ -6302,13 +6302,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT23" t="n">
         <v>6.4</v>
@@ -6320,7 +6320,7 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX23" t="n">
         <v>9</v>
@@ -6332,7 +6332,7 @@
         <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB23" t="n">
         <v>17</v>
@@ -6341,19 +6341,19 @@
         <v>16</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF23" t="n">
         <v>11.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>48</v>
+        <v>4.1</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI23" t="n">
         <v>2.64</v>
@@ -6362,13 +6362,13 @@
         <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN23" t="n">
         <v>4.8</v>
@@ -6380,13 +6380,13 @@
         <v>15</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR23" t="n">
         <v>32</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT23" t="n">
         <v>7.8</v>
@@ -6398,13 +6398,13 @@
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -6451,10 +6451,10 @@
         <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="J24" t="n">
         <v>3.95</v>
@@ -6493,7 +6493,7 @@
         <v>2.02</v>
       </c>
       <c r="V24" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="W24" t="n">
         <v>1.2</v>
@@ -6514,7 +6514,7 @@
         <v>25</v>
       </c>
       <c r="AC24" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AD24" t="n">
         <v>12.5</v>
@@ -6526,10 +6526,10 @@
         <v>60</v>
       </c>
       <c r="AG24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
         <v>44</v>
@@ -6538,13 +6538,13 @@
         <v>180</v>
       </c>
       <c r="AK24" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AL24" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM24" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN24" t="n">
         <v>110</v>
@@ -6553,7 +6553,7 @@
         <v>970</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>8.199999999999999</v>
@@ -6562,55 +6562,55 @@
         <v>9</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU24" t="n">
         <v>7.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA24" t="n">
         <v>5.1</v>
       </c>
-      <c r="AY24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5</v>
-      </c>
       <c r="BB24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE24" t="n">
         <v>5.5</v>
       </c>
-      <c r="BC24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BF24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BH24" t="n">
         <v>3.8</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ24" t="n">
         <v>11</v>
@@ -6622,7 +6622,7 @@
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN24" t="n">
         <v>9.800000000000001</v>
@@ -6634,7 +6634,7 @@
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
@@ -6646,7 +6646,7 @@
         <v>4.4</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BV24" t="n">
         <v>11</v>
@@ -6658,7 +6658,7 @@
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
         <v>1.91</v>
       </c>
       <c r="S25" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="T25" t="n">
         <v>1.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>3.75</v>
       </c>
       <c r="K26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L26" t="n">
         <v>1.23</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
         <v>3.8</v>
       </c>
       <c r="G27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H27" t="n">
         <v>1.76</v>
@@ -7231,13 +7231,13 @@
         <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
         <v>1.14</v>
       </c>
       <c r="P27" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q27" t="n">
         <v>1.43</v>
@@ -7252,7 +7252,7 @@
         <v>1.49</v>
       </c>
       <c r="U27" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V27" t="n">
         <v>2.08</v>
@@ -7270,7 +7270,7 @@
         <v>970</v>
       </c>
       <c r="AA27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB27" t="n">
         <v>27</v>
@@ -7288,7 +7288,7 @@
         <v>40</v>
       </c>
       <c r="AG27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH27" t="n">
         <v>970</v>
@@ -7315,61 +7315,61 @@
         <v>7</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS27" t="n">
         <v>6</v>
       </c>
       <c r="AT27" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AU27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV27" t="n">
         <v>4.9</v>
       </c>
-      <c r="AV27" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AW27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>5.5</v>
       </c>
-      <c r="AX27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BA27" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="BG27" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BH27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI27" t="n">
         <v>4</v>
@@ -7384,7 +7384,7 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BN27" t="n">
         <v>1000</v>
@@ -7396,7 +7396,7 @@
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
@@ -7408,7 +7408,7 @@
         <v>5.4</v>
       </c>
       <c r="BU27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
         <v>4.6</v>
       </c>
       <c r="O28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P28" t="n">
         <v>2.26</v>
@@ -7632,7 +7632,7 @@
         <v>10</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
@@ -7656,7 +7656,7 @@
         <v>23</v>
       </c>
       <c r="BS28" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT28" t="n">
         <v>9.800000000000001</v>
@@ -7674,7 +7674,7 @@
         <v>48</v>
       </c>
       <c r="BY28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ28" t="n">
         <v>15</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>1.84</v>
       </c>
       <c r="G30" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H30" t="n">
         <v>5.1</v>
@@ -8011,7 +8011,7 @@
         <v>5.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U30" t="n">
         <v>1.7</v>
@@ -8020,7 +8020,7 @@
         <v>1.21</v>
       </c>
       <c r="W30" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X30" t="n">
         <v>9.4</v>
@@ -8152,7 +8152,7 @@
         <v>4.3</v>
       </c>
       <c r="BO30" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="BP30" t="n">
         <v>15</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -8229,16 +8229,16 @@
         <v>3.75</v>
       </c>
       <c r="H31" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I31" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>3.45</v>
       </c>
       <c r="K31" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L31" t="n">
         <v>1.44</v>
@@ -8319,7 +8319,7 @@
         <v>60</v>
       </c>
       <c r="AL31" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM31" t="n">
         <v>150</v>
@@ -8346,10 +8346,10 @@
         <v>3.75</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AW31" t="n">
         <v>4.5</v>
@@ -8376,13 +8376,13 @@
         <v>4.9</v>
       </c>
       <c r="BE31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF31" t="n">
         <v>4.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH31" t="n">
         <v>3.3</v>
@@ -8394,7 +8394,7 @@
         <v>10.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
@@ -8406,7 +8406,7 @@
         <v>7.2</v>
       </c>
       <c r="BO31" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
@@ -8424,7 +8424,7 @@
         <v>5.2</v>
       </c>
       <c r="BU31" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G32" t="n">
         <v>2.34</v>
@@ -8489,10 +8489,10 @@
         <v>4.1</v>
       </c>
       <c r="J32" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -8734,37 +8734,37 @@
         <v>1.78</v>
       </c>
       <c r="G33" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H33" t="n">
         <v>5.4</v>
       </c>
       <c r="I33" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K33" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L33" t="n">
         <v>1.49</v>
       </c>
       <c r="M33" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O33" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P33" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R33" t="n">
         <v>1.25</v>
@@ -8773,46 +8773,46 @@
         <v>4.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U33" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V33" t="n">
         <v>1.2</v>
       </c>
       <c r="W33" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X33" t="n">
         <v>970</v>
       </c>
       <c r="Y33" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z33" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AA33" t="n">
         <v>200</v>
       </c>
       <c r="AB33" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC33" t="n">
         <v>7.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE33" t="n">
         <v>120</v>
       </c>
       <c r="AF33" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AG33" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AH33" t="n">
         <v>25</v>
@@ -8821,7 +8821,7 @@
         <v>130</v>
       </c>
       <c r="AJ33" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK33" t="n">
         <v>23</v>
@@ -8842,13 +8842,13 @@
         <v>10</v>
       </c>
       <c r="AQ33" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR33" t="n">
         <v>34</v>
       </c>
       <c r="AS33" t="n">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="AT33" t="n">
         <v>6.4</v>
@@ -8857,10 +8857,10 @@
         <v>7</v>
       </c>
       <c r="AV33" t="n">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="AW33" t="n">
-        <v>4</v>
+        <v>2.32</v>
       </c>
       <c r="AX33" t="n">
         <v>5.6</v>
@@ -8872,37 +8872,37 @@
         <v>21</v>
       </c>
       <c r="BA33" t="n">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="BB33" t="n">
-        <v>17.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC33" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BD33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="BF33" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG33" t="n">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="BH33" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ33" t="n">
         <v>11.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
@@ -8917,7 +8917,7 @@
         <v>3.8</v>
       </c>
       <c r="BP33" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ33" t="n">
         <v>11.5</v>
@@ -8929,10 +8929,10 @@
         <v>24</v>
       </c>
       <c r="BT33" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU33" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
@@ -8947,14 +8947,14 @@
         <v>46</v>
       </c>
       <c r="BZ33" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA33" t="n">
         <v>22</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G2" t="n">
         <v>2.1</v>
@@ -869,25 +869,25 @@
         <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
         <v>2.06</v>
@@ -899,22 +899,22 @@
         <v>3.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U2" t="n">
         <v>2.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
         <v>1.9</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
         <v>36</v>
@@ -938,10 +938,10 @@
         <v>14</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
         <v>75</v>
@@ -971,10 +971,10 @@
         <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
@@ -986,7 +986,7 @@
         <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
         <v>9.800000000000001</v>
@@ -998,7 +998,7 @@
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
         <v>18.5</v>
@@ -1007,22 +1007,22 @@
         <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
         <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
@@ -1037,7 +1037,7 @@
         <v>10</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO2" t="n">
         <v>3.75</v>
@@ -1046,7 +1046,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
         <v>32</v>
@@ -1064,23 +1064,23 @@
         <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>30</v>
       </c>
       <c r="CA2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
         <v>3.7</v>
@@ -1135,13 +1135,13 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
         <v>1.73</v>
@@ -1150,7 +1150,7 @@
         <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="T3" t="n">
         <v>1.66</v>
@@ -1162,19 +1162,19 @@
         <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="X3" t="n">
         <v>19</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AA3" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
         <v>11.5</v>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
       <c r="AE3" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
@@ -1195,13 +1195,13 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AK3" t="n">
         <v>20</v>
@@ -1210,25 +1210,25 @@
         <v>32</v>
       </c>
       <c r="AM3" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
-        <v>42</v>
+        <v>240</v>
       </c>
       <c r="AP3" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>9.6</v>
@@ -1240,7 +1240,7 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX3" t="n">
         <v>12</v>
@@ -1258,13 +1258,13 @@
         <v>20</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3" t="n">
         <v>10</v>
@@ -1276,19 +1276,19 @@
         <v>3.85</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
         <v>5</v>
@@ -1300,41 +1300,41 @@
         <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
         <v>7.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
         <v>8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -1365,31 +1365,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
         <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
         <v>4.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.13</v>
@@ -1401,7 +1401,7 @@
         <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S4" t="n">
         <v>1.99</v>
@@ -1422,16 +1422,16 @@
         <v>36</v>
       </c>
       <c r="Y4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="n">
-        <v>95</v>
+        <v>220</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC4" t="n">
         <v>12.5</v>
@@ -1440,10 +1440,10 @@
         <v>25</v>
       </c>
       <c r="AE4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
@@ -1452,19 +1452,19 @@
         <v>15.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK4" t="n">
         <v>16.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN4" t="n">
         <v>6.4</v>
@@ -1473,7 +1473,7 @@
         <v>30</v>
       </c>
       <c r="AP4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AQ4" t="n">
         <v>19.5</v>
@@ -1491,13 +1491,13 @@
         <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW4" t="n">
         <v>23</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
         <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH4" t="n">
         <v>5.3</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -1619,46 +1619,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2.84</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.92</v>
       </c>
       <c r="R5" t="n">
         <v>1.15</v>
       </c>
       <c r="S5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T5" t="n">
         <v>2.32</v>
@@ -1667,13 +1667,13 @@
         <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W5" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="X5" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="Y5" t="n">
         <v>12.5</v>
@@ -1682,55 +1682,55 @@
         <v>40</v>
       </c>
       <c r="AA5" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
         <v>25</v>
       </c>
       <c r="AE5" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK5" t="n">
         <v>34</v>
       </c>
-      <c r="AI5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>40</v>
-      </c>
       <c r="AL5" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AO5" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.2</v>
+        <v>3.85</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="AR5" t="n">
         <v>1.03</v>
@@ -1739,22 +1739,22 @@
         <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
         <v>1.03</v>
@@ -1763,7 +1763,7 @@
         <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
         <v>1.03</v>
@@ -1775,22 +1775,22 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>27</v>
+        <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>130</v>
+        <v>2.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="BJ5" t="n">
         <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,50 +1799,50 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BP5" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BQ5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>2.68</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
         <v>2.62</v>
@@ -1921,64 +1921,64 @@
         <v>1.61</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
         <v>1.39</v>
       </c>
       <c r="X6" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
         <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>500</v>
       </c>
       <c r="AE6" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>19.5</v>
+        <v>500</v>
       </c>
       <c r="AH6" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AK6" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
         <v>5.2</v>
@@ -2038,7 +2038,7 @@
         <v>2.54</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
         <v>2.82</v>
       </c>
       <c r="T7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U7" t="n">
         <v>2.34</v>
@@ -2190,7 +2190,7 @@
         <v>34</v>
       </c>
       <c r="AA7" t="n">
-        <v>75</v>
+        <v>440</v>
       </c>
       <c r="AB7" t="n">
         <v>14.5</v>
@@ -2244,7 +2244,7 @@
         <v>19.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
         <v>8.800000000000001</v>
@@ -2256,7 +2256,7 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="AX7" t="n">
         <v>11</v>
@@ -2277,16 +2277,16 @@
         <v>17.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
         <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH7" t="n">
         <v>3.9</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
         <v>3.65</v>
@@ -2399,22 +2399,22 @@
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O8" t="n">
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R8" t="n">
         <v>1.53</v>
@@ -2426,7 +2426,7 @@
         <v>1.62</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V8" t="n">
         <v>1.37</v>
@@ -2435,16 +2435,16 @@
         <v>1.87</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
         <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
         <v>13</v>
@@ -2462,7 +2462,7 @@
         <v>15.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
         <v>16</v>
@@ -2480,7 +2480,7 @@
         <v>50</v>
       </c>
       <c r="AM8" t="n">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AN8" t="n">
         <v>12</v>
@@ -2489,10 +2489,10 @@
         <v>32</v>
       </c>
       <c r="AP8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR8" t="n">
         <v>19.5</v>
@@ -2519,13 +2519,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA8" t="n">
         <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC8" t="n">
         <v>18</v>
@@ -2540,7 +2540,7 @@
         <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH8" t="n">
         <v>4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -2674,13 +2674,13 @@
         <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V9" t="n">
         <v>1.09</v>
@@ -2689,10 +2689,10 @@
         <v>2.8</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2704,10 +2704,10 @@
         <v>5.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="AD9" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2716,37 +2716,37 @@
         <v>7.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="AH9" t="n">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>500</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR9" t="n">
         <v>1.03</v>
@@ -2758,16 +2758,16 @@
         <v>4.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW9" t="n">
         <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AY9" t="n">
         <v>1.03</v>
@@ -2779,7 +2779,7 @@
         <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC9" t="n">
         <v>16.5</v>
@@ -2794,7 +2794,7 @@
         <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH9" t="n">
         <v>2.96</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -2943,58 +2943,58 @@
         <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="Z10" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
         <v>7.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AE10" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>15.5</v>
+        <v>500</v>
       </c>
       <c r="AG10" t="n">
-        <v>13.5</v>
+        <v>500</v>
       </c>
       <c r="AH10" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AI10" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AP10" t="n">
         <v>5.7</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="G11" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.29</v>
+        <v>1.96</v>
       </c>
       <c r="O11" t="n">
         <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Q11" t="n">
         <v>2.46</v>
@@ -3191,67 +3191,67 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="W11" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.03</v>
@@ -3263,10 +3263,10 @@
         <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV11" t="n">
         <v>1.03</v>
@@ -3275,7 +3275,7 @@
         <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY11" t="n">
         <v>1.03</v>
@@ -3299,10 +3299,10 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>2.86</v>
       </c>
       <c r="G12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
         <v>2.96</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J12" t="n">
         <v>2.68</v>
@@ -3415,7 +3415,7 @@
         <v>3.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="M12" t="n">
         <v>1.16</v>
@@ -3445,13 +3445,13 @@
         <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X12" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="Y12" t="n">
         <v>8.199999999999999</v>
@@ -3472,31 +3472,31 @@
         <v>18</v>
       </c>
       <c r="AE12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG12" t="n">
         <v>16</v>
       </c>
       <c r="AH12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI12" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AJ12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL12" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AM12" t="n">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="AN12" t="n">
         <v>90</v>
@@ -3505,10 +3505,10 @@
         <v>95</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR12" t="n">
         <v>1.03</v>
@@ -3520,7 +3520,7 @@
         <v>6.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AV12" t="n">
         <v>1.03</v>
@@ -3544,7 +3544,7 @@
         <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>1.03</v>
@@ -3553,7 +3553,7 @@
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>55</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
         <v>65</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>3.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
         <v>1.16</v>
@@ -3750,7 +3750,7 @@
         <v>120</v>
       </c>
       <c r="AM13" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
         <v>110</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -3905,118 +3905,118 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="G14" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="H14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="T14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="X14" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
         <v>19</v>
       </c>
       <c r="Z14" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE14" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AI14" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AJ14" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AR14" t="n">
         <v>1.03</v>
@@ -4025,13 +4025,13 @@
         <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW14" t="n">
         <v>1.03</v>
@@ -4040,19 +4040,19 @@
         <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BA14" t="n">
         <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD14" t="n">
         <v>1.03</v>
@@ -4061,10 +4061,10 @@
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
         <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AB15" t="n">
         <v>7.4</v>
@@ -4234,7 +4234,7 @@
         <v>20</v>
       </c>
       <c r="AE15" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AF15" t="n">
         <v>13</v>
@@ -4246,7 +4246,7 @@
         <v>26</v>
       </c>
       <c r="AI15" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
         <v>34</v>
@@ -4258,73 +4258,73 @@
         <v>70</v>
       </c>
       <c r="AM15" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN15" t="n">
         <v>38</v>
       </c>
       <c r="AO15" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AP15" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BH15" t="n">
         <v>2.76</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="BJ15" t="n">
         <v>12</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>1.72</v>
       </c>
       <c r="G16" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H16" t="n">
         <v>5.4</v>
@@ -4437,7 +4437,7 @@
         <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O16" t="n">
         <v>1.46</v>
@@ -4446,16 +4446,16 @@
         <v>1.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R16" t="n">
         <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U16" t="n">
         <v>1.68</v>
@@ -4464,10 +4464,10 @@
         <v>1.17</v>
       </c>
       <c r="W16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y16" t="n">
         <v>16.5</v>
@@ -4476,7 +4476,7 @@
         <v>50</v>
       </c>
       <c r="AA16" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AB16" t="n">
         <v>6.8</v>
@@ -4488,7 +4488,7 @@
         <v>26</v>
       </c>
       <c r="AE16" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF16" t="n">
         <v>10.5</v>
@@ -4500,25 +4500,25 @@
         <v>28</v>
       </c>
       <c r="AI16" t="n">
-        <v>150</v>
+        <v>540</v>
       </c>
       <c r="AJ16" t="n">
         <v>21</v>
       </c>
       <c r="AK16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
         <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN16" t="n">
         <v>19.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AP16" t="n">
         <v>7.6</v>
@@ -4527,7 +4527,7 @@
         <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS16" t="n">
         <v>1.03</v>
@@ -4539,25 +4539,25 @@
         <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AW16" t="n">
         <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BC16" t="n">
         <v>19.5</v>
@@ -4566,16 +4566,16 @@
         <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI16" t="n">
         <v>2.38</v>
@@ -4593,13 +4593,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ16" t="n">
         <v>10.5</v>
@@ -4611,7 +4611,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU16" t="n">
         <v>6.2</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
         <v>5.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="U17" t="n">
         <v>1.5</v>
@@ -4739,7 +4739,7 @@
         <v>9.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AE17" t="n">
         <v>310</v>
@@ -4787,7 +4787,7 @@
         <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AU17" t="n">
         <v>6.8</v>
@@ -4826,7 +4826,7 @@
         <v>13</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH17" t="n">
         <v>2.74</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -4975,58 +4975,58 @@
         <v>1.71</v>
       </c>
       <c r="X18" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="Y18" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="Z18" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AA18" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AB18" t="n">
-        <v>16.5</v>
+        <v>500</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AD18" t="n">
-        <v>16.5</v>
+        <v>500</v>
       </c>
       <c r="AE18" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AF18" t="n">
-        <v>18.5</v>
+        <v>500</v>
       </c>
       <c r="AG18" t="n">
         <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>17.5</v>
+        <v>500</v>
       </c>
       <c r="AI18" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AJ18" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AL18" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AM18" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AN18" t="n">
         <v>14</v>
       </c>
       <c r="AO18" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AP18" t="n">
         <v>1.03</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -5196,10 +5196,10 @@
         <v>1.29</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.2</v>
@@ -5220,7 +5220,7 @@
         <v>1.66</v>
       </c>
       <c r="U19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V19" t="n">
         <v>1.2</v>
@@ -5229,16 +5229,16 @@
         <v>2.36</v>
       </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="Y19" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="Z19" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AB19" t="n">
         <v>12</v>
@@ -5250,10 +5250,10 @@
         <v>22</v>
       </c>
       <c r="AE19" t="n">
-        <v>65</v>
+        <v>700</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG19" t="n">
         <v>10</v>
@@ -5262,7 +5262,7 @@
         <v>19</v>
       </c>
       <c r="AI19" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AJ19" t="n">
         <v>18</v>
@@ -5271,16 +5271,16 @@
         <v>17</v>
       </c>
       <c r="AL19" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AN19" t="n">
         <v>7.8</v>
       </c>
       <c r="AO19" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AP19" t="n">
         <v>19.5</v>
@@ -5292,7 +5292,7 @@
         <v>36</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -5304,7 +5304,7 @@
         <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX19" t="n">
         <v>10</v>
@@ -5316,7 +5316,7 @@
         <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB19" t="n">
         <v>14.5</v>
@@ -5325,16 +5325,16 @@
         <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF19" t="n">
         <v>5.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH19" t="n">
         <v>4.4</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
         <v>46</v>
       </c>
       <c r="AM20" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AN20" t="n">
         <v>28</v>
@@ -5546,7 +5546,7 @@
         <v>14</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
@@ -5570,13 +5570,13 @@
         <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BB20" t="n">
         <v>34</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD20" t="n">
         <v>1.03</v>
@@ -5594,7 +5594,7 @@
         <v>3.65</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.199999999999999</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="G21" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="H21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J21" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="K21" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.34</v>
@@ -5707,19 +5707,19 @@
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
         <v>2.88</v>
@@ -5728,40 +5728,40 @@
         <v>2.16</v>
       </c>
       <c r="U21" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W21" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="X21" t="n">
         <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="Z21" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA21" t="n">
-        <v>580</v>
+        <v>710</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC21" t="n">
         <v>14</v>
       </c>
       <c r="AD21" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AE21" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AF21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG21" t="n">
         <v>11.5</v>
@@ -5770,7 +5770,7 @@
         <v>32</v>
       </c>
       <c r="AI21" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="AJ21" t="n">
         <v>11.5</v>
@@ -5779,16 +5779,16 @@
         <v>17</v>
       </c>
       <c r="AL21" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM21" t="n">
         <v>220</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO21" t="n">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="AP21" t="n">
         <v>17</v>
@@ -5803,7 +5803,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU21" t="n">
         <v>11</v>
@@ -5833,13 +5833,13 @@
         <v>13.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE21" t="n">
         <v>9.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG21" t="n">
         <v>9.800000000000001</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
         <v>2.6</v>
       </c>
       <c r="H22" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I22" t="n">
         <v>3.15</v>
@@ -5952,7 +5952,7 @@
         <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
         <v>1.35</v>
@@ -5994,16 +5994,16 @@
         <v>18</v>
       </c>
       <c r="Y22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z22" t="n">
         <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AB22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC22" t="n">
         <v>8.800000000000001</v>
@@ -6024,22 +6024,22 @@
         <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
         <v>38</v>
       </c>
       <c r="AK22" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AL22" t="n">
         <v>40</v>
       </c>
       <c r="AM22" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>19.5</v>
+        <v>500</v>
       </c>
       <c r="AO22" t="n">
         <v>27</v>
@@ -6054,7 +6054,7 @@
         <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="AT22" t="n">
         <v>9.199999999999999</v>
@@ -6078,19 +6078,19 @@
         <v>12.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>26</v>
+        <v>7.4</v>
       </c>
       <c r="BC22" t="n">
         <v>19.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BF22" t="n">
         <v>14</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H23" t="n">
         <v>4.1</v>
@@ -6278,7 +6278,7 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="n">
         <v>29</v>
@@ -6305,7 +6305,7 @@
         <v>10.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AS23" t="n">
         <v>4.1</v>
@@ -6320,7 +6320,7 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX23" t="n">
         <v>9</v>
@@ -6344,13 +6344,13 @@
         <v>3.95</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF23" t="n">
         <v>11.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH23" t="n">
         <v>3.35</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G24" t="n">
         <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I24" t="n">
         <v>1.73</v>
       </c>
       <c r="J24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
         <v>4.3</v>
@@ -6469,28 +6469,28 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="P24" t="n">
         <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="U24" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="V24" t="n">
         <v>2.36</v>
@@ -6499,19 +6499,19 @@
         <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA24" t="n">
         <v>970</v>
       </c>
       <c r="AB24" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AC24" t="n">
         <v>9.6</v>
@@ -6520,52 +6520,52 @@
         <v>12.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AG24" t="n">
         <v>25</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AI24" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AJ24" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AK24" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AL24" t="n">
-        <v>85</v>
+        <v>700</v>
       </c>
       <c r="AM24" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AN24" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AO24" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AR24" t="n">
         <v>9</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AU24" t="n">
         <v>7.8</v>
@@ -6574,43 +6574,43 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AY24" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH24" t="n">
         <v>3.8</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="BJ24" t="n">
         <v>11</v>
@@ -6646,7 +6646,7 @@
         <v>4.4</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BV24" t="n">
         <v>11</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6753,7 @@
         <v>1.22</v>
       </c>
       <c r="X25" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="Y25" t="n">
         <v>17.5</v>
@@ -6810,55 +6810,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS25" t="n">
         <v>13</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AT25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY25" t="n">
         <v>15.5</v>
       </c>
-      <c r="AT25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>19</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BA25" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BB25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BD25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE25" t="n">
         <v>9.6</v>
       </c>
-      <c r="BE25" t="n">
-        <v>10</v>
-      </c>
       <c r="BF25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BH25" t="n">
         <v>5.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>3.75</v>
       </c>
       <c r="K26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.23</v>
@@ -6989,10 +6989,10 @@
         <v>1.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S26" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T26" t="n">
         <v>1.48</v>
@@ -7022,7 +7022,7 @@
         <v>20</v>
       </c>
       <c r="AC26" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD26" t="n">
         <v>16.5</v>
@@ -7037,7 +7037,7 @@
         <v>14.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI26" t="n">
         <v>38</v>
@@ -7052,7 +7052,7 @@
         <v>34</v>
       </c>
       <c r="AM26" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AN26" t="n">
         <v>16</v>
@@ -7070,7 +7070,7 @@
         <v>16.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT26" t="n">
         <v>12</v>
@@ -7094,10 +7094,10 @@
         <v>10.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC26" t="n">
         <v>17</v>
@@ -7106,7 +7106,7 @@
         <v>19.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BF26" t="n">
         <v>9.800000000000001</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G27" t="n">
         <v>4.5</v>
       </c>
       <c r="H27" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I27" t="n">
         <v>1.92</v>
@@ -7240,13 +7240,13 @@
         <v>2.92</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R27" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S27" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="T27" t="n">
         <v>1.49</v>
@@ -7261,7 +7261,7 @@
         <v>1.28</v>
       </c>
       <c r="X27" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="Y27" t="n">
         <v>970</v>
@@ -7270,10 +7270,10 @@
         <v>970</v>
       </c>
       <c r="AA27" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AB27" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AC27" t="n">
         <v>970</v>
@@ -7285,88 +7285,88 @@
         <v>970</v>
       </c>
       <c r="AF27" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AG27" t="n">
-        <v>18.5</v>
+        <v>500</v>
       </c>
       <c r="AH27" t="n">
         <v>970</v>
       </c>
       <c r="AI27" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AJ27" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AK27" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AL27" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AM27" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AN27" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AO27" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS27" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AU27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV27" t="n">
         <v>5</v>
       </c>
-      <c r="AV27" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AW27" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BC27" t="n">
         <v>3.85</v>
       </c>
-      <c r="AY27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BD27" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="BG27" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH27" t="n">
         <v>5.3</v>
@@ -7375,7 +7375,7 @@
         <v>4</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK27" t="n">
         <v>6.6</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G28" t="n">
         <v>1.65</v>
       </c>
       <c r="H28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I28" t="n">
         <v>6.2</v>
@@ -7476,67 +7476,67 @@
         <v>4.3</v>
       </c>
       <c r="K28" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N28" t="n">
         <v>4.6</v>
       </c>
       <c r="O28" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="R28" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U28" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V28" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W28" t="n">
         <v>2.56</v>
       </c>
       <c r="X28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z28" t="n">
         <v>55</v>
       </c>
       <c r="AA28" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AB28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC28" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE28" t="n">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AF28" t="n">
         <v>13</v>
@@ -7548,10 +7548,10 @@
         <v>22</v>
       </c>
       <c r="AI28" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AK28" t="n">
         <v>18.5</v>
@@ -7563,7 +7563,7 @@
         <v>100</v>
       </c>
       <c r="AN28" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO28" t="n">
         <v>75</v>
@@ -7575,22 +7575,22 @@
         <v>18</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT28" t="n">
         <v>9</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV28" t="n">
         <v>17</v>
       </c>
       <c r="AW28" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX28" t="n">
         <v>8.6</v>
@@ -7602,7 +7602,7 @@
         <v>14.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB28" t="n">
         <v>12.5</v>
@@ -7611,34 +7611,34 @@
         <v>12</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE28" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH28" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ28" t="n">
         <v>10</v>
       </c>
       <c r="BK28" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN28" t="n">
         <v>4.6</v>
@@ -7647,44 +7647,44 @@
         <v>3.9</v>
       </c>
       <c r="BP28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BQ28" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BR28" t="n">
         <v>23</v>
       </c>
       <c r="BS28" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW28" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BX28" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CA28" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -7718,19 +7718,19 @@
         <v>3.45</v>
       </c>
       <c r="G29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H29" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="I29" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="J29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K29" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L29" t="n">
         <v>1.11</v>
@@ -7739,37 +7739,37 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O29" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P29" t="n">
         <v>3.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="R29" t="n">
         <v>2.88</v>
       </c>
       <c r="S29" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T29" t="n">
         <v>1.24</v>
       </c>
       <c r="U29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="V29" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W29" t="n">
         <v>1.33</v>
       </c>
       <c r="X29" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="Y29" t="n">
         <v>46</v>
@@ -7793,7 +7793,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AG29" t="n">
         <v>27</v>
@@ -7805,7 +7805,7 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AK29" t="n">
         <v>42</v>
@@ -7817,10 +7817,10 @@
         <v>32</v>
       </c>
       <c r="AN29" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AP29" t="n">
         <v>1.03</v>
@@ -7877,10 +7877,10 @@
         <v>3.2</v>
       </c>
       <c r="BH29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BI29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BJ29" t="n">
         <v>8.6</v>
@@ -7895,10 +7895,10 @@
         <v>24</v>
       </c>
       <c r="BN29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BO29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BP29" t="n">
         <v>25</v>
@@ -7907,38 +7907,38 @@
         <v>17</v>
       </c>
       <c r="BR29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BT29" t="n">
         <v>7.4</v>
       </c>
       <c r="BU29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV29" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BX29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BY29" t="n">
         <v>10</v>
       </c>
       <c r="BZ29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CA29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -8002,13 +8002,13 @@
         <v>1.57</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R30" t="n">
         <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="T30" t="n">
         <v>2.26</v>
@@ -8029,10 +8029,10 @@
         <v>13.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AA30" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AB30" t="n">
         <v>6.4</v>
@@ -8041,10 +8041,10 @@
         <v>8.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AE30" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF30" t="n">
         <v>10</v>
@@ -8053,28 +8053,28 @@
         <v>11.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AI30" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AJ30" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AK30" t="n">
         <v>26</v>
       </c>
       <c r="AL30" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM30" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AN30" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AO30" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AP30" t="n">
         <v>8.4</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
         <v>1.36</v>
       </c>
       <c r="X31" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="Y31" t="n">
         <v>10.5</v>
@@ -8286,7 +8286,7 @@
         <v>16</v>
       </c>
       <c r="AA31" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AB31" t="n">
         <v>13.5</v>
@@ -8298,91 +8298,91 @@
         <v>13</v>
       </c>
       <c r="AE31" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AG31" t="n">
         <v>970</v>
       </c>
       <c r="AH31" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AI31" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AJ31" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AK31" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL31" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM31" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN31" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AO31" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AR31" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>4.4</v>
       </c>
-      <c r="AY31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BA31" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF31" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF31" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG31" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH31" t="n">
         <v>3.3</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
         <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -8731,28 +8731,28 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="G33" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="H33" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I33" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K33" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="L33" t="n">
         <v>1.49</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N33" t="n">
         <v>3.1</v>
@@ -8773,22 +8773,22 @@
         <v>4.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U33" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V33" t="n">
         <v>1.2</v>
       </c>
       <c r="W33" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="X33" t="n">
         <v>970</v>
       </c>
       <c r="Y33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z33" t="n">
         <v>55</v>
@@ -8800,10 +8800,10 @@
         <v>7</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE33" t="n">
         <v>120</v>
@@ -8815,16 +8815,16 @@
         <v>970</v>
       </c>
       <c r="AH33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI33" t="n">
         <v>130</v>
       </c>
       <c r="AJ33" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL33" t="n">
         <v>60</v>
@@ -8833,7 +8833,7 @@
         <v>210</v>
       </c>
       <c r="AN33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO33" t="n">
         <v>180</v>
@@ -8842,28 +8842,28 @@
         <v>10</v>
       </c>
       <c r="AQ33" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR33" t="n">
         <v>34</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="AT33" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="AV33" t="n">
         <v>19</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.32</v>
+        <v>5.2</v>
       </c>
       <c r="AX33" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY33" t="n">
         <v>9.199999999999999</v>
@@ -8872,25 +8872,25 @@
         <v>21</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="BB33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC33" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC33" t="n">
-        <v>9</v>
-      </c>
       <c r="BD33" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="BF33" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG33" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="BH33" t="n">
         <v>3</v>
@@ -8911,16 +8911,16 @@
         <v>21</v>
       </c>
       <c r="BN33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BP33" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ33" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
@@ -8929,10 +8929,10 @@
         <v>24</v>
       </c>
       <c r="BT33" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BU33" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="G34" t="n">
         <v>3.1</v>
@@ -9000,7 +9000,7 @@
         <v>3.1</v>
       </c>
       <c r="K34" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9015,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -860,16 +860,16 @@
         <v>1.98</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
@@ -881,7 +881,7 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
         <v>1.36</v>
@@ -899,16 +899,16 @@
         <v>3.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
         <v>2.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X2" t="n">
         <v>14</v>
@@ -917,64 +917,64 @@
         <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AF2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
         <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.2</v>
+        <v>60</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
@@ -983,40 +983,40 @@
         <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AX2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AY2" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="BB2" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BC2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.7</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="BH2" t="n">
         <v>3.35</v>
@@ -1061,7 +1061,7 @@
         <v>4.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW2" t="n">
         <v>8.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K3" t="n">
         <v>4.2</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1144,40 +1144,40 @@
         <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="T3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V3" t="n">
         <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
         <v>19</v>
       </c>
       <c r="Z3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
         <v>9</v>
@@ -1186,49 +1186,49 @@
         <v>17</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AK3" t="n">
         <v>20</v>
       </c>
       <c r="AL3" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>240</v>
+        <v>46</v>
       </c>
       <c r="AP3" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="AT3" t="n">
         <v>9.6</v>
@@ -1240,16 +1240,16 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="AX3" t="n">
         <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
         <v>40</v>
@@ -1258,13 +1258,13 @@
         <v>20</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BF3" t="n">
         <v>10</v>
@@ -1273,68 +1273,68 @@
         <v>34</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>3.05</v>
       </c>
       <c r="BN3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>2.92</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="G4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H4" t="n">
         <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J4" t="n">
         <v>4.4</v>
@@ -1395,25 +1395,25 @@
         <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q4" t="n">
         <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S4" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="T4" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W4" t="n">
         <v>2.16</v>
@@ -1425,61 +1425,61 @@
         <v>36</v>
       </c>
       <c r="Z4" t="n">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="AA4" t="n">
         <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AC4" t="n">
         <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AM4" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AP4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>26</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AS4" t="n">
         <v>36</v>
@@ -1491,58 +1491,58 @@
         <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AX4" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
         <v>25</v>
       </c>
       <c r="BB4" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BC4" t="n">
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BE4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN4" t="n">
         <v>5.4</v>
@@ -1554,19 +1554,19 @@
         <v>11.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
         <v>18</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
         <v>10.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>5.7</v>
       </c>
       <c r="J5" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K5" t="n">
         <v>3.25</v>
@@ -1652,7 +1652,7 @@
         <v>1.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R5" t="n">
         <v>1.15</v>
@@ -1682,7 +1682,7 @@
         <v>40</v>
       </c>
       <c r="AA5" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
         <v>6.4</v>
@@ -1697,7 +1697,7 @@
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
@@ -1727,16 +1727,16 @@
         <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT5" t="n">
         <v>5.2</v>
@@ -1745,40 +1745,40 @@
         <v>4.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AX5" t="n">
         <v>5.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
         <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="BH5" t="n">
         <v>2.62</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G6" t="n">
         <v>3.6</v>
@@ -1927,10 +1927,10 @@
         <v>1.39</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="Z6" t="n">
         <v>500</v>
@@ -1939,10 +1939,10 @@
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="AD6" t="n">
         <v>500</v>
@@ -1960,7 +1960,7 @@
         <v>500</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ6" t="n">
         <v>500</v>
@@ -1969,13 +1969,13 @@
         <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>500</v>
@@ -1984,13 +1984,13 @@
         <v>5.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
@@ -2002,37 +2002,37 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY6" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>60</v>
+        <v>6.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>50</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="n">
         <v>2.54</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="G7" t="n">
         <v>2.28</v>
@@ -2136,7 +2136,7 @@
         <v>3.35</v>
       </c>
       <c r="I7" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J7" t="n">
         <v>3.65</v>
@@ -2157,7 +2157,7 @@
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
         <v>1.72</v>
@@ -2175,7 +2175,7 @@
         <v>2.34</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
         <v>1.79</v>
@@ -2190,7 +2190,7 @@
         <v>34</v>
       </c>
       <c r="AA7" t="n">
-        <v>440</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>14.5</v>
@@ -2280,7 +2280,7 @@
         <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF7" t="n">
         <v>11.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -2393,13 +2393,13 @@
         <v>3.65</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -2408,7 +2408,7 @@
         <v>5.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
         <v>2.36</v>
@@ -2420,19 +2420,19 @@
         <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T8" t="n">
         <v>1.62</v>
       </c>
       <c r="U8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
         <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X8" t="n">
         <v>21</v>
@@ -2444,10 +2444,10 @@
         <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC8" t="n">
         <v>9.199999999999999</v>
@@ -2465,7 +2465,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI8" t="n">
         <v>46</v>
@@ -2543,25 +2543,25 @@
         <v>19.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ8" t="n">
         <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO8" t="n">
         <v>4.7</v>
@@ -2570,13 +2570,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT8" t="n">
         <v>7</v>
@@ -2588,13 +2588,13 @@
         <v>26</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -2647,40 +2647,40 @@
         <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="O9" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
         <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
         <v>1.09</v>
@@ -2689,7 +2689,7 @@
         <v>2.8</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Y9" t="n">
         <v>44</v>
@@ -2728,7 +2728,7 @@
         <v>500</v>
       </c>
       <c r="AK9" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AL9" t="n">
         <v>500</v>
@@ -2737,7 +2737,7 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
@@ -2755,7 +2755,7 @@
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU9" t="n">
         <v>5.6</v>
@@ -2794,25 +2794,25 @@
         <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="BN9" t="n">
         <v>3.75</v>
@@ -2821,7 +2821,7 @@
         <v>2.92</v>
       </c>
       <c r="BP9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
         <v>8</v>
@@ -2830,35 +2830,35 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>21</v>
+        <v>3.8</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>21</v>
+        <v>3.65</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
         <v>3.5</v>
@@ -2904,7 +2904,7 @@
         <v>2.68</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.58</v>
@@ -2940,7 +2940,7 @@
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="X10" t="n">
         <v>14.5</v>
@@ -2952,10 +2952,10 @@
         <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC10" t="n">
         <v>14</v>
@@ -2979,7 +2979,7 @@
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
@@ -3033,7 +3033,7 @@
         <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BC10" t="n">
         <v>1.03</v>
@@ -3045,10 +3045,10 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.55</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.55</v>
       </c>
       <c r="BH10" t="n">
         <v>2.7</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="G11" t="n">
         <v>2.4</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J11" t="n">
         <v>2.46</v>
       </c>
       <c r="K11" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3170,7 +3170,7 @@
         <v>1.96</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P11" t="n">
         <v>1.28</v>
@@ -3185,7 +3185,7 @@
         <v>2.46</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U11" t="n">
         <v>1.01</v>
@@ -3206,13 +3206,13 @@
         <v>500</v>
       </c>
       <c r="AA11" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
         <v>500</v>
       </c>
       <c r="AC11" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AD11" t="n">
         <v>500</v>
@@ -3233,7 +3233,7 @@
         <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
         <v>500</v>
@@ -3302,7 +3302,7 @@
         <v>5.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.38</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="I12" t="n">
         <v>3.35</v>
@@ -3511,10 +3511,10 @@
         <v>4.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT12" t="n">
         <v>6.6</v>
@@ -3523,40 +3523,40 @@
         <v>5.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AY12" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BC12" t="n">
         <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BG12" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="BH12" t="n">
         <v>2.52</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -3654,16 +3654,16 @@
         <v>3.1</v>
       </c>
       <c r="G13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I13" t="n">
         <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K13" t="n">
         <v>3.1</v>
@@ -3684,7 +3684,7 @@
         <v>1.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R13" t="n">
         <v>1.14</v>
@@ -3702,7 +3702,7 @@
         <v>1.48</v>
       </c>
       <c r="W13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X13" t="n">
         <v>7.6</v>
@@ -3711,7 +3711,7 @@
         <v>7.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA13" t="n">
         <v>55</v>
@@ -3738,7 +3738,7 @@
         <v>28</v>
       </c>
       <c r="AI13" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AJ13" t="n">
         <v>80</v>
@@ -3747,7 +3747,7 @@
         <v>65</v>
       </c>
       <c r="AL13" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
@@ -3807,10 +3807,10 @@
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>75</v>
+        <v>1.55</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.55</v>
       </c>
       <c r="BH13" t="n">
         <v>2.52</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
         <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.4</v>
@@ -3959,16 +3959,16 @@
         <v>2.18</v>
       </c>
       <c r="X14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="n">
         <v>19</v>
       </c>
       <c r="Z14" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AA14" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
         <v>8.199999999999999</v>
@@ -3989,19 +3989,19 @@
         <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AI14" t="n">
-        <v>700</v>
+        <v>540</v>
       </c>
       <c r="AJ14" t="n">
         <v>18.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AL14" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM14" t="n">
         <v>500</v>
@@ -4019,10 +4019,10 @@
         <v>12.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
@@ -4034,10 +4034,10 @@
         <v>19</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY14" t="n">
         <v>9.4</v>
@@ -4046,7 +4046,7 @@
         <v>17.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB14" t="n">
         <v>13.5</v>
@@ -4055,16 +4055,16 @@
         <v>16</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF14" t="n">
         <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>24</v>
+        <v>6.8</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
         <v>1.72</v>
       </c>
       <c r="V15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
         <v>1.71</v>
@@ -4216,13 +4216,13 @@
         <v>10</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" t="n">
         <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
         <v>7.4</v>
@@ -4231,7 +4231,7 @@
         <v>7.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE15" t="n">
         <v>500</v>
@@ -4252,10 +4252,10 @@
         <v>34</v>
       </c>
       <c r="AK15" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL15" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
@@ -4273,52 +4273,52 @@
         <v>4.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW15" t="n">
         <v>7</v>
       </c>
-      <c r="AT15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AX15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD15" t="n">
         <v>7</v>
       </c>
-      <c r="BB15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH15" t="n">
         <v>2.76</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
         <v>50</v>
       </c>
       <c r="AA16" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
         <v>6.8</v>
@@ -4500,7 +4500,7 @@
         <v>28</v>
       </c>
       <c r="AI16" t="n">
-        <v>540</v>
+        <v>700</v>
       </c>
       <c r="AJ16" t="n">
         <v>21</v>
@@ -4512,7 +4512,7 @@
         <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
         <v>19.5</v>
@@ -4524,13 +4524,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AR16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT16" t="n">
         <v>5.4</v>
@@ -4542,7 +4542,7 @@
         <v>20</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AX16" t="n">
         <v>4.9</v>
@@ -4563,16 +4563,16 @@
         <v>19.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH16" t="n">
         <v>2.96</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="G17" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I17" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
         <v>1.57</v>
@@ -4691,7 +4691,7 @@
         <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O17" t="n">
         <v>1.57</v>
@@ -4712,37 +4712,37 @@
         <v>2.64</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V17" t="n">
         <v>1.11</v>
       </c>
       <c r="W17" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="X17" t="n">
         <v>10</v>
       </c>
       <c r="Y17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AA17" t="n">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="AB17" t="n">
         <v>6.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AE17" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AF17" t="n">
         <v>8</v>
@@ -4751,10 +4751,10 @@
         <v>14.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AI17" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AJ17" t="n">
         <v>17</v>
@@ -4763,10 +4763,10 @@
         <v>27</v>
       </c>
       <c r="AL17" t="n">
-        <v>100</v>
+        <v>540</v>
       </c>
       <c r="AM17" t="n">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="AN17" t="n">
         <v>22</v>
@@ -4781,34 +4781,34 @@
         <v>13</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AU17" t="n">
         <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AY17" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB17" t="n">
         <v>11.5</v>
@@ -4817,16 +4817,16 @@
         <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
         <v>13</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BH17" t="n">
         <v>2.74</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
         <v>2.4</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I18" t="n">
         <v>3.45</v>
@@ -4954,7 +4954,7 @@
         <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="R18" t="n">
         <v>1.55</v>
@@ -4984,13 +4984,13 @@
         <v>500</v>
       </c>
       <c r="AA18" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
         <v>500</v>
       </c>
       <c r="AC18" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD18" t="n">
         <v>500</v>
@@ -5002,37 +5002,37 @@
         <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI18" t="n">
         <v>500</v>
       </c>
       <c r="AJ18" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL18" t="n">
         <v>500</v>
       </c>
       <c r="AM18" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AO18" t="n">
         <v>500</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
         <v>1.03</v>
@@ -5041,25 +5041,25 @@
         <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU18" t="n">
         <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AW18" t="n">
         <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AY18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BA18" t="n">
         <v>1.03</v>
@@ -5068,7 +5068,7 @@
         <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BD18" t="n">
         <v>1.03</v>
@@ -5080,7 +5080,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG18" t="n">
-        <v>16.5</v>
+        <v>4.1</v>
       </c>
       <c r="BH18" t="n">
         <v>4.4</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G19" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H19" t="n">
         <v>5.2</v>
@@ -5187,19 +5187,19 @@
         <v>5.8</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L19" t="n">
         <v>1.29</v>
       </c>
       <c r="M19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
         <v>1.2</v>
@@ -5208,7 +5208,7 @@
         <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R19" t="n">
         <v>1.54</v>
@@ -5217,7 +5217,7 @@
         <v>2.54</v>
       </c>
       <c r="T19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U19" t="n">
         <v>2.34</v>
@@ -5226,19 +5226,19 @@
         <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X19" t="n">
         <v>40</v>
       </c>
       <c r="Y19" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="Z19" t="n">
         <v>500</v>
       </c>
       <c r="AA19" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
         <v>12</v>
@@ -5274,7 +5274,7 @@
         <v>60</v>
       </c>
       <c r="AM19" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
         <v>7.8</v>
@@ -5292,7 +5292,7 @@
         <v>36</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>2.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
         <v>3.85</v>
@@ -5477,7 +5477,7 @@
         <v>2.26</v>
       </c>
       <c r="V20" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W20" t="n">
         <v>1.51</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -5689,13 +5689,13 @@
         <v>1.34</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="K21" t="n">
         <v>6.2</v>
@@ -5722,7 +5722,7 @@
         <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="T21" t="n">
         <v>2.16</v>
@@ -5734,16 +5734,16 @@
         <v>1.07</v>
       </c>
       <c r="W21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="X21" t="n">
         <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Z21" t="n">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AA21" t="n">
         <v>710</v>
@@ -5782,25 +5782,25 @@
         <v>44</v>
       </c>
       <c r="AM21" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN21" t="n">
         <v>5.7</v>
       </c>
       <c r="AO21" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="AP21" t="n">
         <v>17</v>
       </c>
       <c r="AQ21" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AR21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT21" t="n">
         <v>7.6</v>
@@ -5812,7 +5812,7 @@
         <v>36</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX21" t="n">
         <v>7</v>
@@ -5824,25 +5824,25 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB21" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BC21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF21" t="n">
         <v>5</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BH21" t="n">
         <v>3.95</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L22" t="n">
         <v>1.35</v>
@@ -5964,7 +5964,7 @@
         <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P22" t="n">
         <v>2.06</v>
@@ -5979,28 +5979,28 @@
         <v>3.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U22" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V22" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W22" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y22" t="n">
         <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AA22" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AB22" t="n">
         <v>12.5</v>
@@ -6015,19 +6015,19 @@
         <v>34</v>
       </c>
       <c r="AF22" t="n">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="AG22" t="n">
         <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AJ22" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AK22" t="n">
         <v>500</v>
@@ -6039,7 +6039,7 @@
         <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO22" t="n">
         <v>27</v>
@@ -6078,19 +6078,19 @@
         <v>12.5</v>
       </c>
       <c r="BA22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB22" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>7.4</v>
       </c>
       <c r="BC22" t="n">
         <v>19.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF22" t="n">
         <v>14</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G23" t="n">
         <v>2.1</v>
@@ -6236,7 +6236,7 @@
         <v>1.84</v>
       </c>
       <c r="U23" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V23" t="n">
         <v>1.26</v>
@@ -6278,7 +6278,7 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ23" t="n">
         <v>29</v>
@@ -6290,7 +6290,7 @@
         <v>48</v>
       </c>
       <c r="AM23" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
         <v>19.5</v>
@@ -6305,10 +6305,10 @@
         <v>10.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT23" t="n">
         <v>6.4</v>
@@ -6320,7 +6320,7 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX23" t="n">
         <v>9</v>
@@ -6332,7 +6332,7 @@
         <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB23" t="n">
         <v>17</v>
@@ -6344,13 +6344,13 @@
         <v>3.95</v>
       </c>
       <c r="BE23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG23" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>4</v>
       </c>
       <c r="BH23" t="n">
         <v>3.35</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="G24" t="n">
         <v>6</v>
@@ -6454,10 +6454,10 @@
         <v>1.69</v>
       </c>
       <c r="I24" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K24" t="n">
         <v>4.3</v>
@@ -6478,7 +6478,7 @@
         <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R24" t="n">
         <v>1.4</v>
@@ -6490,34 +6490,34 @@
         <v>1.86</v>
       </c>
       <c r="U24" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="V24" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="W24" t="n">
         <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z24" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AD24" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
         <v>18.5</v>
@@ -6526,7 +6526,7 @@
         <v>500</v>
       </c>
       <c r="AG24" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AH24" t="n">
         <v>60</v>
@@ -6535,7 +6535,7 @@
         <v>500</v>
       </c>
       <c r="AJ24" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AK24" t="n">
         <v>700</v>
@@ -6544,28 +6544,28 @@
         <v>700</v>
       </c>
       <c r="AM24" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AO24" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="AR24" t="n">
         <v>9</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AU24" t="n">
         <v>7.8</v>
@@ -6574,37 +6574,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AX24" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB24" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC24" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH24" t="n">
         <v>3.8</v>
@@ -6616,7 +6616,7 @@
         <v>11</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
@@ -6625,7 +6625,7 @@
         <v>10</v>
       </c>
       <c r="BN24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BO24" t="n">
         <v>5.1</v>
@@ -6634,13 +6634,13 @@
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT24" t="n">
         <v>4.4</v>
@@ -6652,7 +6652,7 @@
         <v>11</v>
       </c>
       <c r="BW24" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
@@ -6664,11 +6664,11 @@
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
         <v>1.59</v>
       </c>
       <c r="I25" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="J25" t="n">
         <v>4.8</v>
@@ -6729,13 +6729,13 @@
         <v>1.12</v>
       </c>
       <c r="P25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q25" t="n">
         <v>1.37</v>
       </c>
       <c r="R25" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S25" t="n">
         <v>1.93</v>
@@ -6744,7 +6744,7 @@
         <v>1.5</v>
       </c>
       <c r="U25" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V25" t="n">
         <v>2.46</v>
@@ -6792,10 +6792,10 @@
         <v>130</v>
       </c>
       <c r="AK25" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AL25" t="n">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="AM25" t="n">
         <v>55</v>
@@ -6807,7 +6807,7 @@
         <v>5.1</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ25" t="n">
         <v>12.5</v>
@@ -6819,10 +6819,10 @@
         <v>13</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="AU25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV25" t="n">
         <v>8.4</v>
@@ -6831,7 +6831,7 @@
         <v>11</v>
       </c>
       <c r="AX25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY25" t="n">
         <v>15.5</v>
@@ -6843,7 +6843,7 @@
         <v>16</v>
       </c>
       <c r="BB25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC25" t="n">
         <v>9.6</v>
@@ -6852,19 +6852,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BH25" t="n">
         <v>5.5</v>
       </c>
       <c r="BI25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ25" t="n">
         <v>9</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G26" t="n">
         <v>2.74</v>
@@ -6962,10 +6962,10 @@
         <v>2.58</v>
       </c>
       <c r="I26" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K26" t="n">
         <v>4.5</v>
@@ -6974,7 +6974,7 @@
         <v>1.23</v>
       </c>
       <c r="M26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N26" t="n">
         <v>5.4</v>
@@ -7007,19 +7007,19 @@
         <v>1.57</v>
       </c>
       <c r="X26" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="Y26" t="n">
         <v>22</v>
       </c>
       <c r="Z26" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AA26" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AB26" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AC26" t="n">
         <v>11</v>
@@ -7028,25 +7028,25 @@
         <v>16.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AF26" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AG26" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
         <v>15.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL26" t="n">
         <v>34</v>
@@ -7055,10 +7055,10 @@
         <v>200</v>
       </c>
       <c r="AN26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO26" t="n">
         <v>16</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>17.5</v>
       </c>
       <c r="AP26" t="n">
         <v>19</v>
@@ -7070,7 +7070,7 @@
         <v>16.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="AT26" t="n">
         <v>12</v>
@@ -7094,10 +7094,10 @@
         <v>10.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="BC26" t="n">
         <v>17</v>
@@ -7106,7 +7106,7 @@
         <v>19.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF26" t="n">
         <v>9.800000000000001</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -7276,10 +7276,10 @@
         <v>500</v>
       </c>
       <c r="AC27" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AD27" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE27" t="n">
         <v>970</v>
@@ -7291,7 +7291,7 @@
         <v>500</v>
       </c>
       <c r="AH27" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI27" t="n">
         <v>500</v>
@@ -7306,7 +7306,7 @@
         <v>500</v>
       </c>
       <c r="AM27" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN27" t="n">
         <v>500</v>
@@ -7315,55 +7315,55 @@
         <v>24</v>
       </c>
       <c r="AP27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF27" t="n">
         <v>5.4</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>3.65</v>
       </c>
       <c r="BG27" t="n">
         <v>5.2</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -7461,19 +7461,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G28" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="H28" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I28" t="n">
         <v>6.2</v>
       </c>
       <c r="J28" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K28" t="n">
         <v>4.8</v>
@@ -7488,7 +7488,7 @@
         <v>4.6</v>
       </c>
       <c r="O28" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
@@ -7509,40 +7509,40 @@
         <v>2.16</v>
       </c>
       <c r="V28" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W28" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="X28" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y28" t="n">
         <v>23</v>
       </c>
-      <c r="Y28" t="n">
-        <v>26</v>
-      </c>
       <c r="Z28" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA28" t="n">
         <v>700</v>
       </c>
       <c r="AB28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC28" t="n">
         <v>10.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE28" t="n">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AF28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH28" t="n">
         <v>22</v>
@@ -7554,10 +7554,10 @@
         <v>17.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM28" t="n">
         <v>100</v>
@@ -7575,10 +7575,10 @@
         <v>18</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="AT28" t="n">
         <v>9</v>
@@ -7590,7 +7590,7 @@
         <v>17</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.5</v>
+        <v>28</v>
       </c>
       <c r="AX28" t="n">
         <v>8.6</v>
@@ -7602,7 +7602,7 @@
         <v>14.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BB28" t="n">
         <v>12.5</v>
@@ -7611,16 +7611,16 @@
         <v>12</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF28" t="n">
         <v>6.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH28" t="n">
         <v>4.2</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -7718,19 +7718,19 @@
         <v>3.45</v>
       </c>
       <c r="G29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H29" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="I29" t="n">
         <v>1.92</v>
       </c>
       <c r="J29" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K29" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="L29" t="n">
         <v>1.11</v>
@@ -7739,7 +7739,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
         <v>1.04</v>
@@ -7763,7 +7763,7 @@
         <v>4.2</v>
       </c>
       <c r="V29" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W29" t="n">
         <v>1.33</v>
@@ -7781,16 +7781,16 @@
         <v>36</v>
       </c>
       <c r="AB29" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AC29" t="n">
         <v>24</v>
       </c>
       <c r="AD29" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF29" t="n">
         <v>500</v>
@@ -7799,19 +7799,19 @@
         <v>27</v>
       </c>
       <c r="AH29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI29" t="n">
         <v>21</v>
       </c>
       <c r="AJ29" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK29" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AL29" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM29" t="n">
         <v>32</v>
@@ -7823,122 +7823,122 @@
         <v>3.95</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>3.2</v>
+        <v>2.52</v>
       </c>
       <c r="BH29" t="n">
         <v>9.6</v>
       </c>
       <c r="BI29" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="BJ29" t="n">
         <v>8.6</v>
       </c>
       <c r="BK29" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>24</v>
+        <v>6.4</v>
       </c>
       <c r="BN29" t="n">
         <v>11</v>
       </c>
       <c r="BO29" t="n">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP29" t="n">
         <v>25</v>
       </c>
       <c r="BQ29" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="BR29" t="n">
         <v>20</v>
       </c>
       <c r="BS29" t="n">
-        <v>14</v>
+        <v>5.7</v>
       </c>
       <c r="BT29" t="n">
         <v>7.4</v>
       </c>
       <c r="BU29" t="n">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="BV29" t="n">
         <v>12</v>
       </c>
       <c r="BW29" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="BX29" t="n">
         <v>14</v>
       </c>
       <c r="BY29" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BZ29" t="n">
         <v>6.4</v>
       </c>
       <c r="CA29" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>1.84</v>
       </c>
       <c r="G30" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H30" t="n">
         <v>5.1</v>
@@ -7981,7 +7981,7 @@
         <v>5.7</v>
       </c>
       <c r="J30" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K30" t="n">
         <v>3.65</v>
@@ -7993,19 +7993,19 @@
         <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O30" t="n">
         <v>1.53</v>
       </c>
       <c r="P30" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S30" t="n">
         <v>5.2</v>
@@ -8014,7 +8014,7 @@
         <v>2.26</v>
       </c>
       <c r="U30" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V30" t="n">
         <v>1.21</v>
@@ -8029,19 +8029,19 @@
         <v>13.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AA30" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB30" t="n">
         <v>6.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AE30" t="n">
         <v>700</v>
@@ -8050,10 +8050,10 @@
         <v>10</v>
       </c>
       <c r="AG30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI30" t="n">
         <v>700</v>
@@ -8062,16 +8062,16 @@
         <v>500</v>
       </c>
       <c r="AK30" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AL30" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM30" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AO30" t="n">
         <v>700</v>
@@ -8083,52 +8083,52 @@
         <v>11.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AS30" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU30" t="n">
         <v>7.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AX30" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BA30" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BB30" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BD30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BE30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BF30" t="n">
         <v>18</v>
       </c>
       <c r="BG30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BH30" t="n">
         <v>2.82</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -8223,13 +8223,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G31" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H31" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I31" t="n">
         <v>2.4</v>
@@ -8238,7 +8238,7 @@
         <v>3.45</v>
       </c>
       <c r="K31" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L31" t="n">
         <v>1.44</v>
@@ -8247,7 +8247,7 @@
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
         <v>1.38</v>
@@ -8256,10 +8256,10 @@
         <v>1.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R31" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -8268,52 +8268,52 @@
         <v>1.86</v>
       </c>
       <c r="U31" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V31" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X31" t="n">
         <v>25</v>
       </c>
       <c r="Y31" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AA31" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB31" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF31" t="n">
         <v>500</v>
       </c>
       <c r="AG31" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH31" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI31" t="n">
         <v>500</v>
       </c>
       <c r="AJ31" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK31" t="n">
         <v>500</v>
@@ -8322,67 +8322,67 @@
         <v>500</v>
       </c>
       <c r="AM31" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN31" t="n">
         <v>500</v>
       </c>
       <c r="AO31" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC31" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH31" t="n">
         <v>3.3</v>
@@ -8406,7 +8406,7 @@
         <v>7.2</v>
       </c>
       <c r="BO31" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
@@ -8427,7 +8427,7 @@
         <v>4.3</v>
       </c>
       <c r="BV31" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW31" t="n">
         <v>6.4</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -8483,16 +8483,16 @@
         <v>2.34</v>
       </c>
       <c r="H32" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I32" t="n">
         <v>4.1</v>
       </c>
       <c r="J32" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K32" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q32" t="n">
         <v>2.02</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8731,22 @@
         </is>
       </c>
       <c r="F33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G33" t="n">
         <v>1.75</v>
       </c>
-      <c r="G33" t="n">
-        <v>1.79</v>
-      </c>
       <c r="H33" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I33" t="n">
         <v>6.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K33" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L33" t="n">
         <v>1.49</v>
@@ -8758,16 +8758,16 @@
         <v>3.1</v>
       </c>
       <c r="O33" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P33" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S33" t="n">
         <v>4.5</v>
@@ -8776,40 +8776,40 @@
         <v>2.16</v>
       </c>
       <c r="U33" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="V33" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W33" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="X33" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Y33" t="n">
         <v>17</v>
       </c>
       <c r="Z33" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA33" t="n">
         <v>200</v>
       </c>
       <c r="AB33" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AE33" t="n">
         <v>120</v>
       </c>
       <c r="AF33" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG33" t="n">
         <v>970</v>
@@ -8821,46 +8821,46 @@
         <v>130</v>
       </c>
       <c r="AJ33" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK33" t="n">
         <v>22</v>
       </c>
       <c r="AL33" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM33" t="n">
         <v>210</v>
       </c>
       <c r="AN33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO33" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AP33" t="n">
         <v>10</v>
       </c>
       <c r="AQ33" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AR33" t="n">
         <v>34</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.66</v>
+        <v>7.2</v>
       </c>
       <c r="AT33" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU33" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AV33" t="n">
         <v>19</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="AX33" t="n">
         <v>7.8</v>
@@ -8869,40 +8869,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.64</v>
+        <v>10.5</v>
       </c>
       <c r="BB33" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC33" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BD33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG33" t="n">
         <v>10.5</v>
       </c>
-      <c r="BE33" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>2.66</v>
-      </c>
       <c r="BH33" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ33" t="n">
         <v>11.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
         <v>3.1</v>
       </c>
       <c r="H34" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I34" t="n">
         <v>3.25</v>
@@ -9015,7 +9015,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="Q34" t="n">
         <v>2.3</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -866,7 +866,7 @@
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
@@ -878,7 +878,7 @@
         <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
         <v>3.55</v>
@@ -887,7 +887,7 @@
         <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
         <v>2.06</v>
@@ -899,13 +899,13 @@
         <v>3.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
         <v>1.92</v>
@@ -914,13 +914,13 @@
         <v>14</v>
       </c>
       <c r="Y2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
         <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AB2" t="n">
         <v>8.800000000000001</v>
@@ -932,10 +932,10 @@
         <v>17.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -944,10 +944,10 @@
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
         <v>23</v>
@@ -965,7 +965,7 @@
         <v>150</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
@@ -974,10 +974,10 @@
         <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
         <v>6.8</v>
@@ -989,7 +989,7 @@
         <v>34</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
         <v>9.800000000000001</v>
@@ -1001,22 +1001,22 @@
         <v>40</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD2" t="n">
         <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BF2" t="n">
         <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH2" t="n">
         <v>3.35</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="G3" t="n">
         <v>2.04</v>
@@ -1120,10 +1120,10 @@
         <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
         <v>4.2</v>
@@ -1147,7 +1147,7 @@
         <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
         <v>2.94</v>
@@ -1156,7 +1156,7 @@
         <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
         <v>1.3</v>
@@ -1168,19 +1168,19 @@
         <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
         <v>40</v>
       </c>
       <c r="AA3" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
         <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>17</v>
@@ -1195,7 +1195,7 @@
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
         <v>65</v>
@@ -1207,10 +1207,10 @@
         <v>20</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN3" t="n">
         <v>11.5</v>
@@ -1222,10 +1222,10 @@
         <v>16</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS3" t="n">
         <v>55</v>
@@ -1252,7 +1252,7 @@
         <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BB3" t="n">
         <v>20</v>
@@ -1261,7 +1261,7 @@
         <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE3" t="n">
         <v>55</v>
@@ -1270,7 +1270,7 @@
         <v>10</v>
       </c>
       <c r="BG3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BH3" t="n">
         <v>3.95</v>
@@ -1282,7 +1282,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>1.79</v>
       </c>
       <c r="G4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H4" t="n">
         <v>4.1</v>
@@ -1377,10 +1377,10 @@
         <v>4.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.22</v>
@@ -1389,19 +1389,19 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="R4" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="S4" t="n">
         <v>1.97</v>
@@ -1410,19 +1410,19 @@
         <v>1.44</v>
       </c>
       <c r="U4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
         <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X4" t="n">
         <v>36</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="Z4" t="n">
         <v>100</v>
@@ -1431,25 +1431,25 @@
         <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AC4" t="n">
         <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AE4" t="n">
         <v>80</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AI4" t="n">
         <v>55</v>
@@ -1458,31 +1458,31 @@
         <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AM4" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AQ4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR4" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AS4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AT4" t="n">
         <v>15.5</v>
@@ -1494,37 +1494,37 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX4" t="n">
         <v>15.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
         <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BF4" t="n">
         <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH4" t="n">
         <v>5.4</v>
@@ -1533,62 +1533,62 @@
         <v>4.9</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN4" t="n">
         <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BP4" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>10.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="G5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
         <v>2.94</v>
@@ -1643,7 +1643,7 @@
         <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
         <v>1.61</v>
@@ -1655,7 +1655,7 @@
         <v>2.86</v>
       </c>
       <c r="R5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S5" t="n">
         <v>6.2</v>
@@ -1667,19 +1667,19 @@
         <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X5" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
         <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
@@ -1691,7 +1691,7 @@
         <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
@@ -1703,7 +1703,7 @@
         <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
@@ -1721,76 +1721,76 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU5" t="n">
         <v>4.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX5" t="n">
         <v>5.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
         <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BJ5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,10 +1802,10 @@
         <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ5" t="n">
         <v>13</v>
@@ -1817,22 +1817,22 @@
         <v>34</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>3.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I6" t="n">
         <v>3.2</v>
@@ -1930,7 +1930,7 @@
         <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
         <v>500</v>
@@ -1939,7 +1939,7 @@
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>15</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>2.18</v>
       </c>
       <c r="G7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H7" t="n">
         <v>3.35</v>
@@ -2139,7 +2139,7 @@
         <v>3.65</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
@@ -2235,13 +2235,13 @@
         <v>38</v>
       </c>
       <c r="AP7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
         <v>5</v>
@@ -2271,7 +2271,7 @@
         <v>34</v>
       </c>
       <c r="BB7" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="BC7" t="n">
         <v>17.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -2399,10 +2399,10 @@
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
         <v>5.1</v>
@@ -2414,19 +2414,19 @@
         <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
         <v>1.62</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V8" t="n">
         <v>1.37</v>
@@ -2435,7 +2435,7 @@
         <v>1.88</v>
       </c>
       <c r="X8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
         <v>18.5</v>
@@ -2489,7 +2489,7 @@
         <v>32</v>
       </c>
       <c r="AP8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ8" t="n">
         <v>15.5</v>
@@ -2498,10 +2498,10 @@
         <v>19.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU8" t="n">
         <v>8.199999999999999</v>
@@ -2534,7 +2534,7 @@
         <v>19.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BF8" t="n">
         <v>10.5</v>
@@ -2570,13 +2570,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR8" t="n">
         <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT8" t="n">
         <v>7</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -2659,13 +2659,13 @@
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="O9" t="n">
         <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q9" t="n">
         <v>2.38</v>
@@ -2743,16 +2743,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS9" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
         <v>4.6</v>
@@ -2761,22 +2761,22 @@
         <v>5.6</v>
       </c>
       <c r="AV9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW9" t="n">
         <v>4.2</v>
       </c>
-      <c r="AW9" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AX9" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB9" t="n">
         <v>6.2</v>
@@ -2785,16 +2785,16 @@
         <v>16.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF9" t="n">
         <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH9" t="n">
         <v>2.98</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G10" t="n">
         <v>2.82</v>
@@ -2901,7 +2901,7 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="K10" t="n">
         <v>3.1</v>
@@ -2934,13 +2934,13 @@
         <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
         <v>14.5</v>
@@ -2955,7 +2955,7 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC10" t="n">
         <v>14</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
         <v>1.96</v>
       </c>
       <c r="O11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P11" t="n">
         <v>1.28</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
         <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC13" t="n">
         <v>7.2</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
         <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
         <v>2.1</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -4165,31 +4165,31 @@
         <v>2.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I15" t="n">
         <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K15" t="n">
         <v>3.35</v>
       </c>
       <c r="L15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O15" t="n">
         <v>1.54</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q15" t="n">
         <v>2.62</v>
@@ -4204,7 +4204,7 @@
         <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V15" t="n">
         <v>1.28</v>
@@ -4219,7 +4219,7 @@
         <v>11.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA15" t="n">
         <v>900</v>
@@ -4231,7 +4231,7 @@
         <v>7.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>500</v>
@@ -4261,70 +4261,70 @@
         <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AO15" t="n">
         <v>500</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AV15" t="n">
         <v>15.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="BJ15" t="n">
         <v>12</v>
@@ -4348,7 +4348,7 @@
         <v>20</v>
       </c>
       <c r="BQ15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
@@ -4357,7 +4357,7 @@
         <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU15" t="n">
         <v>5.4</v>
@@ -4372,7 +4372,7 @@
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.7</v>
+        <v>13.5</v>
       </c>
       <c r="BG16" t="n">
         <v>7.8</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
         <v>2.44</v>
       </c>
       <c r="O17" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P17" t="n">
         <v>1.47</v>
@@ -4754,7 +4754,7 @@
         <v>40</v>
       </c>
       <c r="AI17" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AJ17" t="n">
         <v>17</v>
@@ -4766,7 +4766,7 @@
         <v>540</v>
       </c>
       <c r="AM17" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="AN17" t="n">
         <v>22</v>
@@ -4802,7 +4802,7 @@
         <v>6.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
         <v>5.3</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
         <v>500</v>
       </c>
       <c r="Y18" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="Z18" t="n">
         <v>500</v>
@@ -4990,7 +4990,7 @@
         <v>500</v>
       </c>
       <c r="AC18" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD18" t="n">
         <v>500</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -5178,16 +5178,16 @@
         <v>1.67</v>
       </c>
       <c r="G19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I19" t="n">
         <v>5.8</v>
       </c>
       <c r="J19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
         <v>4.6</v>
@@ -5208,7 +5208,7 @@
         <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R19" t="n">
         <v>1.54</v>
@@ -5226,13 +5226,13 @@
         <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X19" t="n">
         <v>40</v>
       </c>
       <c r="Y19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z19" t="n">
         <v>500</v>
@@ -5250,7 +5250,7 @@
         <v>22</v>
       </c>
       <c r="AE19" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AF19" t="n">
         <v>12.5</v>
@@ -5280,7 +5280,7 @@
         <v>7.8</v>
       </c>
       <c r="AO19" t="n">
-        <v>700</v>
+        <v>60</v>
       </c>
       <c r="AP19" t="n">
         <v>19.5</v>
@@ -5304,7 +5304,7 @@
         <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX19" t="n">
         <v>10</v>
@@ -5316,7 +5316,7 @@
         <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BB19" t="n">
         <v>14.5</v>
@@ -5331,10 +5331,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH19" t="n">
         <v>4.4</v>
@@ -5346,13 +5346,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN19" t="n">
         <v>4.7</v>
@@ -5364,7 +5364,7 @@
         <v>11</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR19" t="n">
         <v>22</v>
@@ -5373,7 +5373,7 @@
         <v>7.2</v>
       </c>
       <c r="BT19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU19" t="n">
         <v>5</v>
@@ -5382,13 +5382,13 @@
         <v>42</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX19" t="n">
         <v>44</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
         <v>5.6</v>
       </c>
       <c r="K21" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
         <v>1.34</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G22" t="n">
         <v>2.64</v>
       </c>
       <c r="H22" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I22" t="n">
         <v>3.2</v>
@@ -5952,7 +5952,7 @@
         <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
         <v>1.35</v>
@@ -5982,7 +5982,7 @@
         <v>1.65</v>
       </c>
       <c r="U22" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V22" t="n">
         <v>1.45</v>
@@ -6006,7 +6006,7 @@
         <v>12.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
         <v>14</v>
@@ -6060,7 +6060,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV22" t="n">
         <v>11</v>
@@ -6078,10 +6078,10 @@
         <v>12.5</v>
       </c>
       <c r="BA22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB22" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>7.6</v>
       </c>
       <c r="BC22" t="n">
         <v>19.5</v>
@@ -6090,7 +6090,7 @@
         <v>18</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
         <v>14</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -6215,25 +6215,25 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O23" t="n">
         <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R23" t="n">
         <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T23" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U23" t="n">
         <v>1.98</v>
@@ -6266,13 +6266,13 @@
         <v>22</v>
       </c>
       <c r="AE23" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF23" t="n">
         <v>15</v>
       </c>
       <c r="AG23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH23" t="n">
         <v>24</v>
@@ -6299,58 +6299,58 @@
         <v>85</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.9</v>
+        <v>23</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW23" t="n">
         <v>4.1</v>
       </c>
       <c r="AX23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY23" t="n">
         <v>9</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>7.8</v>
       </c>
       <c r="AZ23" t="n">
         <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.95</v>
+        <v>28</v>
       </c>
       <c r="BE23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG23" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>4.1</v>
       </c>
       <c r="BH23" t="n">
         <v>3.35</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>1.3</v>
@@ -6553,10 +6553,10 @@
         <v>27</v>
       </c>
       <c r="AP24" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR24" t="n">
         <v>9</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
         <v>8.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX25" t="n">
         <v>9.800000000000001</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
         <v>15.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
         <v>10.5</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
         <v>4.5</v>
       </c>
       <c r="H27" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I27" t="n">
         <v>1.92</v>
@@ -7231,7 +7231,7 @@
         <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="O27" t="n">
         <v>1.14</v>
@@ -7246,7 +7246,7 @@
         <v>1.79</v>
       </c>
       <c r="S27" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T27" t="n">
         <v>1.49</v>
@@ -7318,16 +7318,16 @@
         <v>6.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR27" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS27" t="n">
         <v>10.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU27" t="n">
         <v>6.4</v>
@@ -7342,7 +7342,7 @@
         <v>7.8</v>
       </c>
       <c r="AY27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ27" t="n">
         <v>6</v>
@@ -7357,13 +7357,13 @@
         <v>7.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE27" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG27" t="n">
         <v>5.2</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
         <v>1.63</v>
       </c>
       <c r="G28" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H28" t="n">
         <v>5.2</v>
@@ -7473,7 +7473,7 @@
         <v>6.2</v>
       </c>
       <c r="J28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
         <v>4.8</v>
@@ -7512,7 +7512,7 @@
         <v>1.19</v>
       </c>
       <c r="W28" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X28" t="n">
         <v>21</v>
@@ -7608,7 +7608,7 @@
         <v>12.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD28" t="n">
         <v>14.5</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G30" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H30" t="n">
         <v>5.1</v>
@@ -7990,10 +7990,10 @@
         <v>1.45</v>
       </c>
       <c r="M30" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
         <v>1.53</v>
@@ -8005,7 +8005,7 @@
         <v>2.54</v>
       </c>
       <c r="R30" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
         <v>5.2</v>
@@ -8020,10 +8020,10 @@
         <v>1.21</v>
       </c>
       <c r="W30" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X30" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y30" t="n">
         <v>13.5</v>
@@ -8053,7 +8053,7 @@
         <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI30" t="n">
         <v>700</v>
@@ -8083,22 +8083,22 @@
         <v>11.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU30" t="n">
         <v>7.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX30" t="n">
         <v>8.800000000000001</v>
@@ -8107,10 +8107,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BA30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB30" t="n">
         <v>10.5</v>
@@ -8119,16 +8119,16 @@
         <v>13</v>
       </c>
       <c r="BD30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BF30" t="n">
         <v>18</v>
       </c>
       <c r="BG30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH30" t="n">
         <v>2.82</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
         <v>3.65</v>
       </c>
       <c r="L31" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
@@ -8265,10 +8265,10 @@
         <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U31" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V31" t="n">
         <v>1.72</v>
@@ -8334,7 +8334,7 @@
         <v>6.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AR31" t="n">
         <v>6.4</v>
@@ -8364,19 +8364,19 @@
         <v>6.4</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC31" t="n">
         <v>7.8</v>
       </c>
       <c r="BD31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE31" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF31" t="n">
         <v>8</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -8731,10 +8731,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G33" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H33" t="n">
         <v>5.9</v>
@@ -8746,7 +8746,7 @@
         <v>3.7</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L33" t="n">
         <v>1.49</v>
@@ -8758,7 +8758,7 @@
         <v>3.1</v>
       </c>
       <c r="O33" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P33" t="n">
         <v>1.7</v>
@@ -8767,7 +8767,7 @@
         <v>2.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
         <v>4.5</v>
@@ -8782,13 +8782,13 @@
         <v>1.18</v>
       </c>
       <c r="W33" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X33" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z33" t="n">
         <v>46</v>
@@ -8800,7 +8800,7 @@
         <v>6.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD33" t="n">
         <v>32</v>
@@ -8848,7 +8848,7 @@
         <v>34</v>
       </c>
       <c r="AS33" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT33" t="n">
         <v>6</v>
@@ -8860,7 +8860,7 @@
         <v>19</v>
       </c>
       <c r="AW33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX33" t="n">
         <v>7.8</v>
@@ -8869,28 +8869,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BA33" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF33" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC33" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG33" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH33" t="n">
         <v>3.05</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G34" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="H34" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J34" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9015,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -860,58 +860,58 @@
         <v>1.98</v>
       </c>
       <c r="G2" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
         <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="n">
         <v>15.5</v>
@@ -920,7 +920,7 @@
         <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB2" t="n">
         <v>8.800000000000001</v>
@@ -938,7 +938,7 @@
         <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AH2" t="n">
         <v>23</v>
@@ -956,49 +956,49 @@
         <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>390</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
@@ -1010,77 +1010,77 @@
         <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="BF2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BT2" t="n">
         <v>7.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BV2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -1111,31 +1111,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.25</v>
@@ -1144,40 +1144,40 @@
         <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S3" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V3" t="n">
         <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA3" t="n">
         <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
         <v>8.800000000000001</v>
@@ -1186,25 +1186,25 @@
         <v>17</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AL3" t="n">
         <v>34</v>
@@ -1216,52 +1216,52 @@
         <v>11.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BB3" t="n">
         <v>20</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE3" t="n">
         <v>55</v>
@@ -1270,7 +1270,7 @@
         <v>10</v>
       </c>
       <c r="BG3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BH3" t="n">
         <v>3.95</v>
@@ -1291,22 +1291,22 @@
         <v>3.05</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP3" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3" t="n">
         <v>7.4</v>
@@ -1315,10 +1315,10 @@
         <v>5.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>2.88</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1330,11 +1330,11 @@
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
         <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.22</v>
@@ -1389,184 +1389,184 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.12</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="S4" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="T4" t="n">
         <v>1.44</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Y4" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="Z4" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="n">
         <v>19.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="AF4" t="n">
         <v>18.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AJ4" t="n">
         <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AM4" t="n">
         <v>46</v>
       </c>
       <c r="AN4" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AO4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AQ4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AR4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS4" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AT4" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW4" t="n">
         <v>32</v>
       </c>
       <c r="AX4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG4" t="n">
         <v>18.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN4" t="n">
         <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BP4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1584,11 +1584,11 @@
         <v>10.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -1619,52 +1619,52 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>2.16</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
         <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="M5" t="n">
         <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S5" t="n">
         <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V5" t="n">
         <v>1.22</v>
@@ -1673,13 +1673,13 @@
         <v>1.86</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y5" t="n">
         <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
@@ -1688,10 +1688,10 @@
         <v>6.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
@@ -1712,10 +1712,10 @@
         <v>130</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
@@ -1727,58 +1727,58 @@
         <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT5" t="n">
         <v>5.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD5" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AX5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BE5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH5" t="n">
         <v>2.66</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN5" t="n">
         <v>4.6</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -1876,43 +1876,43 @@
         <v>2.98</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H6" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="K6" t="n">
         <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="M6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N6" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="O6" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="P6" t="n">
         <v>1.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
         <v>1.13</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="T6" t="n">
         <v>2.24</v>
@@ -1921,10 +1921,10 @@
         <v>1.61</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X6" t="n">
         <v>13.5</v>
@@ -1975,10 +1975,10 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
         <v>5.2</v>
@@ -1990,7 +1990,7 @@
         <v>7.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
@@ -1999,7 +1999,7 @@
         <v>5.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="AW6" t="n">
         <v>6.6</v>
@@ -2017,28 +2017,28 @@
         <v>7</v>
       </c>
       <c r="BB6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC6" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE6" t="n">
         <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.6</v>
+        <v>2.76</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH6" t="n">
         <v>2.54</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
@@ -2056,13 +2056,13 @@
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>3.35</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
@@ -2145,28 +2145,28 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
         <v>1.65</v>
@@ -2178,7 +2178,7 @@
         <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -2190,7 +2190,7 @@
         <v>34</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AB7" t="n">
         <v>14.5</v>
@@ -2199,7 +2199,7 @@
         <v>9.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE7" t="n">
         <v>46</v>
@@ -2208,7 +2208,7 @@
         <v>18.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
         <v>17.5</v>
@@ -2217,7 +2217,7 @@
         <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
         <v>26</v>
@@ -2229,64 +2229,64 @@
         <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>14</v>
       </c>
       <c r="AR7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV7" t="n">
         <v>13</v>
       </c>
-      <c r="AS7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11</v>
-      </c>
       <c r="AW7" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AX7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BA7" t="n">
         <v>34</v>
       </c>
       <c r="BB7" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BC7" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BE7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="BF7" t="n">
         <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.9</v>
+        <v>22</v>
       </c>
       <c r="BH7" t="n">
         <v>3.9</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H8" t="n">
         <v>3.5</v>
@@ -2399,7 +2399,7 @@
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
@@ -2408,19 +2408,19 @@
         <v>5.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
         <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
         <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="T8" t="n">
         <v>1.62</v>
@@ -2432,7 +2432,7 @@
         <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
@@ -2447,7 +2447,7 @@
         <v>120</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC8" t="n">
         <v>9.199999999999999</v>
@@ -2462,7 +2462,7 @@
         <v>15.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
         <v>16.5</v>
@@ -2474,7 +2474,7 @@
         <v>30</v>
       </c>
       <c r="AK8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL8" t="n">
         <v>50</v>
@@ -2495,13 +2495,13 @@
         <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AT8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU8" t="n">
         <v>8.199999999999999</v>
@@ -2510,7 +2510,7 @@
         <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AX8" t="n">
         <v>13.5</v>
@@ -2522,25 +2522,25 @@
         <v>13.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BB8" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC8" t="n">
         <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BF8" t="n">
         <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
@@ -2549,16 +2549,16 @@
         <v>3.65</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5.3</v>
@@ -2570,13 +2570,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR8" t="n">
         <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT8" t="n">
         <v>7</v>
@@ -2585,16 +2585,16 @@
         <v>5.2</v>
       </c>
       <c r="BV8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX8" t="n">
         <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="G9" t="n">
         <v>1.55</v>
@@ -2647,40 +2647,40 @@
         <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.66</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.6</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V9" t="n">
         <v>1.09</v>
@@ -2689,7 +2689,7 @@
         <v>2.8</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="Y9" t="n">
         <v>44</v>
@@ -2701,7 +2701,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AC9" t="n">
         <v>42</v>
@@ -2725,10 +2725,10 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AK9" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AL9" t="n">
         <v>500</v>
@@ -2737,22 +2737,22 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
         <v>9</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AT9" t="n">
         <v>4.6</v>
@@ -2761,10 +2761,10 @@
         <v>5.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2773,10 +2773,10 @@
         <v>5.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB9" t="n">
         <v>6.2</v>
@@ -2794,34 +2794,34 @@
         <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>8</v>
@@ -2830,35 +2830,35 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.1</v>
+        <v>9.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.65</v>
+        <v>7.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -2889,40 +2889,40 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="K10" t="n">
         <v>3.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="M10" t="n">
         <v>1.14</v>
       </c>
       <c r="N10" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="O10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="R10" t="n">
         <v>1.16</v>
@@ -2937,10 +2937,10 @@
         <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X10" t="n">
         <v>14.5</v>
@@ -2955,7 +2955,7 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.8</v>
+        <v>500</v>
       </c>
       <c r="AC10" t="n">
         <v>14</v>
@@ -3006,13 +3006,13 @@
         <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
         <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV10" t="n">
         <v>1.03</v>
@@ -3084,7 +3084,7 @@
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
@@ -3102,7 +3102,7 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="G11" t="n">
         <v>2.4</v>
@@ -3155,34 +3155,34 @@
         <v>8.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="K11" t="n">
         <v>3.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Q11" t="n">
         <v>2.46</v>
       </c>
       <c r="R11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="S11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
         <v>1.05</v>
@@ -3194,7 +3194,7 @@
         <v>1.19</v>
       </c>
       <c r="W11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X11" t="n">
         <v>500</v>
@@ -3212,7 +3212,7 @@
         <v>500</v>
       </c>
       <c r="AC11" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AD11" t="n">
         <v>500</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -3397,100 +3397,100 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="I12" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M12" t="n">
         <v>1.16</v>
       </c>
       <c r="N12" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="P12" t="n">
         <v>1.39</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
         <v>1.13</v>
       </c>
       <c r="S12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
         <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.199999999999999</v>
+        <v>60</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.5</v>
+        <v>50</v>
       </c>
       <c r="AA12" t="n">
-        <v>75</v>
+        <v>420</v>
       </c>
       <c r="AB12" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AE12" t="n">
-        <v>60</v>
+        <v>440</v>
       </c>
       <c r="AF12" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AH12" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="AI12" t="n">
         <v>540</v>
       </c>
       <c r="AJ12" t="n">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="AK12" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AL12" t="n">
         <v>540</v>
@@ -3499,76 +3499,76 @@
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AO12" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.9</v>
+        <v>3.85</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.4</v>
+        <v>1.68</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>1.67</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.8</v>
+        <v>1.71</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.9</v>
+        <v>1.63</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>6</v>
+        <v>1.64</v>
       </c>
       <c r="AY12" t="n">
-        <v>11.5</v>
+        <v>1.64</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.8</v>
+        <v>1.66</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.71</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.8</v>
+        <v>1.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>1.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.71</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.6</v>
+        <v>1.72</v>
       </c>
       <c r="BF12" t="n">
-        <v>8</v>
+        <v>1.71</v>
       </c>
       <c r="BG12" t="n">
-        <v>8</v>
+        <v>1.72</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.52</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3577,16 +3577,16 @@
         <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
@@ -3595,22 +3595,22 @@
         <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>3.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
         <v>1.16</v>
@@ -3678,31 +3678,31 @@
         <v>2.22</v>
       </c>
       <c r="O13" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U13" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X13" t="n">
         <v>7.6</v>
@@ -3729,13 +3729,13 @@
         <v>50</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI13" t="n">
         <v>240</v>
@@ -3744,10 +3744,10 @@
         <v>80</v>
       </c>
       <c r="AK13" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL13" t="n">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
@@ -3759,13 +3759,13 @@
         <v>65</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>6.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
         <v>1.03</v>
@@ -3783,10 +3783,10 @@
         <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
         <v>1.03</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN13" t="n">
         <v>6.4</v>
@@ -3864,17 +3864,17 @@
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -3905,67 +3905,67 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P14" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z14" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3977,13 +3977,13 @@
         <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AE14" t="n">
         <v>700</v>
       </c>
       <c r="AF14" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AG14" t="n">
         <v>11.5</v>
@@ -3992,79 +3992,79 @@
         <v>42</v>
       </c>
       <c r="AI14" t="n">
-        <v>540</v>
+        <v>700</v>
       </c>
       <c r="AJ14" t="n">
-        <v>18.5</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AL14" t="n">
-        <v>120</v>
+        <v>460</v>
       </c>
       <c r="AM14" t="n">
         <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO14" t="n">
         <v>700</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>19</v>
+        <v>3.75</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.4</v>
+        <v>3.15</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>16</v>
+        <v>3.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H15" t="n">
         <v>3.9</v>
@@ -4171,31 +4171,31 @@
         <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.54</v>
       </c>
       <c r="P15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S15" t="n">
         <v>5.3</v>
@@ -4204,13 +4204,13 @@
         <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V15" t="n">
         <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X15" t="n">
         <v>10</v>
@@ -4219,7 +4219,7 @@
         <v>11.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA15" t="n">
         <v>900</v>
@@ -4243,7 +4243,7 @@
         <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI15" t="n">
         <v>500</v>
@@ -4252,7 +4252,7 @@
         <v>34</v>
       </c>
       <c r="AK15" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AL15" t="n">
         <v>160</v>
@@ -4270,25 +4270,25 @@
         <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.4</v>
+        <v>4.9</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
         <v>6</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
         <v>15.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -4300,31 +4300,31 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD15" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BE15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG15" t="n">
         <v>8</v>
       </c>
-      <c r="BF15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BH15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ15" t="n">
         <v>12</v>
@@ -4336,16 +4336,16 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ15" t="n">
         <v>13.5</v>
@@ -4354,7 +4354,7 @@
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BT15" t="n">
         <v>7.6</v>
@@ -4366,7 +4366,7 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
@@ -4378,11 +4378,11 @@
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -4413,46 +4413,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="G16" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="M16" t="n">
         <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="O16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P16" t="n">
         <v>1.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="R16" t="n">
         <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T16" t="n">
         <v>2.12</v>
@@ -4461,10 +4461,10 @@
         <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X16" t="n">
         <v>10.5</v>
@@ -4524,7 +4524,7 @@
         <v>7.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
         <v>8.800000000000001</v>
@@ -4617,7 +4617,7 @@
         <v>6.2</v>
       </c>
       <c r="BV16" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
         <v>8.800000000000001</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G17" t="n">
         <v>1.71</v>
@@ -4676,40 +4676,40 @@
         <v>7.8</v>
       </c>
       <c r="I17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
         <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O17" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P17" t="n">
         <v>1.47</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R17" t="n">
         <v>1.16</v>
       </c>
       <c r="S17" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="U17" t="n">
         <v>1.51</v>
@@ -4718,28 +4718,28 @@
         <v>1.11</v>
       </c>
       <c r="W17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X17" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="Y17" t="n">
         <v>21</v>
       </c>
       <c r="Z17" t="n">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AA17" t="n">
         <v>540</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AC17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AE17" t="n">
         <v>300</v>
@@ -4757,7 +4757,7 @@
         <v>300</v>
       </c>
       <c r="AJ17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK17" t="n">
         <v>27</v>
@@ -4766,7 +4766,7 @@
         <v>540</v>
       </c>
       <c r="AM17" t="n">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="AN17" t="n">
         <v>22</v>
@@ -4775,28 +4775,28 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AX17" t="n">
         <v>6.6</v>
@@ -4805,28 +4805,28 @@
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BA17" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BB17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC17" t="n">
         <v>11.5</v>
       </c>
-      <c r="BC17" t="n">
-        <v>21</v>
-      </c>
       <c r="BD17" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BH17" t="n">
         <v>2.74</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -4921,64 +4921,64 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.58</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.55</v>
-      </c>
       <c r="S18" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T18" t="n">
         <v>1.54</v>
       </c>
       <c r="U18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="X18" t="n">
         <v>500</v>
       </c>
       <c r="Y18" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="Z18" t="n">
         <v>500</v>
@@ -5002,7 +5002,7 @@
         <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>16.5</v>
+        <v>36</v>
       </c>
       <c r="AH18" t="n">
         <v>60</v>
@@ -5023,7 +5023,7 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
         <v>500</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -5175,46 +5175,46 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="H19" t="n">
         <v>5.1</v>
       </c>
       <c r="I19" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J19" t="n">
         <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="R19" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="T19" t="n">
         <v>1.67</v>
@@ -5223,7 +5223,7 @@
         <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
         <v>2.38</v>
@@ -5235,7 +5235,7 @@
         <v>25</v>
       </c>
       <c r="Z19" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AA19" t="n">
         <v>900</v>
@@ -5247,7 +5247,7 @@
         <v>11</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
         <v>150</v>
@@ -5259,10 +5259,10 @@
         <v>10</v>
       </c>
       <c r="AH19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AJ19" t="n">
         <v>18</v>
@@ -5271,16 +5271,16 @@
         <v>17</v>
       </c>
       <c r="AL19" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO19" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="AP19" t="n">
         <v>19.5</v>
@@ -5292,7 +5292,7 @@
         <v>36</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -5304,10 +5304,10 @@
         <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
         <v>8.800000000000001</v>
@@ -5328,13 +5328,13 @@
         <v>14.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="BH19" t="n">
         <v>4.4</v>
@@ -5352,7 +5352,7 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN19" t="n">
         <v>4.7</v>
@@ -5370,7 +5370,7 @@
         <v>22</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT19" t="n">
         <v>9.199999999999999</v>
@@ -5379,13 +5379,13 @@
         <v>5</v>
       </c>
       <c r="BV19" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
         <v>8.6</v>
       </c>
       <c r="BX19" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
         <v>8.800000000000001</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -5429,58 +5429,58 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G20" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="H20" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I20" t="n">
         <v>2.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P20" t="n">
         <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
         <v>1.56</v>
       </c>
       <c r="W20" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X20" t="n">
         <v>19</v>
@@ -5492,7 +5492,7 @@
         <v>22</v>
       </c>
       <c r="AA20" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="AB20" t="n">
         <v>15</v>
@@ -5507,7 +5507,7 @@
         <v>34</v>
       </c>
       <c r="AF20" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AG20" t="n">
         <v>15</v>
@@ -5519,10 +5519,10 @@
         <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="n">
         <v>46</v>
@@ -5579,7 +5579,7 @@
         <v>14.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE20" t="n">
         <v>1.03</v>
@@ -5588,28 +5588,28 @@
         <v>20</v>
       </c>
       <c r="BG20" t="n">
-        <v>17.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK20" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO20" t="n">
         <v>5.3</v>
@@ -5618,31 +5618,31 @@
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT20" t="n">
         <v>5.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -5683,19 +5683,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G21" t="n">
         <v>1.34</v>
       </c>
       <c r="H21" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="I21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J21" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
@@ -5710,25 +5710,25 @@
         <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="T21" t="n">
         <v>2.16</v>
       </c>
       <c r="U21" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="V21" t="n">
         <v>1.07</v>
@@ -5740,13 +5740,13 @@
         <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Z21" t="n">
-        <v>540</v>
+        <v>120</v>
       </c>
       <c r="AA21" t="n">
-        <v>710</v>
+        <v>630</v>
       </c>
       <c r="AB21" t="n">
         <v>8.4</v>
@@ -5755,7 +5755,7 @@
         <v>14</v>
       </c>
       <c r="AD21" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AE21" t="n">
         <v>250</v>
@@ -5764,31 +5764,31 @@
         <v>7.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
         <v>32</v>
       </c>
       <c r="AI21" t="n">
-        <v>240</v>
+        <v>470</v>
       </c>
       <c r="AJ21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM21" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AO21" t="n">
-        <v>390</v>
+        <v>310</v>
       </c>
       <c r="AP21" t="n">
         <v>17</v>
@@ -5797,10 +5797,10 @@
         <v>34</v>
       </c>
       <c r="AR21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AT21" t="n">
         <v>7.6</v>
@@ -5812,10 +5812,10 @@
         <v>36</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY21" t="n">
         <v>9.6</v>
@@ -5824,22 +5824,22 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC21" t="n">
         <v>13</v>
       </c>
       <c r="BD21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BG21" t="n">
         <v>15</v>
@@ -5851,37 +5851,37 @@
         <v>3.55</v>
       </c>
       <c r="BJ21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ21" t="n">
         <v>5.7</v>
       </c>
       <c r="BR21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS21" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BT21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BU21" t="n">
         <v>9.6</v>
@@ -5890,13 +5890,13 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -5937,58 +5937,58 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G22" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H22" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J22" t="n">
         <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
         <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R22" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X22" t="n">
         <v>17.5</v>
@@ -5997,10 +5997,10 @@
         <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AB22" t="n">
         <v>12.5</v>
@@ -6015,7 +6015,7 @@
         <v>34</v>
       </c>
       <c r="AF22" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="AG22" t="n">
         <v>12.5</v>
@@ -6036,13 +6036,13 @@
         <v>40</v>
       </c>
       <c r="AM22" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN22" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="AO22" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AP22" t="n">
         <v>13</v>
@@ -6075,22 +6075,22 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="BC22" t="n">
         <v>19.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF22" t="n">
         <v>14</v>
@@ -6129,7 +6129,7 @@
         <v>7</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS22" t="n">
         <v>8.199999999999999</v>
@@ -6138,7 +6138,7 @@
         <v>6.4</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BV22" t="n">
         <v>23</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -6191,85 +6191,85 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W23" t="n">
         <v>1.92</v>
       </c>
-      <c r="G23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.9</v>
-      </c>
       <c r="X23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z23" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AA23" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE23" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AF23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG23" t="n">
         <v>12.5</v>
@@ -6278,13 +6278,13 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AJ23" t="n">
         <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL23" t="n">
         <v>48</v>
@@ -6293,10 +6293,10 @@
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO23" t="n">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="AP23" t="n">
         <v>9.6</v>
@@ -6308,7 +6308,7 @@
         <v>23</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AT23" t="n">
         <v>7.4</v>
@@ -6320,7 +6320,7 @@
         <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AX23" t="n">
         <v>10</v>
@@ -6332,7 +6332,7 @@
         <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB23" t="n">
         <v>20</v>
@@ -6344,67 +6344,67 @@
         <v>28</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BF23" t="n">
         <v>14</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN23" t="n">
         <v>4.8</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR23" t="n">
         <v>32</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU23" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY23" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="G24" t="n">
         <v>6</v>
@@ -6454,46 +6454,46 @@
         <v>1.69</v>
       </c>
       <c r="I24" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="J24" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K24" t="n">
         <v>4.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P24" t="n">
         <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="R24" t="n">
         <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T24" t="n">
         <v>1.86</v>
       </c>
       <c r="U24" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V24" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="W24" t="n">
         <v>1.2</v>
@@ -6514,7 +6514,7 @@
         <v>34</v>
       </c>
       <c r="AC24" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD24" t="n">
         <v>21</v>
@@ -6556,19 +6556,19 @@
         <v>6.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="AS24" t="n">
         <v>8.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV24" t="n">
         <v>8.800000000000001</v>
@@ -6592,7 +6592,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BC24" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD24" t="n">
         <v>9.199999999999999</v>
@@ -6607,40 +6607,40 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="BJ24" t="n">
         <v>11</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN24" t="n">
         <v>9.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT24" t="n">
         <v>4.4</v>
@@ -6658,17 +6658,17 @@
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -6702,49 +6702,49 @@
         <v>4.8</v>
       </c>
       <c r="G25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H25" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="I25" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="J25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K25" t="n">
         <v>5.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="M25" t="n">
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O25" t="n">
         <v>1.12</v>
       </c>
       <c r="P25" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R25" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S25" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="T25" t="n">
         <v>1.5</v>
       </c>
       <c r="U25" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V25" t="n">
         <v>2.46</v>
@@ -6801,13 +6801,13 @@
         <v>55</v>
       </c>
       <c r="AN25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO25" t="n">
         <v>5.1</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ25" t="n">
         <v>12.5</v>
@@ -6831,7 +6831,7 @@
         <v>13</v>
       </c>
       <c r="AX25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>15.5</v>
@@ -6846,13 +6846,13 @@
         <v>11</v>
       </c>
       <c r="BC25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BF25" t="n">
         <v>8.6</v>
@@ -6864,7 +6864,7 @@
         <v>5.5</v>
       </c>
       <c r="BI25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ25" t="n">
         <v>9</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -6953,109 +6953,109 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="G26" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="H26" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="I26" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="J26" t="n">
         <v>3.8</v>
       </c>
       <c r="K26" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P26" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T26" t="n">
         <v>1.5</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.48</v>
-      </c>
       <c r="U26" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V26" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W26" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X26" t="n">
         <v>80</v>
       </c>
       <c r="Y26" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="Z26" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AA26" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB26" t="n">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="AC26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
         <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AK26" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AL26" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AM26" t="n">
         <v>200</v>
       </c>
       <c r="AN26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO26" t="n">
         <v>16</v>
@@ -7106,7 +7106,7 @@
         <v>19.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BF26" t="n">
         <v>9.800000000000001</v>
@@ -7115,10 +7115,10 @@
         <v>10.5</v>
       </c>
       <c r="BH26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ26" t="n">
         <v>9</v>
@@ -7130,19 +7130,19 @@
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BN26" t="n">
         <v>6.6</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP26" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR26" t="n">
         <v>26</v>
@@ -7160,23 +7160,23 @@
         <v>19</v>
       </c>
       <c r="BW26" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BX26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY26" t="n">
         <v>6.2</v>
       </c>
       <c r="BZ26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CA26" t="n">
         <v>5.5</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="G27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H27" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="I27" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="J27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K27" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
         <v>1.24</v>
@@ -7237,28 +7237,28 @@
         <v>1.14</v>
       </c>
       <c r="P27" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="R27" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S27" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="T27" t="n">
         <v>1.49</v>
       </c>
       <c r="U27" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V27" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W27" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X27" t="n">
         <v>500</v>
@@ -7315,7 +7315,7 @@
         <v>24</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ27" t="n">
         <v>6.2</v>
@@ -7324,7 +7324,7 @@
         <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="AT27" t="n">
         <v>7.2</v>
@@ -7366,7 +7366,7 @@
         <v>5.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH27" t="n">
         <v>5.3</v>
@@ -7387,7 +7387,7 @@
         <v>46</v>
       </c>
       <c r="BN27" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BO27" t="n">
         <v>6.4</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G28" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H28" t="n">
         <v>5.2</v>
@@ -7473,34 +7473,34 @@
         <v>6.2</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K28" t="n">
         <v>4.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M28" t="n">
         <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
         <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R28" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="T28" t="n">
         <v>1.73</v>
@@ -7509,10 +7509,10 @@
         <v>2.16</v>
       </c>
       <c r="V28" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W28" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X28" t="n">
         <v>21</v>
@@ -7524,7 +7524,7 @@
         <v>48</v>
       </c>
       <c r="AA28" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
         <v>11</v>
@@ -7539,13 +7539,13 @@
         <v>160</v>
       </c>
       <c r="AF28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG28" t="n">
         <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI28" t="n">
         <v>65</v>
@@ -7560,10 +7560,10 @@
         <v>32</v>
       </c>
       <c r="AM28" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO28" t="n">
         <v>75</v>
@@ -7575,16 +7575,16 @@
         <v>18</v>
       </c>
       <c r="AR28" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT28" t="n">
         <v>9</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV28" t="n">
         <v>17</v>
@@ -7602,7 +7602,7 @@
         <v>14.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB28" t="n">
         <v>12.5</v>
@@ -7614,13 +7614,13 @@
         <v>14.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF28" t="n">
         <v>6.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH28" t="n">
         <v>4.2</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G29" t="n">
         <v>4.2</v>
@@ -7727,10 +7727,10 @@
         <v>1.92</v>
       </c>
       <c r="J29" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="K29" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
         <v>1.11</v>
@@ -7745,25 +7745,25 @@
         <v>1.04</v>
       </c>
       <c r="P29" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="R29" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S29" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="T29" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>4.2</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W29" t="n">
         <v>1.33</v>
@@ -7772,109 +7772,109 @@
         <v>500</v>
       </c>
       <c r="Y29" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="Z29" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AA29" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AC29" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AD29" t="n">
-        <v>17.5</v>
+        <v>500</v>
       </c>
       <c r="AE29" t="n">
-        <v>19.5</v>
+        <v>500</v>
       </c>
       <c r="AF29" t="n">
         <v>500</v>
       </c>
       <c r="AG29" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AH29" t="n">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="AI29" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AJ29" t="n">
         <v>900</v>
       </c>
       <c r="AK29" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AL29" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AM29" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="AO29" t="n">
-        <v>3.95</v>
+        <v>29</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.6</v>
+        <v>1.38</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6</v>
+        <v>1.33</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.9</v>
+        <v>1.35</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.9</v>
+        <v>1.36</v>
       </c>
       <c r="AT29" t="n">
-        <v>6.4</v>
+        <v>1.36</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.4</v>
+        <v>1.34</v>
       </c>
       <c r="AV29" t="n">
-        <v>5</v>
+        <v>1.32</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.2</v>
+        <v>1.35</v>
       </c>
       <c r="AX29" t="n">
-        <v>6.4</v>
+        <v>1.36</v>
       </c>
       <c r="AY29" t="n">
-        <v>5.6</v>
+        <v>1.36</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5</v>
+        <v>1.32</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.3</v>
+        <v>1.37</v>
       </c>
       <c r="BB29" t="n">
-        <v>6.6</v>
+        <v>1.37</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.9</v>
+        <v>1.36</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.6</v>
+        <v>1.35</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.8</v>
+        <v>1.38</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.52</v>
+        <v>1.32</v>
       </c>
       <c r="BH29" t="n">
         <v>9.6</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -7969,49 +7969,49 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G30" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H30" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I30" t="n">
         <v>5.7</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K30" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="M30" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P30" t="n">
         <v>1.58</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S30" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U30" t="n">
         <v>1.72</v>
@@ -8020,10 +8020,10 @@
         <v>1.21</v>
       </c>
       <c r="W30" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y30" t="n">
         <v>13.5</v>
@@ -8038,7 +8038,7 @@
         <v>6.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD30" t="n">
         <v>70</v>
@@ -8047,7 +8047,7 @@
         <v>700</v>
       </c>
       <c r="AF30" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG30" t="n">
         <v>11</v>
@@ -8062,7 +8062,7 @@
         <v>500</v>
       </c>
       <c r="AK30" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AL30" t="n">
         <v>460</v>
@@ -8080,61 +8080,61 @@
         <v>8.4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS30" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
         <v>19.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX30" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
         <v>13</v>
       </c>
       <c r="BA30" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BB30" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BC30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD30" t="n">
         <v>13</v>
       </c>
-      <c r="BD30" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BE30" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BF30" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BH30" t="n">
         <v>2.82</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="BJ30" t="n">
         <v>12</v>
@@ -8146,7 +8146,7 @@
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN30" t="n">
         <v>4.3</v>
@@ -8170,19 +8170,19 @@
         <v>8.6</v>
       </c>
       <c r="BU30" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G31" t="n">
         <v>3.8</v>
       </c>
       <c r="H31" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J31" t="n">
         <v>3.45</v>
@@ -8241,46 +8241,46 @@
         <v>3.65</v>
       </c>
       <c r="L31" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O31" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P31" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Q31" t="n">
         <v>2.14</v>
       </c>
       <c r="R31" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="U31" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V31" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X31" t="n">
         <v>25</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z31" t="n">
         <v>25</v>
@@ -8298,7 +8298,7 @@
         <v>20</v>
       </c>
       <c r="AE31" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF31" t="n">
         <v>500</v>
@@ -8331,67 +8331,67 @@
         <v>55</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AQ31" t="n">
         <v>7.6</v>
       </c>
       <c r="AR31" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
       </c>
       <c r="AU31" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX31" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AY31" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF31" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>8</v>
-      </c>
       <c r="BG31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH31" t="n">
         <v>3.3</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="BJ31" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK31" t="n">
         <v>7.8</v>
@@ -8400,53 +8400,53 @@
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BN31" t="n">
         <v>7.2</v>
       </c>
       <c r="BO31" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT31" t="n">
         <v>5.2</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BW31" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -8480,16 +8480,16 @@
         <v>2.12</v>
       </c>
       <c r="G32" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="H32" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I32" t="n">
         <v>4.1</v>
       </c>
       <c r="J32" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K32" t="n">
         <v>3.7</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8731,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="G33" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="H33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I33" t="n">
         <v>5.9</v>
       </c>
-      <c r="I33" t="n">
-        <v>6.4</v>
-      </c>
       <c r="J33" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K33" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L33" t="n">
         <v>1.49</v>
@@ -8755,34 +8755,34 @@
         <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P33" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q33" t="n">
         <v>2.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S33" t="n">
         <v>4.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U33" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="V33" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W33" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X33" t="n">
         <v>14</v>
@@ -8791,13 +8791,13 @@
         <v>16.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA33" t="n">
         <v>200</v>
       </c>
       <c r="AB33" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC33" t="n">
         <v>8.4</v>
@@ -8809,19 +8809,19 @@
         <v>120</v>
       </c>
       <c r="AF33" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG33" t="n">
         <v>970</v>
       </c>
       <c r="AH33" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI33" t="n">
         <v>130</v>
       </c>
       <c r="AJ33" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK33" t="n">
         <v>22</v>
@@ -8833,10 +8833,10 @@
         <v>210</v>
       </c>
       <c r="AN33" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP33" t="n">
         <v>10</v>
@@ -8845,58 +8845,58 @@
         <v>13.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS33" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT33" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU33" t="n">
         <v>7.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="AW33" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX33" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="AY33" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BA33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BB33" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC33" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="BD33" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BE33" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF33" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BG33" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH33" t="n">
         <v>3.05</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ33" t="n">
         <v>11.5</v>
@@ -8920,7 +8920,7 @@
         <v>12.5</v>
       </c>
       <c r="BQ33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
@@ -8929,7 +8929,7 @@
         <v>24</v>
       </c>
       <c r="BT33" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BU33" t="n">
         <v>7</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G34" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="H34" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="I34" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J34" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K34" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
         <v>1.57</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -860,19 +860,19 @@
         <v>1.98</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
         <v>4.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.46</v>
@@ -881,34 +881,34 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
         <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
         <v>14.5</v>
@@ -920,7 +920,7 @@
         <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB2" t="n">
         <v>8.800000000000001</v>
@@ -929,22 +929,22 @@
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF2" t="n">
         <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH2" t="n">
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
         <v>25</v>
@@ -956,13 +956,13 @@
         <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>390</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
         <v>16.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP2" t="n">
         <v>12.5</v>
@@ -974,37 +974,37 @@
         <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
         <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
         <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
         <v>30</v>
@@ -1013,10 +1013,10 @@
         <v>85</v>
       </c>
       <c r="BF2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BH2" t="n">
         <v>3.3</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G3" t="n">
         <v>1.97</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
         <v>3.8</v>
@@ -1129,34 +1129,34 @@
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U3" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V3" t="n">
         <v>1.3</v>
@@ -1165,7 +1165,7 @@
         <v>2.02</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
@@ -1174,25 +1174,25 @@
         <v>42</v>
       </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>17</v>
       </c>
       <c r="AE3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH3" t="n">
         <v>18.5</v>
@@ -1201,7 +1201,7 @@
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK3" t="n">
         <v>18.5</v>
@@ -1210,19 +1210,19 @@
         <v>34</v>
       </c>
       <c r="AM3" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="AN3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
         <v>48</v>
       </c>
       <c r="AP3" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
         <v>28</v>
@@ -1246,13 +1246,13 @@
         <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
         <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB3" t="n">
         <v>20</v>
@@ -1267,28 +1267,28 @@
         <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG3" t="n">
         <v>28</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.05</v>
+        <v>14</v>
       </c>
       <c r="BN3" t="n">
         <v>4.8</v>
@@ -1297,16 +1297,16 @@
         <v>4.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT3" t="n">
         <v>7.4</v>
@@ -1318,23 +1318,23 @@
         <v>42</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.88</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.92</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G4" t="n">
         <v>1.82</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.86</v>
-      </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J4" t="n">
         <v>4.5</v>
@@ -1395,58 +1395,58 @@
         <v>1.12</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R4" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="S4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="T4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W4" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z4" t="n">
         <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB4" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AF4" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
         <v>14.5</v>
@@ -1455,37 +1455,37 @@
         <v>36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN4" t="n">
         <v>5.7</v>
       </c>
       <c r="AO4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR4" t="n">
         <v>38</v>
       </c>
       <c r="AS4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AT4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AU4" t="n">
         <v>11.5</v>
@@ -1494,7 +1494,7 @@
         <v>16.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX4" t="n">
         <v>16</v>
@@ -1509,28 +1509,28 @@
         <v>30</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
         <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
         <v>38</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH4" t="n">
         <v>5.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.4</v>
@@ -1539,56 +1539,56 @@
         <v>7</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM4" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP4" t="n">
         <v>11</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>990</v>
+        <v>17</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>8.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1631,10 @@
         <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
         <v>1.63</v>
@@ -1649,10 +1649,10 @@
         <v>1.6</v>
       </c>
       <c r="P5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R5" t="n">
         <v>1.15</v>
@@ -1664,13 +1664,13 @@
         <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
         <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X5" t="n">
         <v>7.8</v>
@@ -1733,7 +1733,7 @@
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS5" t="n">
         <v>9.4</v>
@@ -1742,10 +1742,10 @@
         <v>5.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AW5" t="n">
         <v>9.199999999999999</v>
@@ -1754,19 +1754,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD5" t="n">
         <v>8.800000000000001</v>
@@ -1775,7 +1775,7 @@
         <v>9.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
         <v>9.6</v>
@@ -1790,59 +1790,59 @@
         <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
         <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BP5" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS5" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
         <v>8.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -1879,34 +1879,34 @@
         <v>3.55</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J6" t="n">
         <v>2.72</v>
       </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="M6" t="n">
         <v>1.16</v>
       </c>
       <c r="N6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O6" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="P6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R6" t="n">
         <v>1.13</v>
@@ -1915,10 +1915,10 @@
         <v>6.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V6" t="n">
         <v>1.48</v>
@@ -1930,7 +1930,7 @@
         <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="Z6" t="n">
         <v>500</v>
@@ -1939,7 +1939,7 @@
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="AC6" t="n">
         <v>15</v>
@@ -1981,28 +1981,28 @@
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR6" t="n">
         <v>7.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AU6" t="n">
         <v>5.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
         <v>8.4</v>
@@ -2011,28 +2011,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BG6" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>7</v>
       </c>
       <c r="BH6" t="n">
         <v>2.54</v>
@@ -2044,59 +2044,59 @@
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
         <v>6</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G7" t="n">
         <v>2.26</v>
@@ -2136,10 +2136,10 @@
         <v>3.35</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
@@ -2151,31 +2151,31 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R7" t="n">
         <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
         <v>1.8</v>
@@ -2187,28 +2187,28 @@
         <v>19.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="n">
         <v>150</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC7" t="n">
         <v>9.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
         <v>46</v>
       </c>
       <c r="AF7" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
         <v>17.5</v>
@@ -2220,25 +2220,25 @@
         <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO7" t="n">
         <v>38</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>34</v>
       </c>
       <c r="AP7" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR7" t="n">
         <v>21</v>
@@ -2271,10 +2271,10 @@
         <v>34</v>
       </c>
       <c r="BB7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD7" t="n">
         <v>23</v>
@@ -2283,7 +2283,7 @@
         <v>50</v>
       </c>
       <c r="BF7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG7" t="n">
         <v>22</v>
@@ -2298,13 +2298,13 @@
         <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
         <v>5.3</v>
@@ -2322,7 +2322,7 @@
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
         <v>7</v>
@@ -2331,16 +2331,16 @@
         <v>6</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW7" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY7" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G8" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
         <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>1.34</v>
@@ -2411,16 +2411,16 @@
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R8" t="n">
         <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
         <v>1.62</v>
@@ -2429,34 +2429,34 @@
         <v>2.52</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AB8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF8" t="n">
         <v>15.5</v>
@@ -2465,19 +2465,19 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ8" t="n">
         <v>30</v>
       </c>
       <c r="AK8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AM8" t="n">
         <v>190</v>
@@ -2486,55 +2486,55 @@
         <v>12</v>
       </c>
       <c r="AO8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP8" t="n">
         <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS8" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AT8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BC8" t="n">
         <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BE8" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BF8" t="n">
         <v>10.5</v>
@@ -2543,7 +2543,7 @@
         <v>24</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI8" t="n">
         <v>3.65</v>
@@ -2552,13 +2552,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5.3</v>
@@ -2570,13 +2570,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR8" t="n">
         <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT8" t="n">
         <v>7</v>
@@ -2588,13 +2588,13 @@
         <v>25</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
         <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -2644,43 +2644,43 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P9" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q9" t="n">
         <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="U9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
         <v>1.09</v>
@@ -2689,19 +2689,19 @@
         <v>2.8</v>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="n">
         <v>44</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AC9" t="n">
         <v>42</v>
@@ -2716,13 +2716,13 @@
         <v>7.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
         <v>190</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AJ9" t="n">
         <v>16</v>
@@ -2731,7 +2731,7 @@
         <v>70</v>
       </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2743,40 +2743,40 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
         <v>9</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT9" t="n">
         <v>4.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV9" t="n">
         <v>18</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB9" t="n">
         <v>6.2</v>
@@ -2785,43 +2785,43 @@
         <v>16.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF9" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="BJ9" t="n">
         <v>16</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BO9" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="BP9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ9" t="n">
         <v>8</v>
@@ -2830,25 +2830,25 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT9" t="n">
         <v>14</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K10" t="n">
         <v>3.1</v>
@@ -2916,13 +2916,13 @@
         <v>2.44</v>
       </c>
       <c r="O10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R10" t="n">
         <v>1.16</v>
@@ -2940,7 +2940,7 @@
         <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
         <v>14.5</v>
@@ -2961,7 +2961,7 @@
         <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
@@ -2991,64 +2991,64 @@
         <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
         <v>5.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AU10" t="n">
         <v>5.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AW10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
         <v>30</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.55</v>
+        <v>6.8</v>
       </c>
       <c r="BH10" t="n">
         <v>2.7</v>
@@ -3060,13 +3060,13 @@
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
@@ -3078,13 +3078,13 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="H11" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2.52</v>
+        <v>2.86</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
         <v>1.64</v>
@@ -3170,37 +3170,37 @@
         <v>2.3</v>
       </c>
       <c r="O11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.6</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="X11" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="n">
         <v>500</v>
@@ -3209,10 +3209,10 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>500</v>
+        <v>7.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>500</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD11" t="n">
         <v>500</v>
@@ -3221,10 +3221,10 @@
         <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AH11" t="n">
         <v>500</v>
@@ -3245,76 +3245,76 @@
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
         <v>4.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.55</v>
+        <v>7.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3323,10 +3323,10 @@
         <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
@@ -3344,7 +3344,7 @@
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -3397,46 +3397,46 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="H12" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="K12" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="L12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="O12" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="P12" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="R12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T12" t="n">
         <v>1.92</v>
@@ -3445,52 +3445,52 @@
         <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>500</v>
       </c>
       <c r="Y12" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="Z12" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="AB12" t="n">
-        <v>16.5</v>
+        <v>500</v>
       </c>
       <c r="AC12" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD12" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AE12" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AG12" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AH12" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AI12" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AK12" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
         <v>540</v>
@@ -3499,22 +3499,22 @@
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>180</v>
+        <v>600</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
         <v>3.85</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AT12" t="n">
         <v>4.2</v>
@@ -3523,40 +3523,40 @@
         <v>4.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -3657,13 +3657,13 @@
         <v>3.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I13" t="n">
         <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K13" t="n">
         <v>3.1</v>
@@ -3675,16 +3675,16 @@
         <v>1.16</v>
       </c>
       <c r="N13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="P13" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R13" t="n">
         <v>1.13</v>
@@ -3726,10 +3726,10 @@
         <v>15</v>
       </c>
       <c r="AE13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
         <v>17.5</v>
@@ -3741,7 +3741,7 @@
         <v>240</v>
       </c>
       <c r="AJ13" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>150</v>
@@ -3756,61 +3756,61 @@
         <v>110</v>
       </c>
       <c r="AO13" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP13" t="n">
         <v>5.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.55</v>
+        <v>8.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="BH13" t="n">
         <v>2.52</v>
@@ -3822,13 +3822,13 @@
         <v>13</v>
       </c>
       <c r="BK13" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
         <v>6.4</v>
@@ -3840,13 +3840,13 @@
         <v>36</v>
       </c>
       <c r="BQ13" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
         <v>70</v>
       </c>
       <c r="BS13" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
         <v>5.7</v>
@@ -3858,23 +3858,23 @@
         <v>29</v>
       </c>
       <c r="BW13" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="H14" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.49</v>
@@ -3929,16 +3929,16 @@
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
         <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R14" t="n">
         <v>1.27</v>
@@ -3947,169 +3947,169 @@
         <v>4.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U14" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="X14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z14" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
         <v>700</v>
       </c>
       <c r="AF14" t="n">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="AG14" t="n">
         <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="AL14" t="n">
-        <v>460</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
         <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO14" t="n">
         <v>700</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="AQ14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO14" t="n">
         <v>3.5</v>
       </c>
-      <c r="AR14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ14" t="n">
         <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS14" t="n">
         <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU14" t="n">
         <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -4159,79 +4159,79 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G15" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
         <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L15" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="P15" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S15" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="V15" t="n">
         <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="AA15" t="n">
         <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC15" t="n">
         <v>7.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE15" t="n">
         <v>500</v>
@@ -4243,7 +4243,7 @@
         <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AI15" t="n">
         <v>500</v>
@@ -4252,43 +4252,43 @@
         <v>34</v>
       </c>
       <c r="AK15" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO15" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU15" t="n">
         <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -4297,92 +4297,92 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF15" t="n">
-        <v>19</v>
-      </c>
       <c r="BG15" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="BJ15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP15" t="n">
         <v>21</v>
       </c>
-      <c r="BN15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BQ15" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
         <v>7.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -4413,100 +4413,100 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="H16" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="I16" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O16" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R16" t="n">
         <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T16" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U16" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="X16" t="n">
         <v>10.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Z16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AA16" t="n">
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="AF16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG16" t="n">
         <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI16" t="n">
-        <v>700</v>
+        <v>540</v>
       </c>
       <c r="AJ16" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL16" t="n">
         <v>60</v>
@@ -4515,128 +4515,128 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AO16" t="n">
         <v>700</v>
       </c>
       <c r="AP16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS16" t="n">
         <v>7.6</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR16" t="n">
+      <c r="AT16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AS16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>9.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD16" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BE16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP16" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BQ16" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="CA16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G17" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="H17" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I17" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
         <v>1.6</v>
@@ -4697,7 +4697,7 @@
         <v>1.58</v>
       </c>
       <c r="P17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q17" t="n">
         <v>2.78</v>
@@ -4706,58 +4706,58 @@
         <v>1.16</v>
       </c>
       <c r="S17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="U17" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="X17" t="n">
         <v>8.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z17" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AA17" t="n">
-        <v>540</v>
+        <v>460</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE17" t="n">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="AF17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG17" t="n">
         <v>14.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI17" t="n">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK17" t="n">
         <v>27</v>
@@ -4766,79 +4766,79 @@
         <v>540</v>
       </c>
       <c r="AM17" t="n">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AP17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW17" t="n">
         <v>7.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BA17" t="n">
         <v>7.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG17" t="n">
         <v>8</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BJ17" t="n">
         <v>15</v>
       </c>
       <c r="BK17" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4847,28 +4847,28 @@
         <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BO17" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BP17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS17" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU17" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
@@ -4886,11 +4886,11 @@
         <v>38</v>
       </c>
       <c r="CA17" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -4927,19 +4927,19 @@
         <v>2.34</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J18" t="n">
         <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
@@ -4951,7 +4951,7 @@
         <v>1.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q18" t="n">
         <v>1.63</v>
@@ -4960,7 +4960,7 @@
         <v>1.58</v>
       </c>
       <c r="S18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
         <v>1.54</v>
@@ -4969,7 +4969,7 @@
         <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
         <v>1.75</v>
@@ -5035,10 +5035,10 @@
         <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -5050,7 +5050,7 @@
         <v>8.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AX18" t="n">
         <v>9</v>
@@ -5062,25 +5062,25 @@
         <v>8.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BC18" t="n">
         <v>10.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BH18" t="n">
         <v>4.4</v>
@@ -5092,13 +5092,13 @@
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
         <v>5.7</v>
@@ -5110,13 +5110,13 @@
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
@@ -5128,13 +5128,13 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I19" t="n">
         <v>5.6</v>
@@ -5223,16 +5223,16 @@
         <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X19" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z19" t="n">
         <v>46</v>
@@ -5259,10 +5259,10 @@
         <v>10</v>
       </c>
       <c r="AH19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AJ19" t="n">
         <v>18</v>
@@ -5271,13 +5271,13 @@
         <v>17</v>
       </c>
       <c r="AL19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AO19" t="n">
         <v>140</v>
@@ -5286,10 +5286,10 @@
         <v>19.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR19" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AS19" t="n">
         <v>10</v>
@@ -5304,19 +5304,19 @@
         <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>9.4</v>
+        <v>40</v>
       </c>
       <c r="AX19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB19" t="n">
         <v>14.5</v>
@@ -5325,34 +5325,34 @@
         <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF19" t="n">
         <v>6.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI19" t="n">
         <v>3.45</v>
       </c>
       <c r="BJ19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN19" t="n">
         <v>4.7</v>
@@ -5364,31 +5364,31 @@
         <v>11</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BR19" t="n">
         <v>22</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BT19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H20" t="n">
         <v>2.62</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
         <v>3.8</v>
@@ -5453,19 +5453,19 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
         <v>1.29</v>
       </c>
       <c r="P20" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
         <v>1.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
         <v>3.25</v>
@@ -5474,13 +5474,13 @@
         <v>1.7</v>
       </c>
       <c r="U20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V20" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W20" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
         <v>19</v>
@@ -5498,7 +5498,7 @@
         <v>15</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD20" t="n">
         <v>14.5</v>
@@ -5519,7 +5519,7 @@
         <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AK20" t="n">
         <v>80</v>
@@ -5582,7 +5582,7 @@
         <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BF20" t="n">
         <v>20</v>
@@ -5591,7 +5591,7 @@
         <v>5.2</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI20" t="n">
         <v>3.25</v>
@@ -5600,16 +5600,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO20" t="n">
         <v>5.3</v>
@@ -5618,31 +5618,31 @@
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT20" t="n">
         <v>5.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -5686,55 +5686,55 @@
         <v>1.33</v>
       </c>
       <c r="G21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H21" t="n">
         <v>11.5</v>
       </c>
       <c r="I21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J21" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="U21" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="X21" t="n">
         <v>22</v>
@@ -5746,28 +5746,28 @@
         <v>120</v>
       </c>
       <c r="AA21" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AC21" t="n">
         <v>14</v>
       </c>
       <c r="AD21" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AE21" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AF21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG21" t="n">
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI21" t="n">
         <v>470</v>
@@ -5779,28 +5779,28 @@
         <v>16.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM21" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AO21" t="n">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="AP21" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>34</v>
       </c>
       <c r="AR21" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AT21" t="n">
         <v>7.6</v>
@@ -5812,7 +5812,7 @@
         <v>36</v>
       </c>
       <c r="AW21" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AX21" t="n">
         <v>6.8</v>
@@ -5824,7 +5824,7 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BB21" t="n">
         <v>9</v>
@@ -5836,7 +5836,7 @@
         <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BF21" t="n">
         <v>4.7</v>
@@ -5845,25 +5845,25 @@
         <v>15</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BJ21" t="n">
         <v>12.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="BN21" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BO21" t="n">
         <v>3.35</v>
@@ -5875,10 +5875,10 @@
         <v>5.7</v>
       </c>
       <c r="BR21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS21" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BT21" t="n">
         <v>14</v>
@@ -5890,13 +5890,13 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -5937,16 +5937,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G22" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H22" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I22" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J22" t="n">
         <v>3.45</v>
@@ -5961,13 +5961,13 @@
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
         <v>1.84</v>
@@ -5976,7 +5976,7 @@
         <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T22" t="n">
         <v>1.64</v>
@@ -5985,10 +5985,10 @@
         <v>2.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X22" t="n">
         <v>17.5</v>
@@ -6039,7 +6039,7 @@
         <v>320</v>
       </c>
       <c r="AN22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="n">
         <v>44</v>
@@ -6066,7 +6066,7 @@
         <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AX22" t="n">
         <v>13</v>
@@ -6078,25 +6078,25 @@
         <v>13</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="BB22" t="n">
         <v>29</v>
       </c>
       <c r="BC22" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD22" t="n">
         <v>26</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.4</v>
+        <v>23</v>
       </c>
       <c r="BF22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BH22" t="n">
         <v>3.8</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>2.08</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I23" t="n">
         <v>4.5</v>
@@ -6209,34 +6209,34 @@
         <v>3.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O23" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R23" t="n">
         <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T23" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V23" t="n">
         <v>1.28</v>
@@ -6278,7 +6278,7 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="AJ23" t="n">
         <v>29</v>
@@ -6296,7 +6296,7 @@
         <v>19</v>
       </c>
       <c r="AO23" t="n">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AP23" t="n">
         <v>9.6</v>
@@ -6308,7 +6308,7 @@
         <v>23</v>
       </c>
       <c r="AS23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT23" t="n">
         <v>7.4</v>
@@ -6332,7 +6332,7 @@
         <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB23" t="n">
         <v>20</v>
@@ -6344,7 +6344,7 @@
         <v>28</v>
       </c>
       <c r="BE23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BF23" t="n">
         <v>14</v>
@@ -6353,58 +6353,58 @@
         <v>4.9</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO23" t="n">
         <v>3.65</v>
       </c>
       <c r="BP23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BR23" t="n">
         <v>32</v>
       </c>
       <c r="BS23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT23" t="n">
         <v>7.6</v>
       </c>
       <c r="BU23" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BX23" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G24" t="n">
         <v>6</v>
@@ -6454,46 +6454,46 @@
         <v>1.69</v>
       </c>
       <c r="I24" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T24" t="n">
         <v>1.86</v>
       </c>
       <c r="U24" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V24" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="W24" t="n">
         <v>1.2</v>
@@ -6514,31 +6514,31 @@
         <v>34</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="AE24" t="n">
         <v>18.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AG24" t="n">
         <v>44</v>
       </c>
       <c r="AH24" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AI24" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AJ24" t="n">
         <v>900</v>
       </c>
       <c r="AK24" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="AL24" t="n">
         <v>700</v>
@@ -6550,58 +6550,58 @@
         <v>110</v>
       </c>
       <c r="AO24" t="n">
-        <v>27</v>
+        <v>10.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AU24" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AV24" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW24" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="AY24" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA24" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BB24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE24" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BF24" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="BG24" t="n">
         <v>8.199999999999999</v>
@@ -6616,31 +6616,31 @@
         <v>11</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN24" t="n">
         <v>9.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT24" t="n">
         <v>4.4</v>
@@ -6658,17 +6658,17 @@
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA24" t="n">
         <v>7.4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>4.8</v>
       </c>
       <c r="G25" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H25" t="n">
         <v>1.61</v>
@@ -6801,13 +6801,13 @@
         <v>55</v>
       </c>
       <c r="AN25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO25" t="n">
         <v>5.1</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ25" t="n">
         <v>12.5</v>
@@ -6831,7 +6831,7 @@
         <v>13</v>
       </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY25" t="n">
         <v>15.5</v>
@@ -6846,10 +6846,10 @@
         <v>11</v>
       </c>
       <c r="BC25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE25" t="n">
         <v>36</v>
@@ -6870,31 +6870,31 @@
         <v>9</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN25" t="n">
         <v>9.6</v>
       </c>
       <c r="BO25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BP25" t="n">
         <v>34</v>
       </c>
       <c r="BQ25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR25" t="n">
         <v>32</v>
       </c>
       <c r="BS25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT25" t="n">
         <v>5.1</v>
@@ -6906,23 +6906,23 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BW25" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BX25" t="n">
         <v>17.5</v>
       </c>
       <c r="BY25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CA25" t="n">
         <v>5.8</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -6953,58 +6953,58 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="G26" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="H26" t="n">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="I26" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P26" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="R26" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="S26" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="U26" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="V26" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W26" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="X26" t="n">
         <v>80</v>
@@ -7016,82 +7016,82 @@
         <v>50</v>
       </c>
       <c r="AA26" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB26" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="AC26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AF26" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AG26" t="n">
         <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AJ26" t="n">
         <v>500</v>
       </c>
       <c r="AK26" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="AL26" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AM26" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN26" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP26" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AR26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX26" t="n">
         <v>16.5</v>
       </c>
-      <c r="AS26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA26" t="n">
         <v>14.5</v>
@@ -7103,25 +7103,25 @@
         <v>17</v>
       </c>
       <c r="BD26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE26" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BF26" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG26" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH26" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BJ26" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK26" t="n">
         <v>4.3</v>
@@ -7133,50 +7133,50 @@
         <v>7.4</v>
       </c>
       <c r="BN26" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BS26" t="n">
         <v>6.2</v>
       </c>
       <c r="BT26" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BU26" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BW26" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BX26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
         <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O27" t="n">
         <v>1.14</v>
@@ -7240,10 +7240,10 @@
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R27" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S27" t="n">
         <v>2.12</v>
@@ -7288,7 +7288,7 @@
         <v>500</v>
       </c>
       <c r="AG27" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH27" t="n">
         <v>60</v>
@@ -7318,13 +7318,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR27" t="n">
         <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT27" t="n">
         <v>7.2</v>
@@ -7378,34 +7378,34 @@
         <v>9</v>
       </c>
       <c r="BK27" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BN27" t="n">
         <v>8.6</v>
       </c>
       <c r="BO27" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BT27" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU27" t="n">
         <v>4.2</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
         <v>1.64</v>
       </c>
       <c r="G28" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H28" t="n">
         <v>5.2</v>
@@ -7476,13 +7476,13 @@
         <v>4.2</v>
       </c>
       <c r="K28" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N28" t="n">
         <v>4.7</v>
@@ -7494,25 +7494,25 @@
         <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R28" t="n">
         <v>1.51</v>
       </c>
       <c r="S28" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U28" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V28" t="n">
         <v>1.2</v>
       </c>
       <c r="W28" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X28" t="n">
         <v>21</v>
@@ -7521,13 +7521,13 @@
         <v>23</v>
       </c>
       <c r="Z28" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AA28" t="n">
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC28" t="n">
         <v>10.5</v>
@@ -7563,7 +7563,7 @@
         <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AO28" t="n">
         <v>75</v>
@@ -7575,13 +7575,13 @@
         <v>18</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU28" t="n">
         <v>8.6</v>
@@ -7602,7 +7602,7 @@
         <v>14.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB28" t="n">
         <v>12.5</v>
@@ -7614,25 +7614,25 @@
         <v>14.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH28" t="n">
         <v>4.2</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ28" t="n">
         <v>10</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
@@ -7656,35 +7656,35 @@
         <v>23</v>
       </c>
       <c r="BS28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT28" t="n">
         <v>9.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV28" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX28" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ28" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA28" t="n">
         <v>6.6</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -7715,25 +7715,25 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H29" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="I29" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="J29" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
@@ -7745,28 +7745,28 @@
         <v>1.04</v>
       </c>
       <c r="P29" t="n">
-        <v>2.8</v>
+        <v>1.08</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="R29" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="S29" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>4.8</v>
       </c>
       <c r="V29" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W29" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X29" t="n">
         <v>500</v>
@@ -7784,7 +7784,7 @@
         <v>500</v>
       </c>
       <c r="AC29" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AD29" t="n">
         <v>500</v>
@@ -7796,13 +7796,13 @@
         <v>500</v>
       </c>
       <c r="AG29" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AH29" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AI29" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AJ29" t="n">
         <v>900</v>
@@ -7811,134 +7811,134 @@
         <v>500</v>
       </c>
       <c r="AL29" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AM29" t="n">
         <v>500</v>
       </c>
       <c r="AN29" t="n">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
-        <v>29</v>
+        <v>3.5</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.38</v>
+        <v>3.7</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.33</v>
+        <v>3.35</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.35</v>
+        <v>3.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.36</v>
+        <v>3.55</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.36</v>
+        <v>3.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.34</v>
+        <v>3.3</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.32</v>
+        <v>3.3</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.35</v>
+        <v>3.55</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.36</v>
+        <v>3.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.36</v>
+        <v>3.3</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.32</v>
+        <v>3.05</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.37</v>
+        <v>3.1</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.37</v>
+        <v>3.7</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.36</v>
+        <v>3.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.35</v>
+        <v>3.3</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.38</v>
+        <v>3.7</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.55</v>
+        <v>3.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.32</v>
+        <v>2.88</v>
       </c>
       <c r="BH29" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BI29" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BJ29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BL29" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BM29" t="n">
         <v>6.4</v>
       </c>
       <c r="BN29" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BO29" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP29" t="n">
         <v>25</v>
       </c>
       <c r="BQ29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BS29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BT29" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BU29" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BV29" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BW29" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BX29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BY29" t="n">
         <v>5.1</v>
       </c>
       <c r="BZ29" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="CA29" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -7969,19 +7969,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G30" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="H30" t="n">
         <v>5.3</v>
       </c>
       <c r="I30" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J30" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K30" t="n">
         <v>3.55</v>
@@ -8002,7 +8002,7 @@
         <v>1.58</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R30" t="n">
         <v>1.21</v>
@@ -8020,13 +8020,13 @@
         <v>1.21</v>
       </c>
       <c r="W30" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="X30" t="n">
         <v>9.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="Z30" t="n">
         <v>95</v>
@@ -8116,10 +8116,10 @@
         <v>19</v>
       </c>
       <c r="BC30" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BD30" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="BE30" t="n">
         <v>16</v>
@@ -8155,7 +8155,7 @@
         <v>3.85</v>
       </c>
       <c r="BP30" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ30" t="n">
         <v>7.8</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -8223,22 +8223,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="G31" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H31" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I31" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L31" t="n">
         <v>1.45</v>
@@ -8247,43 +8247,43 @@
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P31" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T31" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U31" t="n">
         <v>1.98</v>
       </c>
       <c r="V31" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X31" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA31" t="n">
         <v>900</v>
@@ -8328,7 +8328,7 @@
         <v>500</v>
       </c>
       <c r="AO31" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AP31" t="n">
         <v>10</v>
@@ -8367,7 +8367,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB31" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC31" t="n">
         <v>8.199999999999999</v>
@@ -8382,10 +8382,10 @@
         <v>8.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI31" t="n">
         <v>2.7</v>
@@ -8400,7 +8400,7 @@
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN31" t="n">
         <v>7.2</v>
@@ -8412,13 +8412,13 @@
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT31" t="n">
         <v>5.2</v>
@@ -8427,26 +8427,26 @@
         <v>4.4</v>
       </c>
       <c r="BV31" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW31" t="n">
         <v>7.2</v>
       </c>
       <c r="BX31" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY31" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA31" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8731,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="G33" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="H33" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I33" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J33" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K33" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L33" t="n">
         <v>1.49</v>
@@ -8761,7 +8761,7 @@
         <v>1.42</v>
       </c>
       <c r="P33" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q33" t="n">
         <v>2.3</v>
@@ -8773,31 +8773,31 @@
         <v>4.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U33" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V33" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W33" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="X33" t="n">
         <v>14</v>
       </c>
       <c r="Y33" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA33" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AB33" t="n">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="AC33" t="n">
         <v>8.4</v>
@@ -8806,34 +8806,34 @@
         <v>32</v>
       </c>
       <c r="AE33" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG33" t="n">
         <v>970</v>
       </c>
       <c r="AH33" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI33" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ33" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AK33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL33" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM33" t="n">
         <v>210</v>
       </c>
       <c r="AN33" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO33" t="n">
         <v>200</v>
@@ -8842,13 +8842,13 @@
         <v>10</v>
       </c>
       <c r="AQ33" t="n">
-        <v>13.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR33" t="n">
-        <v>36</v>
+        <v>3.55</v>
       </c>
       <c r="AS33" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="AT33" t="n">
         <v>6.2</v>
@@ -8857,49 +8857,49 @@
         <v>7.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AX33" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY33" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD33" t="n">
         <v>7.4</v>
       </c>
-      <c r="BA33" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BE33" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="BF33" t="n">
         <v>13</v>
       </c>
       <c r="BG33" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="BH33" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK33" t="n">
         <v>8.6</v>
@@ -8908,53 +8908,53 @@
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO33" t="n">
         <v>3.7</v>
       </c>
       <c r="BP33" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ33" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BT33" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU33" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BZ33" t="n">
         <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -8985,19 +8985,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G34" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="H34" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="I34" t="n">
         <v>3.05</v>
       </c>
       <c r="J34" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
         <v>3.3</v>
@@ -9015,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="G2" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.35</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T2" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.84</v>
-      </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="X2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AN2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV2" t="n">
         <v>16.5</v>
       </c>
-      <c r="AO2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>15</v>
-      </c>
       <c r="AW2" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
         <v>85</v>
       </c>
       <c r="BF2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11.5</v>
+        <v>110</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BP2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BQ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU2" t="n">
         <v>6.8</v>
       </c>
-      <c r="BR2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>6</v>
-      </c>
       <c r="BV2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
         <v>10</v>
       </c>
       <c r="BZ2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="G3" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="T3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U3" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA3" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK3" t="n">
         <v>18.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM3" t="n">
         <v>90</v>
       </c>
       <c r="AN3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO3" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AP3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AS3" t="n">
         <v>70</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BB3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BC3" t="n">
         <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE3" t="n">
         <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BG3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BV3" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -1371,55 +1371,55 @@
         <v>1.82</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="O4" t="n">
         <v>1.12</v>
       </c>
       <c r="P4" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="R4" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Y4" t="n">
         <v>34</v>
@@ -1428,25 +1428,25 @@
         <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
         <v>38</v>
       </c>
       <c r="AF4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
         <v>14.5</v>
@@ -1455,49 +1455,49 @@
         <v>36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
         <v>15.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AQ4" t="n">
         <v>29</v>
       </c>
       <c r="AR4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS4" t="n">
         <v>75</v>
       </c>
       <c r="AT4" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AU4" t="n">
         <v>11.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
         <v>34</v>
       </c>
       <c r="AX4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
@@ -1509,86 +1509,86 @@
         <v>30</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
         <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BL4" t="n">
         <v>55</v>
       </c>
       <c r="BM4" t="n">
-        <v>14.5</v>
+        <v>42</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP4" t="n">
         <v>11</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BT4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="CA4" t="n">
         <v>8.4</v>
       </c>
-      <c r="BU4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>10</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H5" t="n">
         <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L5" t="n">
         <v>1.63</v>
@@ -1649,28 +1649,28 @@
         <v>1.6</v>
       </c>
       <c r="P5" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S5" t="n">
         <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V5" t="n">
         <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="X5" t="n">
         <v>7.8</v>
@@ -1679,7 +1679,7 @@
         <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
@@ -1691,7 +1691,7 @@
         <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
@@ -1709,10 +1709,10 @@
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AL5" t="n">
         <v>460</v>
@@ -1721,7 +1721,7 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
@@ -1733,13 +1733,13 @@
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
@@ -1748,7 +1748,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX5" t="n">
         <v>9.199999999999999</v>
@@ -1757,31 +1757,31 @@
         <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
         <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BI5" t="n">
         <v>2.18</v>
@@ -1802,7 +1802,7 @@
         <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP5" t="n">
         <v>18.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -1873,31 +1873,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="K6" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
         <v>1.16</v>
       </c>
       <c r="N6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O6" t="n">
         <v>1.67</v>
@@ -1906,10 +1906,10 @@
         <v>1.39</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S6" t="n">
         <v>6.6</v>
@@ -1921,10 +1921,10 @@
         <v>1.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
         <v>13.5</v>
@@ -1975,10 +1975,10 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
         <v>3.85</v>
@@ -2029,10 +2029,10 @@
         <v>8</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="BH6" t="n">
         <v>2.54</v>
@@ -2056,7 +2056,7 @@
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G7" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H7" t="n">
         <v>3.35</v>
@@ -2139,10 +2139,10 @@
         <v>3.55</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.34</v>
@@ -2151,19 +2151,19 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
         <v>1.71</v>
       </c>
       <c r="R7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
         <v>2.8</v>
@@ -2172,13 +2172,13 @@
         <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
         <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -2193,10 +2193,10 @@
         <v>150</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD7" t="n">
         <v>16</v>
@@ -2205,7 +2205,7 @@
         <v>46</v>
       </c>
       <c r="AF7" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -2235,7 +2235,7 @@
         <v>38</v>
       </c>
       <c r="AP7" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>14.5</v>
@@ -2250,7 +2250,7 @@
         <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
         <v>13</v>
@@ -2259,7 +2259,7 @@
         <v>25</v>
       </c>
       <c r="AX7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY7" t="n">
         <v>9.6</v>
@@ -2271,7 +2271,7 @@
         <v>34</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC7" t="n">
         <v>17.5</v>
@@ -2289,7 +2289,7 @@
         <v>22</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI7" t="n">
         <v>3.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -2384,49 +2384,49 @@
         <v>2.14</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="T8" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="U8" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V8" t="n">
         <v>1.39</v>
@@ -2435,31 +2435,31 @@
         <v>1.84</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG8" t="n">
         <v>11</v>
@@ -2468,91 +2468,91 @@
         <v>15.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AK8" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM8" t="n">
-        <v>190</v>
+        <v>65</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ8" t="n">
         <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>13.5</v>
       </c>
-      <c r="AW8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC8" t="n">
         <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2564,7 +2564,7 @@
         <v>5.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP8" t="n">
         <v>14.5</v>
@@ -2582,19 +2582,19 @@
         <v>7</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BV8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW8" t="n">
         <v>10</v>
       </c>
       <c r="BX8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -2635,55 +2635,55 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G9" t="n">
         <v>1.55</v>
       </c>
       <c r="H9" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="O9" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
         <v>2.8</v>
@@ -2692,7 +2692,7 @@
         <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="Z9" t="n">
         <v>120</v>
@@ -2701,7 +2701,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AC9" t="n">
         <v>42</v>
@@ -2713,7 +2713,7 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG9" t="n">
         <v>12.5</v>
@@ -2728,7 +2728,7 @@
         <v>16</v>
       </c>
       <c r="AK9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL9" t="n">
         <v>380</v>
@@ -2743,16 +2743,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ9" t="n">
         <v>9</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT9" t="n">
         <v>4.6</v>
@@ -2764,7 +2764,7 @@
         <v>18</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX9" t="n">
         <v>5.9</v>
@@ -2773,46 +2773,46 @@
         <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BC9" t="n">
         <v>16.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH9" t="n">
         <v>2.98</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="BJ9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
         <v>3.75</v>
@@ -2830,7 +2830,7 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT9" t="n">
         <v>14</v>
@@ -2842,23 +2842,23 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J10" t="n">
         <v>2.76</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.78</v>
       </c>
       <c r="K10" t="n">
         <v>3.1</v>
@@ -2913,13 +2913,13 @@
         <v>1.14</v>
       </c>
       <c r="N10" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O10" t="n">
         <v>1.59</v>
       </c>
       <c r="P10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q10" t="n">
         <v>2.84</v>
@@ -2928,19 +2928,19 @@
         <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T10" t="n">
         <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V10" t="n">
         <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X10" t="n">
         <v>14.5</v>
@@ -2961,7 +2961,7 @@
         <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
@@ -2997,19 +2997,19 @@
         <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="AU10" t="n">
         <v>5.5</v>
@@ -3021,34 +3021,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AX10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA10" t="n">
         <v>5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
         <v>30</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.8</v>
+        <v>3.25</v>
       </c>
       <c r="BH10" t="n">
         <v>2.7</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H11" t="n">
         <v>4.5</v>
@@ -3155,10 +3155,10 @@
         <v>5.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.64</v>
@@ -3167,13 +3167,13 @@
         <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q11" t="n">
         <v>2.84</v>
@@ -3182,10 +3182,10 @@
         <v>1.15</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
         <v>1.6</v>
@@ -3194,7 +3194,7 @@
         <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="X11" t="n">
         <v>17</v>
@@ -3209,7 +3209,7 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC11" t="n">
         <v>9.199999999999999</v>
@@ -3248,7 +3248,7 @@
         <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
         <v>4.2</v>
@@ -3257,22 +3257,22 @@
         <v>8</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AV11" t="n">
         <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX11" t="n">
         <v>7.4</v>
@@ -3284,25 +3284,25 @@
         <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BC11" t="n">
         <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="BH11" t="n">
         <v>2.66</v>
@@ -3314,7 +3314,7 @@
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G12" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H12" t="n">
         <v>3.35</v>
@@ -3409,10 +3409,10 @@
         <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="K12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.66</v>
@@ -3427,7 +3427,7 @@
         <v>1.63</v>
       </c>
       <c r="P12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q12" t="n">
         <v>2.96</v>
@@ -3448,7 +3448,7 @@
         <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X12" t="n">
         <v>500</v>
@@ -3499,22 +3499,22 @@
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
         <v>3.85</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AR12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS12" t="n">
         <v>1.39</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.4</v>
       </c>
       <c r="AT12" t="n">
         <v>4.2</v>
@@ -3523,40 +3523,40 @@
         <v>4.2</v>
       </c>
       <c r="AV12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BB12" t="n">
         <v>1.38</v>
       </c>
-      <c r="AW12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BC12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BD12" t="n">
         <v>1.39</v>
       </c>
-      <c r="BD12" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BE12" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BF12" t="n">
         <v>1.55</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H13" t="n">
         <v>2.68</v>
@@ -3663,10 +3663,10 @@
         <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L13" t="n">
         <v>1.7</v>
@@ -3678,10 +3678,10 @@
         <v>2.24</v>
       </c>
       <c r="O13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P13" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Q13" t="n">
         <v>3.15</v>
@@ -3693,10 +3693,10 @@
         <v>6.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U13" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V13" t="n">
         <v>1.5</v>
@@ -3717,13 +3717,13 @@
         <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
         <v>55</v>
@@ -3738,10 +3738,10 @@
         <v>29</v>
       </c>
       <c r="AI13" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK13" t="n">
         <v>150</v>
@@ -3756,7 +3756,7 @@
         <v>110</v>
       </c>
       <c r="AO13" t="n">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
         <v>5.4</v>
@@ -3768,7 +3768,7 @@
         <v>12</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3780,13 +3780,13 @@
         <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
         <v>7</v>
@@ -3798,19 +3798,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE13" t="n">
         <v>9</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13" t="n">
         <v>2.52</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G14" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="H14" t="n">
         <v>5.3</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -3935,49 +3935,49 @@
         <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W14" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
         <v>11.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AE14" t="n">
         <v>700</v>
@@ -3989,40 +3989,40 @@
         <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
-        <v>260</v>
+        <v>540</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
         <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
         <v>700</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>6.6</v>
@@ -4031,46 +4031,46 @@
         <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AW14" t="n">
         <v>50</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB14" t="n">
         <v>15.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD14" t="n">
         <v>28</v>
       </c>
       <c r="BE14" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="BF14" t="n">
         <v>11</v>
       </c>
       <c r="BG14" t="n">
-        <v>75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH14" t="n">
         <v>3.1</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BJ14" t="n">
         <v>12</v>
@@ -4091,25 +4091,25 @@
         <v>3.5</v>
       </c>
       <c r="BP14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ14" t="n">
         <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS14" t="n">
         <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BU14" t="n">
         <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -4162,58 +4162,58 @@
         <v>2.18</v>
       </c>
       <c r="G15" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H15" t="n">
         <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J15" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="K15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.14</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.16</v>
-      </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="Y15" t="n">
         <v>11</v>
@@ -4225,13 +4225,13 @@
         <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC15" t="n">
         <v>7.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
         <v>500</v>
@@ -4240,7 +4240,7 @@
         <v>13</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
         <v>65</v>
@@ -4249,10 +4249,10 @@
         <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AL15" t="n">
         <v>500</v>
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ15" t="n">
         <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS15" t="n">
         <v>9.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU15" t="n">
         <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW15" t="n">
         <v>9.4</v>
@@ -4297,7 +4297,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
         <v>9.6</v>
@@ -4306,7 +4306,7 @@
         <v>8</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD15" t="n">
         <v>9.199999999999999</v>
@@ -4321,13 +4321,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="BJ15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK15" t="n">
         <v>1.01</v>
@@ -4342,10 +4342,10 @@
         <v>5</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ15" t="n">
         <v>1.01</v>
@@ -4360,7 +4360,7 @@
         <v>7.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>1.94</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
         <v>5.6</v>
@@ -4428,7 +4428,7 @@
         <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L16" t="n">
         <v>1.54</v>
@@ -4443,16 +4443,16 @@
         <v>1.49</v>
       </c>
       <c r="P16" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q16" t="n">
         <v>2.48</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T16" t="n">
         <v>2.06</v>
@@ -4464,31 +4464,31 @@
         <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="X16" t="n">
         <v>10.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA16" t="n">
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="AF16" t="n">
         <v>11.5</v>
@@ -4503,7 +4503,7 @@
         <v>540</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
         <v>27</v>
@@ -4515,128 +4515,128 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>700</v>
       </c>
       <c r="AP16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ16" t="n">
         <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB16" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC16" t="n">
         <v>21</v>
       </c>
       <c r="BD16" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF16" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ16" t="n">
         <v>12.5</v>
       </c>
       <c r="BK16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT16" t="n">
         <v>9</v>
       </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BU16" t="n">
         <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW16" t="n">
         <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY16" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="CA16" t="n">
         <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
         <v>1.73</v>
       </c>
       <c r="H17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
         <v>8.800000000000001</v>
@@ -4715,10 +4715,10 @@
         <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X17" t="n">
         <v>8.4</v>
@@ -4772,7 +4772,7 @@
         <v>23</v>
       </c>
       <c r="AO17" t="n">
-        <v>570</v>
+        <v>620</v>
       </c>
       <c r="AP17" t="n">
         <v>6.8</v>
@@ -4781,7 +4781,7 @@
         <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AS17" t="n">
         <v>8</v>
@@ -4805,7 +4805,7 @@
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>23</v>
+        <v>6.6</v>
       </c>
       <c r="BA17" t="n">
         <v>7.8</v>
@@ -4817,7 +4817,7 @@
         <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BE17" t="n">
         <v>8</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G18" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I18" t="n">
         <v>3.2</v>
       </c>
-      <c r="I18" t="n">
-        <v>3.3</v>
-      </c>
       <c r="J18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
         <v>4.2</v>
@@ -4945,142 +4945,142 @@
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O18" t="n">
         <v>1.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q18" t="n">
         <v>1.63</v>
       </c>
       <c r="R18" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S18" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="T18" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X18" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="Y18" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="Z18" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>440</v>
       </c>
       <c r="AB18" t="n">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AC18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX18" t="n">
         <v>14</v>
       </c>
-      <c r="AD18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9</v>
-      </c>
       <c r="AY18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="BC18" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="BF18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BH18" t="n">
         <v>4.4</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G19" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H19" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I19" t="n">
         <v>5.6</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.31</v>
@@ -5199,16 +5199,16 @@
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O19" t="n">
         <v>1.21</v>
       </c>
       <c r="P19" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R19" t="n">
         <v>1.57</v>
@@ -5217,19 +5217,19 @@
         <v>2.66</v>
       </c>
       <c r="T19" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="U19" t="n">
         <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y19" t="n">
         <v>26</v>
@@ -5238,22 +5238,22 @@
         <v>46</v>
       </c>
       <c r="AA19" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AB19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF19" t="n">
         <v>12</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>12.5</v>
       </c>
       <c r="AG19" t="n">
         <v>10</v>
@@ -5262,79 +5262,79 @@
         <v>18</v>
       </c>
       <c r="AI19" t="n">
-        <v>700</v>
+        <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AM19" t="n">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO19" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="AP19" t="n">
         <v>19.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="AS19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT19" t="n">
         <v>10</v>
       </c>
-      <c r="AT19" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AU19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AW19" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AX19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB19" t="n">
         <v>15</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BC19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD19" t="n">
         <v>24</v>
       </c>
-      <c r="BB19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>15</v>
-      </c>
       <c r="BE19" t="n">
-        <v>9.6</v>
+        <v>65</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BH19" t="n">
         <v>4.3</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G20" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="H20" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="I20" t="n">
         <v>2.72</v>
@@ -5453,10 +5453,10 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P20" t="n">
         <v>2.06</v>
@@ -5465,25 +5465,25 @@
         <v>1.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
         <v>3.25</v>
       </c>
       <c r="T20" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U20" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
         <v>1.58</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y20" t="n">
         <v>14.5</v>
@@ -5492,10 +5492,10 @@
         <v>22</v>
       </c>
       <c r="AA20" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="AB20" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC20" t="n">
         <v>8.4</v>
@@ -5507,7 +5507,7 @@
         <v>34</v>
       </c>
       <c r="AF20" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
         <v>15</v>
@@ -5519,10 +5519,10 @@
         <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AK20" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AL20" t="n">
         <v>46</v>
@@ -5531,22 +5531,22 @@
         <v>320</v>
       </c>
       <c r="AN20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO20" t="n">
         <v>25</v>
       </c>
       <c r="AP20" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ20" t="n">
         <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS20" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
@@ -5558,37 +5558,37 @@
         <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY20" t="n">
         <v>11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="BB20" t="n">
         <v>34</v>
       </c>
       <c r="BC20" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.7</v>
+        <v>60</v>
       </c>
       <c r="BF20" t="n">
         <v>20</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BH20" t="n">
         <v>3.6</v>
@@ -5597,16 +5597,16 @@
         <v>3.25</v>
       </c>
       <c r="BJ20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BN20" t="n">
         <v>6</v>
@@ -5618,16 +5618,16 @@
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT20" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU20" t="n">
         <v>5.1</v>
@@ -5636,13 +5636,13 @@
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
         <v>14</v>
@@ -5701,40 +5701,40 @@
         <v>6.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R21" t="n">
         <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="T21" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="V21" t="n">
         <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X21" t="n">
         <v>22</v>
@@ -5746,7 +5746,7 @@
         <v>120</v>
       </c>
       <c r="AA21" t="n">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="AB21" t="n">
         <v>9</v>
@@ -5755,10 +5755,10 @@
         <v>14</v>
       </c>
       <c r="AD21" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AE21" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AF21" t="n">
         <v>8</v>
@@ -5767,19 +5767,19 @@
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI21" t="n">
-        <v>470</v>
+        <v>170</v>
       </c>
       <c r="AJ21" t="n">
         <v>10.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM21" t="n">
         <v>180</v>
@@ -5788,7 +5788,7 @@
         <v>5.2</v>
       </c>
       <c r="AO21" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AP21" t="n">
         <v>19.5</v>
@@ -5797,10 +5797,10 @@
         <v>34</v>
       </c>
       <c r="AR21" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AT21" t="n">
         <v>7.6</v>
@@ -5812,7 +5812,7 @@
         <v>36</v>
       </c>
       <c r="AW21" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AX21" t="n">
         <v>6.8</v>
@@ -5824,7 +5824,7 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB21" t="n">
         <v>9</v>
@@ -5836,13 +5836,13 @@
         <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BF21" t="n">
         <v>4.7</v>
       </c>
       <c r="BG21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH21" t="n">
         <v>4.2</v>
@@ -5854,13 +5854,13 @@
         <v>12.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN21" t="n">
         <v>3.75</v>
@@ -5878,7 +5878,7 @@
         <v>24</v>
       </c>
       <c r="BS21" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT21" t="n">
         <v>14</v>
@@ -5890,13 +5890,13 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -5940,10 +5940,10 @@
         <v>2.52</v>
       </c>
       <c r="G22" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H22" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I22" t="n">
         <v>3.1</v>
@@ -5967,7 +5967,7 @@
         <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
         <v>1.84</v>
@@ -5988,7 +5988,7 @@
         <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X22" t="n">
         <v>17.5</v>
@@ -5997,7 +5997,7 @@
         <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
         <v>50</v>
@@ -6039,10 +6039,10 @@
         <v>320</v>
       </c>
       <c r="AN22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="AP22" t="n">
         <v>13</v>
@@ -6051,13 +6051,13 @@
         <v>11.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AS22" t="n">
         <v>34</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU22" t="n">
         <v>7</v>
@@ -6069,13 +6069,13 @@
         <v>25</v>
       </c>
       <c r="AX22" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
         <v>32</v>
@@ -6093,7 +6093,7 @@
         <v>23</v>
       </c>
       <c r="BF22" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BG22" t="n">
         <v>21</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="G23" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I23" t="n">
         <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L23" t="n">
         <v>1.44</v>
@@ -6236,13 +6236,13 @@
         <v>1.89</v>
       </c>
       <c r="U23" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X23" t="n">
         <v>15</v>
@@ -6257,16 +6257,16 @@
         <v>900</v>
       </c>
       <c r="AB23" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD23" t="n">
         <v>21</v>
       </c>
       <c r="AE23" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AF23" t="n">
         <v>14.5</v>
@@ -6278,10 +6278,10 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="AJ23" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK23" t="n">
         <v>26</v>
@@ -6296,10 +6296,10 @@
         <v>19</v>
       </c>
       <c r="AO23" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
         <v>12.5</v>
@@ -6308,7 +6308,7 @@
         <v>23</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.9</v>
+        <v>60</v>
       </c>
       <c r="AT23" t="n">
         <v>7.4</v>
@@ -6317,40 +6317,40 @@
         <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.8</v>
+        <v>36</v>
       </c>
       <c r="AX23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.8</v>
+        <v>46</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
         <v>19.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.9</v>
+        <v>80</v>
       </c>
       <c r="BF23" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.9</v>
+        <v>42</v>
       </c>
       <c r="BH23" t="n">
         <v>3.25</v>
@@ -6362,7 +6362,7 @@
         <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
@@ -6374,13 +6374,13 @@
         <v>4.7</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BP23" t="n">
         <v>15</v>
       </c>
       <c r="BQ23" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BR23" t="n">
         <v>32</v>
@@ -6392,7 +6392,7 @@
         <v>7.6</v>
       </c>
       <c r="BU23" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6445,230 +6445,230 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H24" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="I24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P24" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="T24" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U24" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X24" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z24" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AA24" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AB24" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AC24" t="n">
         <v>9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF24" t="n">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="AG24" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI24" t="n">
         <v>36</v>
       </c>
-      <c r="AI24" t="n">
-        <v>95</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AK24" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AL24" t="n">
-        <v>700</v>
+        <v>190</v>
       </c>
       <c r="AM24" t="n">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AO24" t="n">
         <v>10.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV24" t="n">
         <v>9</v>
       </c>
-      <c r="AS24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV24" t="n">
+      <c r="AW24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG24" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AW24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ24" t="n">
+      <c r="BH24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
         <v>11</v>
       </c>
-      <c r="BA24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC24" t="n">
+      <c r="BN24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
         <v>9.6</v>
       </c>
-      <c r="BD24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE24" t="n">
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>9.6</v>
       </c>
       <c r="BT24" t="n">
         <v>4.4</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BV24" t="n">
         <v>11</v>
       </c>
       <c r="BW24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BX24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>8</v>
-      </c>
       <c r="BZ24" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="CA24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6702,227 +6702,227 @@
         <v>4.8</v>
       </c>
       <c r="G25" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H25" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="I25" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="J25" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K25" t="n">
         <v>5.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="M25" t="n">
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P25" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="R25" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="S25" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="U25" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="V25" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X25" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Y25" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="Z25" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AA25" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AC25" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AD25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
         <v>15.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AG25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ25" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AK25" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AL25" t="n">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="AM25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT25" t="n">
         <v>32</v>
       </c>
-      <c r="AO25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>16</v>
-      </c>
       <c r="AU25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV25" t="n">
         <v>10</v>
       </c>
-      <c r="AV25" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AW25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX25" t="n">
-        <v>9.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="AY25" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AZ25" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB25" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="BC25" t="n">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="BD25" t="n">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BE25" t="n">
         <v>36</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BH25" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BI25" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BJ25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS25" t="n">
         <v>9</v>
       </c>
-      <c r="BK25" t="n">
+      <c r="BT25" t="n">
         <v>5.4</v>
       </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>34</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BU25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BV25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BW25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BX25" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BY25" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ25" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="CA25" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6956,82 +6956,82 @@
         <v>2.4</v>
       </c>
       <c r="G26" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="H26" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J26" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P26" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="R26" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="S26" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="T26" t="n">
         <v>1.45</v>
       </c>
       <c r="U26" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="V26" t="n">
         <v>1.51</v>
       </c>
       <c r="W26" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="X26" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y26" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Z26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA26" t="n">
         <v>50</v>
       </c>
-      <c r="AA26" t="n">
-        <v>500</v>
-      </c>
       <c r="AB26" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AF26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG26" t="n">
         <v>12.5</v>
@@ -7040,143 +7040,143 @@
         <v>14.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AJ26" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AK26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP26" t="n">
         <v>23</v>
       </c>
-      <c r="AL26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO26" t="n">
+      <c r="AQ26" t="n">
         <v>17</v>
       </c>
-      <c r="AP26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>18</v>
-      </c>
       <c r="AR26" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV26" t="n">
         <v>12.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
         <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BB26" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC26" t="n">
         <v>18</v>
       </c>
-      <c r="BC26" t="n">
-        <v>17</v>
-      </c>
       <c r="BD26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="BF26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH26" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BJ26" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BN26" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO26" t="n">
         <v>4.7</v>
       </c>
       <c r="BP26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS26" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BT26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU26" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW26" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BX26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY26" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BZ26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="G27" t="n">
         <v>4.4</v>
       </c>
       <c r="H27" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="I27" t="n">
         <v>1.88</v>
       </c>
       <c r="J27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L27" t="n">
         <v>1.24</v>
@@ -7240,10 +7240,10 @@
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R27" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S27" t="n">
         <v>2.12</v>
@@ -7258,7 +7258,7 @@
         <v>2.12</v>
       </c>
       <c r="W27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
         <v>500</v>
@@ -7309,25 +7309,25 @@
         <v>580</v>
       </c>
       <c r="AN27" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO27" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ27" t="n">
         <v>8.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS27" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="AT27" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU27" t="n">
         <v>6.4</v>
@@ -7336,37 +7336,37 @@
         <v>6.2</v>
       </c>
       <c r="AW27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY27" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>6.4</v>
       </c>
       <c r="AZ27" t="n">
         <v>6</v>
       </c>
       <c r="BA27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH27" t="n">
         <v>5.3</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -7461,76 +7461,76 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="G28" t="n">
         <v>1.7</v>
       </c>
       <c r="H28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I28" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K28" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M28" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="R28" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="T28" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="U28" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="V28" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W28" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X28" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z28" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AA28" t="n">
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD28" t="n">
         <v>23</v>
@@ -7539,13 +7539,13 @@
         <v>160</v>
       </c>
       <c r="AF28" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG28" t="n">
         <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI28" t="n">
         <v>65</v>
@@ -7554,85 +7554,85 @@
         <v>17.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AO28" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP28" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
         <v>18</v>
       </c>
       <c r="AR28" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="AS28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV28" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB28" t="n">
         <v>14.5</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>12.5</v>
       </c>
       <c r="BC28" t="n">
         <v>14</v>
       </c>
       <c r="BD28" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BE28" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="BF28" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BH28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BJ28" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
@@ -7641,50 +7641,50 @@
         <v>10</v>
       </c>
       <c r="BN28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ28" t="n">
         <v>5.5</v>
       </c>
       <c r="BR28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT28" t="n">
         <v>9.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV28" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX28" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BY28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ28" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA28" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H29" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="I29" t="n">
         <v>1.89</v>
@@ -7730,43 +7730,43 @@
         <v>4.9</v>
       </c>
       <c r="K29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="P29" t="n">
-        <v>1.08</v>
+        <v>7.4</v>
       </c>
       <c r="Q29" t="n">
         <v>1.11</v>
       </c>
       <c r="R29" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="S29" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T29" t="n">
         <v>1.2</v>
       </c>
       <c r="U29" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="V29" t="n">
         <v>2.12</v>
       </c>
       <c r="W29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X29" t="n">
         <v>500</v>
@@ -7775,10 +7775,10 @@
         <v>500</v>
       </c>
       <c r="Z29" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AA29" t="n">
-        <v>900</v>
+        <v>80</v>
       </c>
       <c r="AB29" t="n">
         <v>500</v>
@@ -7787,100 +7787,100 @@
         <v>29</v>
       </c>
       <c r="AD29" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
         <v>500</v>
       </c>
       <c r="AG29" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="AH29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI29" t="n">
         <v>19</v>
       </c>
       <c r="AJ29" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK29" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AL29" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AM29" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AO29" t="n">
         <v>3.5</v>
       </c>
       <c r="AP29" t="n">
-        <v>3.7</v>
+        <v>24</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="AR29" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>3.55</v>
+        <v>6.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.3</v>
+        <v>15.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>3.55</v>
+        <v>16</v>
       </c>
       <c r="AX29" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3.05</v>
+        <v>13.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>3.1</v>
+        <v>14.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BH29" t="n">
         <v>11</v>
       </c>
       <c r="BI29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BJ29" t="n">
         <v>8.800000000000001</v>
@@ -7889,28 +7889,28 @@
         <v>4.3</v>
       </c>
       <c r="BL29" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN29" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BO29" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP29" t="n">
         <v>25</v>
       </c>
       <c r="BQ29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR29" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BS29" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BT29" t="n">
         <v>8</v>
@@ -7922,23 +7922,23 @@
         <v>12.5</v>
       </c>
       <c r="BW29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BX29" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BY29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BZ29" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CA29" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G30" t="n">
         <v>1.94</v>
@@ -7981,7 +7981,7 @@
         <v>5.6</v>
       </c>
       <c r="J30" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K30" t="n">
         <v>3.55</v>
@@ -7999,10 +7999,10 @@
         <v>1.52</v>
       </c>
       <c r="P30" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R30" t="n">
         <v>1.21</v>
@@ -8011,13 +8011,13 @@
         <v>5.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U30" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W30" t="n">
         <v>2.06</v>
@@ -8026,7 +8026,7 @@
         <v>9.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="Z30" t="n">
         <v>95</v>
@@ -8041,7 +8041,7 @@
         <v>8</v>
       </c>
       <c r="AD30" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AE30" t="n">
         <v>700</v>
@@ -8062,7 +8062,7 @@
         <v>500</v>
       </c>
       <c r="AK30" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AL30" t="n">
         <v>460</v>
@@ -8083,13 +8083,13 @@
         <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU30" t="n">
         <v>7</v>
@@ -8098,10 +8098,10 @@
         <v>19.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY30" t="n">
         <v>9.800000000000001</v>
@@ -8110,25 +8110,25 @@
         <v>13</v>
       </c>
       <c r="BA30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB30" t="n">
         <v>19</v>
       </c>
       <c r="BC30" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BD30" t="n">
         <v>28</v>
       </c>
       <c r="BE30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BF30" t="n">
         <v>18.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH30" t="n">
         <v>2.82</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -8253,10 +8253,10 @@
         <v>1.4</v>
       </c>
       <c r="P31" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R31" t="n">
         <v>1.27</v>
@@ -8265,7 +8265,7 @@
         <v>4.2</v>
       </c>
       <c r="T31" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U31" t="n">
         <v>1.98</v>
@@ -8400,7 +8400,7 @@
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN31" t="n">
         <v>7.2</v>
@@ -8412,13 +8412,13 @@
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT31" t="n">
         <v>5.2</v>
@@ -8427,7 +8427,7 @@
         <v>4.4</v>
       </c>
       <c r="BV31" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW31" t="n">
         <v>7.2</v>
@@ -8436,17 +8436,17 @@
         <v>38</v>
       </c>
       <c r="BY31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ31" t="n">
         <v>36</v>
       </c>
       <c r="CA31" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
         <v>2.24</v>
       </c>
       <c r="H32" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I32" t="n">
         <v>4.1</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -8731,82 +8731,82 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="G33" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="H33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I33" t="n">
         <v>5.2</v>
       </c>
-      <c r="I33" t="n">
-        <v>5.6</v>
-      </c>
       <c r="J33" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L33" t="n">
         <v>1.49</v>
       </c>
       <c r="M33" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N33" t="n">
         <v>3.15</v>
       </c>
       <c r="O33" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P33" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R33" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S33" t="n">
         <v>4.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U33" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="V33" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W33" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="X33" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z33" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA33" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB33" t="n">
-        <v>17.5</v>
+        <v>7.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD33" t="n">
         <v>32</v>
       </c>
       <c r="AE33" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF33" t="n">
         <v>10.5</v>
@@ -8815,22 +8815,22 @@
         <v>970</v>
       </c>
       <c r="AH33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI33" t="n">
         <v>120</v>
       </c>
       <c r="AJ33" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AK33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM33" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN33" t="n">
         <v>18.5</v>
@@ -8842,25 +8842,25 @@
         <v>10</v>
       </c>
       <c r="AQ33" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AR33" t="n">
-        <v>3.55</v>
+        <v>7.8</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT33" t="n">
         <v>6.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV33" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AW33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX33" t="n">
         <v>8.199999999999999</v>
@@ -8869,31 +8869,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="BA33" t="n">
-        <v>3.75</v>
+        <v>9</v>
       </c>
       <c r="BB33" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC33" t="n">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="BD33" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="BF33" t="n">
         <v>13</v>
       </c>
       <c r="BG33" t="n">
-        <v>3.8</v>
+        <v>9.4</v>
       </c>
       <c r="BH33" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI33" t="n">
         <v>2.52</v>
@@ -8911,13 +8911,13 @@
         <v>1.01</v>
       </c>
       <c r="BN33" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BO33" t="n">
         <v>3.7</v>
       </c>
       <c r="BP33" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BQ33" t="n">
         <v>1.01</v>
@@ -8929,7 +8929,7 @@
         <v>1.01</v>
       </c>
       <c r="BT33" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU33" t="n">
         <v>1.01</v>
@@ -8947,14 +8947,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ33" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA33" t="n">
         <v>1.01</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -8991,13 +8991,13 @@
         <v>3.05</v>
       </c>
       <c r="H34" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="I34" t="n">
         <v>3.05</v>
       </c>
       <c r="J34" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K34" t="n">
         <v>3.3</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.86</v>
+        <v>3.45</v>
       </c>
       <c r="G2" t="n">
-        <v>1.88</v>
+        <v>3.95</v>
       </c>
       <c r="H2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>790</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU2" t="n">
         <v>4.6</v>
       </c>
-      <c r="I2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X2" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="AV2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE2" t="n">
         <v>65</v>
       </c>
-      <c r="AF2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ2" t="n">
+      <c r="BF2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>15</v>
       </c>
-      <c r="AR2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>44</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BK2" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>110</v>
+        <v>2.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.85</v>
+        <v>2.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="BR2" t="n">
+        <v>330</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BV2" t="n">
         <v>29</v>
       </c>
-      <c r="BS2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>44</v>
-      </c>
       <c r="BW2" t="n">
-        <v>9.800000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>2.48</v>
       </c>
       <c r="BZ2" t="n">
-        <v>25</v>
+        <v>830</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.4</v>
+        <v>2.48</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.86</v>
+        <v>1.41</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>1.02</v>
       </c>
       <c r="O3" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U3" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>9.800000000000001</v>
+        <v>860</v>
       </c>
       <c r="AH3" t="n">
-        <v>18</v>
+        <v>870</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>22</v>
+        <v>690</v>
       </c>
       <c r="AK3" t="n">
-        <v>18.5</v>
+        <v>990</v>
       </c>
       <c r="AL3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>10</v>
+        <v>990</v>
       </c>
       <c r="AO3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AR3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AS3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>1.13</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>15.5</v>
+        <v>1.13</v>
       </c>
       <c r="AW3" t="n">
-        <v>34</v>
+        <v>1.13</v>
       </c>
       <c r="AX3" t="n">
-        <v>11.5</v>
+        <v>4.9</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>2.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>42</v>
+        <v>2.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>18.5</v>
+        <v>1.13</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>1.13</v>
       </c>
       <c r="BD3" t="n">
-        <v>26</v>
+        <v>2.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>55</v>
+        <v>2.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>9</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
-        <v>29</v>
+        <v>1.13</v>
       </c>
       <c r="BH3" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>23</v>
+        <v>860</v>
       </c>
       <c r="BS3" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>17.5</v>
+        <v>820</v>
       </c>
       <c r="CA3" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -1365,94 +1365,94 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="G4" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P4" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="R4" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="T4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U4" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W4" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="X4" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="Y4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA4" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AB4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF4" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ4" t="n">
         <v>23</v>
@@ -1461,46 +1461,46 @@
         <v>15.5</v>
       </c>
       <c r="AL4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AT4" t="n">
         <v>21</v>
       </c>
-      <c r="AM4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP4" t="n">
+      <c r="AU4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW4" t="n">
         <v>36</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>34</v>
-      </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>13.5</v>
@@ -1515,80 +1515,80 @@
         <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BM4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BS4" t="n">
         <v>14</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV4" t="n">
         <v>26</v>
       </c>
       <c r="BW4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY4" t="n">
         <v>22</v>
       </c>
-      <c r="BX4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BZ4" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -1625,10 +1625,10 @@
         <v>2.18</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
         <v>2.92</v>
@@ -1646,7 +1646,7 @@
         <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P5" t="n">
         <v>1.48</v>
@@ -1655,7 +1655,7 @@
         <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S5" t="n">
         <v>6.2</v>
@@ -1670,22 +1670,22 @@
         <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="X5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
         <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC5" t="n">
         <v>7.6</v>
@@ -1697,7 +1697,7 @@
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
@@ -1715,13 +1715,13 @@
         <v>48</v>
       </c>
       <c r="AL5" t="n">
-        <v>460</v>
+        <v>170</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
@@ -1733,13 +1733,13 @@
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
@@ -1748,40 +1748,40 @@
         <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
         <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF5" t="n">
         <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BI5" t="n">
         <v>2.18</v>
@@ -1790,59 +1790,59 @@
         <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN5" t="n">
         <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR5" t="n">
         <v>48</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -1873,43 +1873,43 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J6" t="n">
         <v>2.92</v>
       </c>
       <c r="K6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="M6" t="n">
         <v>1.16</v>
       </c>
       <c r="N6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="P6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S6" t="n">
         <v>6.6</v>
@@ -1921,31 +1921,31 @@
         <v>1.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X6" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AA6" t="n">
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>19</v>
+        <v>8.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
         <v>500</v>
@@ -1957,7 +1957,7 @@
         <v>500</v>
       </c>
       <c r="AH6" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
         <v>540</v>
@@ -1975,34 +1975,34 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
         <v>7.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AV6" t="n">
         <v>5.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX6" t="n">
         <v>8.4</v>
@@ -2011,46 +2011,46 @@
         <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE6" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC6" t="n">
+      <c r="BF6" t="n">
         <v>7.2</v>
       </c>
-      <c r="BD6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.14</v>
-      </c>
       <c r="BG6" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
@@ -2062,41 +2062,41 @@
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BT6" t="n">
         <v>6</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -2130,73 +2130,73 @@
         <v>2.12</v>
       </c>
       <c r="G7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
         <v>3.35</v>
       </c>
       <c r="I7" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="J7" t="n">
         <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T7" t="n">
         <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA7" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AB7" t="n">
         <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
         <v>16</v>
@@ -2205,7 +2205,7 @@
         <v>46</v>
       </c>
       <c r="AF7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -2217,7 +2217,7 @@
         <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK7" t="n">
         <v>23</v>
@@ -2229,25 +2229,25 @@
         <v>200</v>
       </c>
       <c r="AN7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP7" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU7" t="n">
         <v>8.199999999999999</v>
@@ -2256,7 +2256,7 @@
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AX7" t="n">
         <v>13.5</v>
@@ -2268,10 +2268,10 @@
         <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BB7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC7" t="n">
         <v>17.5</v>
@@ -2280,31 +2280,31 @@
         <v>23</v>
       </c>
       <c r="BE7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BJ7" t="n">
         <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN7" t="n">
         <v>5.3</v>
@@ -2313,16 +2313,16 @@
         <v>4.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT7" t="n">
         <v>7</v>
@@ -2334,13 +2334,13 @@
         <v>36</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX7" t="n">
         <v>46</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G8" t="n">
         <v>2.18</v>
@@ -2393,10 +2393,10 @@
         <v>3.55</v>
       </c>
       <c r="J8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>1.33</v>
@@ -2411,22 +2411,22 @@
         <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
         <v>1.65</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
         <v>1.59</v>
       </c>
       <c r="U8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V8" t="n">
         <v>1.39</v>
@@ -2435,7 +2435,7 @@
         <v>1.84</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
         <v>18.5</v>
@@ -2444,19 +2444,19 @@
         <v>28</v>
       </c>
       <c r="AA8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB8" t="n">
         <v>13.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD8" t="n">
         <v>14.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF8" t="n">
         <v>16</v>
@@ -2465,13 +2465,13 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK8" t="n">
         <v>19.5</v>
@@ -2486,13 +2486,13 @@
         <v>11.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP8" t="n">
         <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR8" t="n">
         <v>25</v>
@@ -2513,7 +2513,7 @@
         <v>30</v>
       </c>
       <c r="AX8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
@@ -2540,10 +2540,10 @@
         <v>10</v>
       </c>
       <c r="BG8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI8" t="n">
         <v>3.75</v>
@@ -2552,13 +2552,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5.3</v>
@@ -2570,13 +2570,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR8" t="n">
         <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT8" t="n">
         <v>7</v>
@@ -2588,13 +2588,13 @@
         <v>24</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX8" t="n">
         <v>30</v>
       </c>
       <c r="BY8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -2641,16 +2641,16 @@
         <v>1.55</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="I9" t="n">
         <v>12.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.51</v>
@@ -2662,13 +2662,13 @@
         <v>2.84</v>
       </c>
       <c r="O9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R9" t="n">
         <v>1.21</v>
@@ -2677,31 +2677,31 @@
         <v>4.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V9" t="n">
         <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="X9" t="n">
         <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AC9" t="n">
         <v>42</v>
@@ -2710,19 +2710,19 @@
         <v>180</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AF9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
         <v>190</v>
       </c>
       <c r="AI9" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AJ9" t="n">
         <v>16</v>
@@ -2752,28 +2752,28 @@
         <v>6</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU9" t="n">
         <v>8.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AW9" t="n">
         <v>6.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA9" t="n">
         <v>6.2</v>
@@ -2782,10 +2782,10 @@
         <v>10.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="BE9" t="n">
         <v>6.2</v>
@@ -2794,10 +2794,10 @@
         <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BI9" t="n">
         <v>2.58</v>
@@ -2806,13 +2806,13 @@
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN9" t="n">
         <v>3.75</v>
@@ -2830,35 +2830,35 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT9" t="n">
         <v>14</v>
       </c>
       <c r="BU9" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K10" t="n">
         <v>3.1</v>
@@ -2913,13 +2913,13 @@
         <v>1.14</v>
       </c>
       <c r="N10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q10" t="n">
         <v>2.84</v>
@@ -2928,25 +2928,25 @@
         <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>500</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2955,25 +2955,25 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>500</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -2994,61 +2994,61 @@
         <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AW10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
         <v>30</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE10" t="n">
         <v>7</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BF10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG10" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.25</v>
       </c>
       <c r="BH10" t="n">
         <v>2.7</v>
@@ -3060,7 +3060,7 @@
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3072,7 +3072,7 @@
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
@@ -3087,13 +3087,13 @@
         <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G11" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H11" t="n">
         <v>4.5</v>
@@ -3158,7 +3158,7 @@
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.64</v>
@@ -3167,28 +3167,28 @@
         <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="O11" t="n">
         <v>1.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
         <v>1.15</v>
       </c>
       <c r="S11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V11" t="n">
         <v>1.22</v>
@@ -3197,7 +3197,7 @@
         <v>1.87</v>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y11" t="n">
         <v>21</v>
@@ -3212,7 +3212,7 @@
         <v>6.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
         <v>500</v>
@@ -3227,7 +3227,7 @@
         <v>36</v>
       </c>
       <c r="AH11" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AI11" t="n">
         <v>500</v>
@@ -3239,28 +3239,28 @@
         <v>500</v>
       </c>
       <c r="AL11" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AM11" t="n">
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>600</v>
+        <v>34</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT11" t="n">
         <v>5.1</v>
@@ -3269,40 +3269,40 @@
         <v>5.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AY11" t="n">
         <v>8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH11" t="n">
         <v>2.66</v>
@@ -3311,7 +3311,7 @@
         <v>2.18</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK11" t="n">
         <v>1.01</v>
@@ -3329,13 +3329,13 @@
         <v>3.8</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ11" t="n">
         <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>2.48</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J12" t="n">
         <v>2.72</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="L12" t="n">
         <v>1.66</v>
@@ -3421,7 +3421,7 @@
         <v>1.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O12" t="n">
         <v>1.63</v>
@@ -3430,7 +3430,7 @@
         <v>1.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>1.14</v>
@@ -3445,10 +3445,10 @@
         <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W12" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X12" t="n">
         <v>500</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -3654,37 +3654,37 @@
         <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H13" t="n">
         <v>2.68</v>
       </c>
       <c r="I13" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="K13" t="n">
         <v>3.05</v>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="M13" t="n">
         <v>1.16</v>
       </c>
       <c r="N13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O13" t="n">
         <v>1.7</v>
       </c>
       <c r="P13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
         <v>1.13</v>
@@ -3693,7 +3693,7 @@
         <v>6.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
         <v>1.61</v>
@@ -3717,13 +3717,13 @@
         <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC13" t="n">
         <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE13" t="n">
         <v>55</v>
@@ -3768,7 +3768,7 @@
         <v>12</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3780,7 +3780,7 @@
         <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX13" t="n">
         <v>16.5</v>
@@ -3789,31 +3789,31 @@
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="n">
         <v>25</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BI13" t="n">
         <v>2.1</v>
@@ -3822,13 +3822,13 @@
         <v>13</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN13" t="n">
         <v>6.4</v>
@@ -3840,13 +3840,13 @@
         <v>36</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR13" t="n">
         <v>70</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT13" t="n">
         <v>5.7</v>
@@ -3858,23 +3858,23 @@
         <v>29</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -3905,67 +3905,67 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="H14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I14" t="n">
         <v>6.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U14" t="n">
         <v>1.83</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X14" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
         <v>21</v>
       </c>
       <c r="Z14" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3974,161 +3974,161 @@
         <v>7.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD14" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AF14" t="n">
         <v>10.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
         <v>540</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
         <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
         <v>17.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA14" t="n">
-        <v>50</v>
+        <v>9.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC14" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BD14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
         <v>11</v>
       </c>
-      <c r="BG14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BN14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BP14" t="n">
         <v>13</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR14" t="n">
         <v>34</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -4159,79 +4159,79 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N15" t="n">
         <v>2.18</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="O15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3.2</v>
       </c>
-      <c r="L15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.94</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="S15" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="V15" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="AA15" t="n">
         <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AE15" t="n">
         <v>500</v>
@@ -4240,7 +4240,7 @@
         <v>13</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
         <v>65</v>
@@ -4267,76 +4267,76 @@
         <v>600</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU15" t="n">
         <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
       </c>
       <c r="AY15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE15" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>10</v>
       </c>
       <c r="BF15" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="BJ15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN15" t="n">
         <v>5</v>
@@ -4345,44 +4345,44 @@
         <v>3.7</v>
       </c>
       <c r="BP15" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -4413,40 +4413,40 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
         <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="R16" t="n">
         <v>1.21</v>
@@ -4455,22 +4455,22 @@
         <v>4.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U16" t="n">
         <v>1.73</v>
       </c>
       <c r="V16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z16" t="n">
         <v>42</v>
@@ -4479,7 +4479,7 @@
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC16" t="n">
         <v>8.199999999999999</v>
@@ -4488,7 +4488,7 @@
         <v>23</v>
       </c>
       <c r="AE16" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AF16" t="n">
         <v>11.5</v>
@@ -4503,10 +4503,10 @@
         <v>540</v>
       </c>
       <c r="AJ16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL16" t="n">
         <v>60</v>
@@ -4515,22 +4515,22 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>700</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT16" t="n">
         <v>5.7</v>
@@ -4542,101 +4542,101 @@
         <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>8.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ16" t="n">
         <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB16" t="n">
         <v>18.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD16" t="n">
         <v>38</v>
       </c>
       <c r="BE16" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ16" t="n">
         <v>12.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO16" t="n">
         <v>3.45</v>
       </c>
       <c r="BP16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BR16" t="n">
         <v>40</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT16" t="n">
         <v>9</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV16" t="n">
         <v>60</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX16" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ16" t="n">
         <v>40</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L17" t="n">
         <v>1.6</v>
@@ -4691,61 +4691,61 @@
         <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O17" t="n">
         <v>1.58</v>
       </c>
       <c r="P17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q17" t="n">
         <v>2.78</v>
       </c>
       <c r="R17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S17" t="n">
         <v>5.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W17" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="X17" t="n">
         <v>8.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AA17" t="n">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE17" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AF17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG17" t="n">
         <v>14.5</v>
@@ -4754,143 +4754,143 @@
         <v>38</v>
       </c>
       <c r="AI17" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AJ17" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK17" t="n">
         <v>27</v>
       </c>
       <c r="AL17" t="n">
-        <v>540</v>
+        <v>170</v>
       </c>
       <c r="AM17" t="n">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="AN17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>620</v>
+        <v>500</v>
       </c>
       <c r="AP17" t="n">
         <v>6.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS17" t="n">
         <v>8</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AW17" t="n">
         <v>7.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BA17" t="n">
         <v>7.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG17" t="n">
         <v>8</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BJ17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BO17" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BP17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -4924,10 +4924,10 @@
         <v>2.26</v>
       </c>
       <c r="G18" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I18" t="n">
         <v>3.2</v>
@@ -4942,7 +4942,7 @@
         <v>1.31</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
         <v>5.5</v>
@@ -4954,16 +4954,16 @@
         <v>2.52</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S18" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="T18" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="U18" t="n">
         <v>2.62</v>
@@ -4972,10 +4972,10 @@
         <v>1.45</v>
       </c>
       <c r="W18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y18" t="n">
         <v>22</v>
@@ -4990,7 +4990,7 @@
         <v>16.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
         <v>16.5</v>
@@ -4999,13 +4999,13 @@
         <v>40</v>
       </c>
       <c r="AF18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI18" t="n">
         <v>95</v>
@@ -5014,22 +5014,22 @@
         <v>34</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>14.5</v>
@@ -5047,28 +5047,28 @@
         <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
         <v>23</v>
       </c>
       <c r="AX18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA18" t="n">
         <v>26</v>
       </c>
       <c r="BB18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BD18" t="n">
         <v>23</v>
@@ -5080,46 +5080,46 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG18" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BH18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU18" t="n">
         <v>5.8</v>
@@ -5128,13 +5128,13 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -5178,67 +5178,67 @@
         <v>1.7</v>
       </c>
       <c r="G19" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="H19" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I19" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P19" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R19" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T19" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W19" t="n">
         <v>2.34</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.4</v>
       </c>
       <c r="X19" t="n">
         <v>22</v>
       </c>
       <c r="Y19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
         <v>11.5</v>
@@ -5247,10 +5247,10 @@
         <v>10.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE19" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AF19" t="n">
         <v>12</v>
@@ -5265,46 +5265,46 @@
         <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK19" t="n">
         <v>16.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AM19" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AN19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP19" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR19" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AS19" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="AT19" t="n">
         <v>10</v>
       </c>
       <c r="AU19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW19" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -5313,52 +5313,52 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA19" t="n">
         <v>50</v>
       </c>
       <c r="BB19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE19" t="n">
         <v>65</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="BJ19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BP19" t="n">
         <v>11</v>
@@ -5370,25 +5370,25 @@
         <v>22</v>
       </c>
       <c r="BS19" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT19" t="n">
         <v>9</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -5429,16 +5429,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="H20" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I20" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
         <v>3.6</v>
@@ -5450,46 +5450,46 @@
         <v>1.4</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N20" t="n">
         <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V20" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W20" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
         <v>17</v>
       </c>
       <c r="Y20" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
         <v>44</v>
@@ -5507,7 +5507,7 @@
         <v>34</v>
       </c>
       <c r="AF20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG20" t="n">
         <v>15</v>
@@ -5519,7 +5519,7 @@
         <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK20" t="n">
         <v>42</v>
@@ -5531,7 +5531,7 @@
         <v>320</v>
       </c>
       <c r="AN20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO20" t="n">
         <v>25</v>
@@ -5540,10 +5540,10 @@
         <v>13.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AS20" t="n">
         <v>30</v>
@@ -5555,22 +5555,22 @@
         <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
         <v>22</v>
       </c>
       <c r="AX20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB20" t="n">
         <v>34</v>
@@ -5585,46 +5585,46 @@
         <v>60</v>
       </c>
       <c r="BF20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BG20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK20" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BN20" t="n">
         <v>6</v>
       </c>
       <c r="BO20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT20" t="n">
         <v>5.7</v>
@@ -5636,13 +5636,13 @@
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY20" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -5683,19 +5683,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G21" t="n">
         <v>1.34</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="I21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J21" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K21" t="n">
         <v>6.2</v>
@@ -5713,19 +5713,19 @@
         <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R21" t="n">
         <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
         <v>1.89</v>
@@ -5734,7 +5734,7 @@
         <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="X21" t="n">
         <v>22</v>
@@ -5743,25 +5743,25 @@
         <v>40</v>
       </c>
       <c r="Z21" t="n">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AA21" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="AB21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC21" t="n">
         <v>14</v>
       </c>
       <c r="AD21" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AE21" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AF21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG21" t="n">
         <v>10.5</v>
@@ -5770,7 +5770,7 @@
         <v>32</v>
       </c>
       <c r="AI21" t="n">
-        <v>170</v>
+        <v>470</v>
       </c>
       <c r="AJ21" t="n">
         <v>10.5</v>
@@ -5782,13 +5782,13 @@
         <v>40</v>
       </c>
       <c r="AM21" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN21" t="n">
         <v>5.2</v>
       </c>
       <c r="AO21" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AP21" t="n">
         <v>19.5</v>
@@ -5797,25 +5797,25 @@
         <v>34</v>
       </c>
       <c r="AR21" t="n">
-        <v>14.5</v>
+        <v>46</v>
       </c>
       <c r="AS21" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV21" t="n">
         <v>36</v>
       </c>
       <c r="AW21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY21" t="n">
         <v>9.6</v>
@@ -5824,7 +5824,7 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BB21" t="n">
         <v>9</v>
@@ -5836,37 +5836,37 @@
         <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BF21" t="n">
         <v>4.7</v>
       </c>
       <c r="BG21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH21" t="n">
         <v>4.2</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ21" t="n">
         <v>12.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP21" t="n">
         <v>7.6</v>
@@ -5878,10 +5878,10 @@
         <v>24</v>
       </c>
       <c r="BS21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BU21" t="n">
         <v>9.6</v>
@@ -5890,13 +5890,13 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -5940,16 +5940,16 @@
         <v>2.52</v>
       </c>
       <c r="G22" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H22" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
         <v>3.55</v>
@@ -5958,10 +5958,10 @@
         <v>1.38</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
         <v>1.27</v>
@@ -5985,16 +5985,16 @@
         <v>2.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X22" t="n">
         <v>17.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z22" t="n">
         <v>23</v>
@@ -6003,7 +6003,7 @@
         <v>50</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC22" t="n">
         <v>8.6</v>
@@ -6015,7 +6015,7 @@
         <v>34</v>
       </c>
       <c r="AF22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG22" t="n">
         <v>12.5</v>
@@ -6030,19 +6030,19 @@
         <v>80</v>
       </c>
       <c r="AK22" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AL22" t="n">
         <v>40</v>
       </c>
       <c r="AM22" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN22" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="n">
-        <v>600</v>
+        <v>27</v>
       </c>
       <c r="AP22" t="n">
         <v>13</v>
@@ -6051,7 +6051,7 @@
         <v>11.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS22" t="n">
         <v>34</v>
@@ -6060,16 +6060,16 @@
         <v>10</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV22" t="n">
         <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
@@ -6081,10 +6081,10 @@
         <v>32</v>
       </c>
       <c r="BB22" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="BC22" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="BD22" t="n">
         <v>26</v>
@@ -6093,7 +6093,7 @@
         <v>23</v>
       </c>
       <c r="BF22" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BG22" t="n">
         <v>21</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H23" t="n">
         <v>4.2</v>
@@ -6203,16 +6203,16 @@
         <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L23" t="n">
         <v>1.44</v>
       </c>
       <c r="M23" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N23" t="n">
         <v>3.55</v>
@@ -6236,16 +6236,16 @@
         <v>1.89</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V23" t="n">
         <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y23" t="n">
         <v>17</v>
@@ -6254,19 +6254,19 @@
         <v>32</v>
       </c>
       <c r="AA23" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AB23" t="n">
         <v>9.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
         <v>21</v>
       </c>
       <c r="AE23" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF23" t="n">
         <v>14.5</v>
@@ -6278,7 +6278,7 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ23" t="n">
         <v>27</v>
@@ -6305,7 +6305,7 @@
         <v>12.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS23" t="n">
         <v>60</v>
@@ -6326,7 +6326,7 @@
         <v>10.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
         <v>17.5</v>
@@ -6344,7 +6344,7 @@
         <v>29</v>
       </c>
       <c r="BE23" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF23" t="n">
         <v>15.5</v>
@@ -6374,7 +6374,7 @@
         <v>4.7</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BP23" t="n">
         <v>15</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -6448,22 +6448,22 @@
         <v>5.3</v>
       </c>
       <c r="G24" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H24" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I24" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
         <v>4.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
@@ -6475,25 +6475,25 @@
         <v>1.29</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T24" t="n">
         <v>1.84</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V24" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="W24" t="n">
         <v>1.21</v>
@@ -6508,22 +6508,22 @@
         <v>11</v>
       </c>
       <c r="AA24" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AB24" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE24" t="n">
         <v>18</v>
       </c>
       <c r="AF24" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG24" t="n">
         <v>21</v>
@@ -6532,22 +6532,22 @@
         <v>20</v>
       </c>
       <c r="AI24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ24" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="n">
         <v>80</v>
       </c>
       <c r="AL24" t="n">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO24" t="n">
         <v>10.5</v>
@@ -6565,7 +6565,7 @@
         <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AU24" t="n">
         <v>8.4</v>
@@ -6589,86 +6589,86 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="BC24" t="n">
         <v>32</v>
       </c>
       <c r="BD24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE24" t="n">
         <v>29</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>28</v>
       </c>
       <c r="BF24" t="n">
         <v>14</v>
       </c>
       <c r="BG24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BJ24" t="n">
         <v>10.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BN24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ24" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS24" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BT24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BV24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BW24" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY24" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BZ24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA24" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -6702,19 +6702,19 @@
         <v>4.8</v>
       </c>
       <c r="G25" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="I25" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="J25" t="n">
         <v>5.1</v>
       </c>
       <c r="K25" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L25" t="n">
         <v>1.19</v>
@@ -6723,22 +6723,22 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O25" t="n">
         <v>1.1</v>
       </c>
       <c r="P25" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R25" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S25" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="T25" t="n">
         <v>1.43</v>
@@ -6747,10 +6747,10 @@
         <v>3</v>
       </c>
       <c r="V25" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="W25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
         <v>55</v>
@@ -6759,16 +6759,16 @@
         <v>22</v>
       </c>
       <c r="Z25" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA25" t="n">
         <v>19.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AC25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD25" t="n">
         <v>12</v>
@@ -6777,13 +6777,13 @@
         <v>15.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AG25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH25" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI25" t="n">
         <v>21</v>
@@ -6792,25 +6792,25 @@
         <v>700</v>
       </c>
       <c r="AK25" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AL25" t="n">
         <v>38</v>
       </c>
       <c r="AM25" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO25" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AP25" t="n">
         <v>29</v>
       </c>
       <c r="AQ25" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR25" t="n">
         <v>15.5</v>
@@ -6828,25 +6828,25 @@
         <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX25" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AY25" t="n">
         <v>19</v>
       </c>
       <c r="AZ25" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA25" t="n">
         <v>18</v>
       </c>
       <c r="BB25" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BC25" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BD25" t="n">
         <v>30</v>
@@ -6858,7 +6858,7 @@
         <v>20</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BH25" t="n">
         <v>6.2</v>
@@ -6870,7 +6870,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
@@ -6879,7 +6879,7 @@
         <v>10.5</v>
       </c>
       <c r="BN25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO25" t="n">
         <v>5.7</v>
@@ -6888,13 +6888,13 @@
         <v>32</v>
       </c>
       <c r="BQ25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR25" t="n">
         <v>29</v>
       </c>
       <c r="BS25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT25" t="n">
         <v>5.4</v>
@@ -6906,7 +6906,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BW25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX25" t="n">
         <v>16</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -6953,55 +6953,55 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H26" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I26" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>3.9</v>
       </c>
       <c r="K26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O26" t="n">
         <v>1.15</v>
       </c>
       <c r="P26" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R26" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="S26" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="T26" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U26" t="n">
         <v>2.84</v>
       </c>
       <c r="V26" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W26" t="n">
         <v>1.66</v>
@@ -7010,76 +7010,76 @@
         <v>40</v>
       </c>
       <c r="Y26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z26" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AA26" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD26" t="n">
         <v>15.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AF26" t="n">
         <v>23</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH26" t="n">
         <v>14.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AJ26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL26" t="n">
         <v>38</v>
       </c>
-      <c r="AK26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>40</v>
-      </c>
       <c r="AM26" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AN26" t="n">
         <v>11</v>
       </c>
       <c r="AO26" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AP26" t="n">
         <v>23</v>
       </c>
       <c r="AQ26" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV26" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW26" t="n">
         <v>19.5</v>
@@ -7097,7 +7097,7 @@
         <v>22</v>
       </c>
       <c r="BB26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC26" t="n">
         <v>18</v>
@@ -7112,19 +7112,19 @@
         <v>8.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ26" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK26" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
@@ -7136,13 +7136,13 @@
         <v>6.6</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BP26" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR26" t="n">
         <v>23</v>
@@ -7160,23 +7160,23 @@
         <v>19.5</v>
       </c>
       <c r="BW26" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY26" t="n">
         <v>6</v>
       </c>
       <c r="BZ26" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA26" t="n">
         <v>5.1</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G27" t="n">
         <v>4.4</v>
@@ -7222,7 +7222,7 @@
         <v>4.3</v>
       </c>
       <c r="K27" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L27" t="n">
         <v>1.24</v>
@@ -7231,28 +7231,28 @@
         <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O27" t="n">
         <v>1.14</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="R27" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="S27" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="T27" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U27" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V27" t="n">
         <v>2.12</v>
@@ -7261,7 +7261,7 @@
         <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="Y27" t="n">
         <v>970</v>
@@ -7291,10 +7291,10 @@
         <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="AI27" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AJ27" t="n">
         <v>500</v>
@@ -7309,61 +7309,61 @@
         <v>580</v>
       </c>
       <c r="AN27" t="n">
-        <v>600</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AR27" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AV27" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AW27" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AX27" t="n">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="AZ27" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC27" t="n">
-        <v>7.6</v>
+        <v>16.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="BE27" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="BG27" t="n">
         <v>5.8</v>
@@ -7372,37 +7372,37 @@
         <v>5.3</v>
       </c>
       <c r="BI27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN27" t="n">
         <v>8.6</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT27" t="n">
         <v>5.5</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -7464,10 +7464,10 @@
         <v>1.68</v>
       </c>
       <c r="G28" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I28" t="n">
         <v>5.9</v>
@@ -7476,7 +7476,7 @@
         <v>4.3</v>
       </c>
       <c r="K28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L28" t="n">
         <v>1.3</v>
@@ -7485,13 +7485,13 @@
         <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O28" t="n">
         <v>1.21</v>
       </c>
       <c r="P28" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q28" t="n">
         <v>1.63</v>
@@ -7506,19 +7506,19 @@
         <v>1.69</v>
       </c>
       <c r="U28" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V28" t="n">
         <v>1.21</v>
       </c>
       <c r="W28" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X28" t="n">
         <v>24</v>
       </c>
       <c r="Y28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z28" t="n">
         <v>48</v>
@@ -7536,7 +7536,7 @@
         <v>23</v>
       </c>
       <c r="AE28" t="n">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="AF28" t="n">
         <v>12</v>
@@ -7563,7 +7563,7 @@
         <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO28" t="n">
         <v>65</v>
@@ -7572,10 +7572,10 @@
         <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR28" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AS28" t="n">
         <v>9.4</v>
@@ -7590,7 +7590,7 @@
         <v>18.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX28" t="n">
         <v>9.6</v>
@@ -7602,7 +7602,7 @@
         <v>16</v>
       </c>
       <c r="BA28" t="n">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB28" t="n">
         <v>14.5</v>
@@ -7614,16 +7614,16 @@
         <v>22</v>
       </c>
       <c r="BE28" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="BF28" t="n">
         <v>6.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI28" t="n">
         <v>3.8</v>
@@ -7632,59 +7632,59 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN28" t="n">
         <v>4.7</v>
       </c>
       <c r="BO28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP28" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BR28" t="n">
         <v>22</v>
       </c>
       <c r="BS28" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT28" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU28" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BV28" t="n">
         <v>42</v>
       </c>
       <c r="BW28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX28" t="n">
         <v>44</v>
       </c>
       <c r="BY28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ28" t="n">
         <v>14.5</v>
       </c>
       <c r="CA28" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -7718,28 +7718,28 @@
         <v>3.45</v>
       </c>
       <c r="G29" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="I29" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="J29" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="K29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L29" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.11</v>
+        <v>7.6</v>
       </c>
       <c r="O29" t="n">
         <v>1.01</v>
@@ -7751,7 +7751,7 @@
         <v>1.11</v>
       </c>
       <c r="R29" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="S29" t="n">
         <v>1.32</v>
@@ -7760,13 +7760,13 @@
         <v>1.2</v>
       </c>
       <c r="U29" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="V29" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="W29" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X29" t="n">
         <v>500</v>
@@ -7784,7 +7784,7 @@
         <v>500</v>
       </c>
       <c r="AC29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AD29" t="n">
         <v>21</v>
@@ -7796,22 +7796,22 @@
         <v>500</v>
       </c>
       <c r="AG29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH29" t="n">
         <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AJ29" t="n">
         <v>500</v>
       </c>
       <c r="AK29" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AL29" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="AM29" t="n">
         <v>26</v>
@@ -7820,125 +7820,125 @@
         <v>9.6</v>
       </c>
       <c r="AO29" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AP29" t="n">
         <v>24</v>
       </c>
       <c r="AQ29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR29" t="n">
         <v>7</v>
       </c>
-      <c r="AR29" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AS29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT29" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>15.5</v>
+        <v>5.9</v>
       </c>
       <c r="AW29" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>13.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA29" t="n">
-        <v>14.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD29" t="n">
         <v>6.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BH29" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BI29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BJ29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BL29" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BM29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BN29" t="n">
         <v>12</v>
       </c>
       <c r="BO29" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BP29" t="n">
         <v>25</v>
       </c>
       <c r="BQ29" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR29" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BS29" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BT29" t="n">
         <v>8</v>
       </c>
       <c r="BU29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="CA29" t="n">
         <v>4.1</v>
       </c>
-      <c r="BV29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BW29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BX29" t="n">
-        <v>13</v>
-      </c>
-      <c r="BY29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BZ29" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="CA29" t="n">
-        <v>3.3</v>
-      </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G30" t="n">
         <v>1.94</v>
@@ -7984,7 +7984,7 @@
         <v>3.35</v>
       </c>
       <c r="K30" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L30" t="n">
         <v>1.56</v>
@@ -7993,7 +7993,7 @@
         <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O30" t="n">
         <v>1.52</v>
@@ -8035,13 +8035,13 @@
         <v>900</v>
       </c>
       <c r="AB30" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC30" t="n">
         <v>8</v>
       </c>
       <c r="AD30" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AE30" t="n">
         <v>700</v>
@@ -8059,10 +8059,10 @@
         <v>700</v>
       </c>
       <c r="AJ30" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AL30" t="n">
         <v>460</v>
@@ -8071,7 +8071,7 @@
         <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
         <v>700</v>
@@ -8083,13 +8083,13 @@
         <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="AS30" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU30" t="n">
         <v>7</v>
@@ -8098,7 +8098,7 @@
         <v>19.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AX30" t="n">
         <v>8.6</v>
@@ -8107,34 +8107,34 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA30" t="n">
         <v>13</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>14</v>
       </c>
       <c r="BB30" t="n">
         <v>19</v>
       </c>
       <c r="BC30" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE30" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG30" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BH30" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ30" t="n">
         <v>12</v>
@@ -8155,22 +8155,22 @@
         <v>3.85</v>
       </c>
       <c r="BP30" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT30" t="n">
         <v>8.6</v>
       </c>
       <c r="BU30" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
@@ -8188,11 +8188,11 @@
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -8226,52 +8226,52 @@
         <v>3.65</v>
       </c>
       <c r="G31" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H31" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K31" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L31" t="n">
         <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P31" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T31" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U31" t="n">
         <v>1.98</v>
       </c>
       <c r="V31" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W31" t="n">
         <v>1.35</v>
@@ -8280,55 +8280,55 @@
         <v>12.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z31" t="n">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AB31" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AC31" t="n">
         <v>8</v>
       </c>
       <c r="AD31" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AF31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>500</v>
       </c>
-      <c r="AG31" t="n">
-        <v>500</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>900</v>
-      </c>
       <c r="AK31" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AL31" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AM31" t="n">
         <v>580</v>
       </c>
       <c r="AN31" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO31" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AP31" t="n">
         <v>10</v>
@@ -8340,7 +8340,7 @@
         <v>11.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
@@ -8349,104 +8349,104 @@
         <v>6.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW31" t="n">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="AX31" t="n">
         <v>20</v>
       </c>
       <c r="AY31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6.6</v>
+        <v>16.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BB31" t="n">
-        <v>8.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="BC31" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BD31" t="n">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BE31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BG31" t="n">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BJ31" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK31" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BN31" t="n">
         <v>7.2</v>
       </c>
       <c r="BO31" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BR31" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS31" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT31" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU31" t="n">
         <v>4.4</v>
       </c>
       <c r="BV31" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW31" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BX31" t="n">
         <v>38</v>
       </c>
       <c r="BY31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ31" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G32" t="n">
         <v>2.24</v>
@@ -8486,13 +8486,13 @@
         <v>3.7</v>
       </c>
       <c r="I32" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J32" t="n">
         <v>3.35</v>
       </c>
       <c r="K32" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8731,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="G33" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="H33" t="n">
         <v>4.8</v>
       </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K33" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L33" t="n">
         <v>1.49</v>
@@ -8758,13 +8758,13 @@
         <v>3.15</v>
       </c>
       <c r="O33" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P33" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R33" t="n">
         <v>1.26</v>
@@ -8773,188 +8773,188 @@
         <v>4.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V33" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W33" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X33" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AA33" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB33" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AE33" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF33" t="n">
         <v>10.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI33" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AJ33" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK33" t="n">
         <v>24</v>
       </c>
       <c r="AL33" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM33" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN33" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO33" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AP33" t="n">
         <v>10</v>
       </c>
       <c r="AQ33" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AR33" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.9</v>
+        <v>32</v>
       </c>
       <c r="AT33" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AW33" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="AX33" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA33" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BB33" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD33" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BE33" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="BF33" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="BH33" t="n">
         <v>3.05</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BJ33" t="n">
         <v>11</v>
       </c>
       <c r="BK33" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BN33" t="n">
         <v>4.4</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BP33" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BT33" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU33" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BZ33" t="n">
         <v>32</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G34" t="n">
         <v>3.05</v>
       </c>
       <c r="H34" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I34" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>3.1</v>
       </c>
       <c r="K34" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,78 +843,78 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.98</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
-        <v>1.99</v>
+        <v>260</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4</v>
+        <v>1.17</v>
       </c>
       <c r="I2" t="n">
-        <v>6.8</v>
+        <v>1.18</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9</v>
+        <v>6.6</v>
       </c>
       <c r="K2" t="n">
-        <v>2.94</v>
+        <v>7.6</v>
       </c>
       <c r="L2" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.17</v>
+        <v>6</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -923,10 +923,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -935,7 +935,7 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
         <v>1000</v>
@@ -944,7 +944,7 @@
         <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>1.36</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -956,131 +956,131 @@
         <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.3</v>
+        <v>50</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.3</v>
+        <v>50</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>50</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.3</v>
+        <v>50</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.3</v>
+        <v>55</v>
       </c>
       <c r="AX2" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.3</v>
+        <v>50</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.3</v>
+        <v>1.33</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.3</v>
+        <v>50</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.3</v>
+        <v>50</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.2</v>
+        <v>50</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.3</v>
+        <v>9.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>530</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -1097,1006 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.71</v>
+        <v>11.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.82</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7</v>
+        <v>1.46</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6</v>
+        <v>1.49</v>
       </c>
       <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>3.55</v>
       </c>
-      <c r="K3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>6</v>
-      </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>2.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="S3" t="n">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>1.19</v>
+        <v>3.05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.26</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>460</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR3" t="n">
         <v>5.6</v>
       </c>
-      <c r="AD3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO3" t="n">
+      <c r="AS3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC3" t="n">
         <v>75</v>
       </c>
-      <c r="AP3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>20</v>
-      </c>
       <c r="BD3" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="BE3" t="n">
-        <v>90</v>
+        <v>13.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>28</v>
+        <v>220</v>
       </c>
       <c r="BG3" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>12.5</v>
+        <v>1.25</v>
       </c>
       <c r="BJ3" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>1.25</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>1.25</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.46</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9</v>
+        <v>1.25</v>
       </c>
       <c r="BR3" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>40</v>
+        <v>1.25</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>1.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>890</v>
       </c>
       <c r="BW3" t="n">
-        <v>12.5</v>
+        <v>1.25</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>14.5</v>
+        <v>1.25</v>
       </c>
       <c r="BZ3" t="n">
-        <v>830</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>85</v>
+        <v>1.25</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Uruguayan Primera Division</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Deportivo Maldonado</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Albion FC</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>370</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>520</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>110</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>250</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>200</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>800</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>800</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-07-10 19:47:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>940</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>130</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>95</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>160</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>65</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>40</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-07-10 19:47:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:15:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Tecnico Universitario</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Macara</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>140</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>170</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>55</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
